--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'르노 트랜스폰더 DB'!$A$1:$N$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'르노 트랜스폰더 DB'!$A$1:$N$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,17 +52,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF9C6500"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="FF9C0006"/>
       <sz val="10"/>
     </font>
@@ -91,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -145,12 +140,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -520,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -639,13 +628,13 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60) 또는 ID46(PCF7936) 추정</t>
+          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -658,12 +647,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(SM3 2002.9.2 판매 개시, 블루버드 실피 G10 기반), abkeys.com(닛산 4D-60 NSN14 1999+)</t>
+          <t>wikipedia(SM3 2002.9.2 판매 개시, 블루버드 실피 G10 기반), abkeys.com(닛산 4D-60 NSN14 1999+), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>SM3 1세대 칩을 직접 밝힌 자료 없음 — 닛산 블루버드 실피 기준 추정(실물 키 확인 필요) / 닛산은 2003 전후로 4D60→ID46 전환</t>
+          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음 / 닛산 일본판 초기형은 4D60 사례 있어 실물 확인 필요</t>
         </is>
       </c>
     </row>
@@ -695,13 +684,13 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936) 추정(닛산 2003+ NSN14 기준)</t>
+          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -714,12 +703,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>gskeyae.com(2003+ 닛산 NSN14 PCF7936 ID46), kecool.com(ICC: 르노삼성 SM3·SM5·SM7 12자리 코드)</t>
+          <t>gskeyae.com(2003+ 닛산 NSN14 PCF7936 ID46), kecool.com(ICC: 르노삼성 SM3·SM5·SM7 12자리 코드), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>SM3 1세대 칩을 직접 밝힌 자료 없음 — 닛산 블루버드 실피 기준 추정(실물 키 확인 필요)</t>
+          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음</t>
         </is>
       </c>
     </row>
@@ -751,13 +740,13 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936) 추정(닛산 2003+ NSN14 기준)</t>
+          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -770,12 +759,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>abkeys.com(닛산 NSN14 PCF7936 ID46 2003+), nissanforums.com(블루버드 실피 2004 이그니션)</t>
+          <t>abkeys.com(닛산 NSN14 PCF7936 ID46 2003+), nissanforums.com(블루버드 실피 2004 이그니션), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>SM3 1세대 칩을 직접 밝힌 자료 없음 — 닛산 블루버드 실피 기준 추정(실물 키 확인 필요)</t>
+          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음</t>
         </is>
       </c>
     </row>
@@ -807,13 +796,13 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936) 추정(닛산 2003+ NSN14 기준)</t>
+          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -826,12 +815,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>gskeyae.com(2003+ NSN14 ID46), namu.wiki(2005.8 뉴 제너레이션 페이스리프트)</t>
+          <t>gskeyae.com(2003+ NSN14 ID46), namu.wiki(2005.8 뉴 제너레이션 페이스리프트), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>SM3 1세대 칩을 직접 밝힌 자료 없음 — 닛산 블루버드 실피 기준 추정(실물 키 확인 필요)</t>
+          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음</t>
         </is>
       </c>
     </row>
@@ -861,33 +850,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936) 추정(닛산 NSN14 기준)</t>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>danawa(SM3 뉴 제너레이션 N17 제원), namu.wiki(2005.8 뉴 제너레이션 출시)</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>칩 직접 자료 없음 — 닛산 동일 플랫폼 기준 추정 / 1세대와 연식 겹침</t>
+          <t>danawa(SM3 뉴 제너레이션 N17 제원), namu.wiki(2005.8 뉴 제너레이션 출시), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인 / 1세대와 연식 겹침</t>
         </is>
       </c>
     </row>
@@ -917,33 +906,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936) 추정(닛산 NSN14 기준)</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>clien.net(구형 SM3 리모컨키 CR2032), abkeys.com(닛산 NSN14 PCF7936 ID46 2003+)</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>칩 직접 자료 없음 — 닛산 동일 플랫폼 기준 추정</t>
+          <t>clien.net(구형 SM3 리모컨키 CR2032), abkeys.com(닛산 NSN14 PCF7936 ID46 2003+), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
         </is>
       </c>
     </row>
@@ -973,33 +962,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936) 추정(닛산 NSN14 기준)</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>carisyou.com(2007 SM3 뉴제너레이션), gskeyae.com(2003+ NSN14 ID46)</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>칩 직접 자료 없음 — 닛산 동일 플랫폼 기준 추정</t>
+          <t>carisyou.com(2007 SM3 뉴제너레이션), gskeyae.com(2003+ NSN14 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
         </is>
       </c>
     </row>
@@ -1029,33 +1018,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936) 추정(닛산 NSN14 기준)</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>danawa(SM3 뉴 제너레이션), interpark(뉴SM3 리모컨 폴딩키 케이스)</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>칩 직접 자료 없음 — 닛산 동일 플랫폼 기준 추정</t>
+          <t>danawa(SM3 뉴 제너레이션), interpark(뉴SM3 리모컨 폴딩키 케이스), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
         </is>
       </c>
     </row>
@@ -1085,33 +1074,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936) 추정(닛산 NSN14 기준)</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(2009.11 2세대 판매 개시, 구형 병행), gskeyae.com(NSN14 ID46), ko.wikipedia(SM3 CE 2009.7.13 출시)</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>칩 직접 자료 없음 — 닛산 동일 플랫폼 기준 추정 / 2세대(L38)와 병행 판매</t>
+          <t>wikipedia(2009.11 2세대 판매 개시, 구형 병행), gskeyae.com(NSN14 ID46), ko.wikipedia(SM3 CE 2009.7.13 출시), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인 / 2세대(L38)와 병행 판매</t>
         </is>
       </c>
     </row>
@@ -1141,33 +1130,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936) 추정(닛산 NSN14 기준)</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>dailycar.co.kr(SM3 CE 2009.7 출시, 신·구형 병행 판매), abkeys.com(NSN14 PCF7936 ID46)</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>칩 직접 자료 없음 — 닛산 동일 플랫폼 기준 추정 / 2세대(L38)와 병행 판매</t>
+          <t>dailycar.co.kr(SM3 CE 2009.7 출시, 신·구형 병행 판매), abkeys.com(NSN14 PCF7936 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인 / 2세대(L38)와 병행 판매</t>
         </is>
       </c>
     </row>
@@ -1197,33 +1186,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936) 추정(닛산 NSN14 기준)</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>NSN14 (닛산 기준)</t>
+          <t>NSN14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>ko.wikipedia(SM3 CE 2011.3.31 단종), gskeyae.com(2003-2020 닛산 NSN14 ID46)</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>칩 직접 자료 없음 — 닛산 동일 플랫폼 기준 추정</t>
+          <t>ko.wikipedia(SM3 CE 2011.3.31 단종), gskeyae.com(2003-2020 닛산 NSN14 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
         </is>
       </c>
     </row>
@@ -1586,14 +1575,14 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1603,7 +1592,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1626,12 +1615,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>ebay(플루언스 2012-2016 ID46 PCF7952A 카드키), hankyung.com(2016년형 SM3 네오 2015.4), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
+          <t>ebay(플루언스 2012-2016 ID46 PCF7952A 카드키), hankyung.com(2016년형 SM3 네오 2015.4), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Abrites RR018은 메간3 2015+·SM3를 신형 목록에 포함 — 후기형 UCH/칩 변경 여부 미확인</t>
+          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
         </is>
       </c>
     </row>
@@ -1646,14 +1635,14 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1663,7 +1652,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1686,12 +1675,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>ebay(플루언스 2012-2016 카드키), keyshop-online.com(플루언스 VA2 ID46), hankyung.com(2016년형 SM3 네오), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
+          <t>ebay(플루언스 2012-2016 카드키), keyshop-online.com(플루언스 VA2 ID46), hankyung.com(2016년형 SM3 네오), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Abrites RR018은 메간3 2015+·SM3를 신형 목록에 포함 — 후기형 UCH/칩 변경 여부 미확인</t>
+          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
         </is>
       </c>
     </row>
@@ -1706,14 +1695,14 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1723,7 +1712,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1746,12 +1735,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>clien.net(SM3 스마트카드), abkeys.com(285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
+          <t>clien.net(SM3 스마트카드), abkeys.com(285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>Abrites RR018은 메간3 2015+·SM3를 신형 목록에 포함 — 후기형 UCH/칩 변경 여부 미확인</t>
+          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
         </is>
       </c>
     </row>
@@ -1766,14 +1755,14 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1783,7 +1772,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1806,12 +1795,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>renaultkoream.com e-guide(SM3 인텔리전트 스마트카드), mk3.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
+          <t>renaultkoream.com e-guide(SM3 인텔리전트 스마트카드), mk3.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Abrites RR018은 메간3 2015+·SM3를 신형 목록에 포함 — 후기형 UCH/칩 변경 여부 미확인</t>
+          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
         </is>
       </c>
     </row>
@@ -1826,14 +1815,14 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1843,7 +1832,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1866,12 +1855,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(SM3 2019 내연기관 생산 종료), remkeys.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
+          <t>wikipedia(SM3 2019 내연기관 생산 종료), remkeys.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Abrites RR018은 메간3 2015+·SM3를 신형 목록에 포함 — 후기형 UCH/칩 변경 여부 미확인</t>
+          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함 / 2019 내연기관 생산 종료</t>
         </is>
       </c>
     </row>
@@ -1886,14 +1875,14 @@
           <t>2020(단종)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1903,7 +1892,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1926,12 +1915,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(SM3 2003-2020), remkeys.com(285975779R PCF7952 433MHz), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
+          <t>wikipedia(SM3 2003-2020), remkeys.com(285975779R PCF7952 433MHz), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Abrites RR018은 메간3 2015+·SM3를 신형 목록에 포함 — 후기형 UCH/칩 변경 여부 미확인</t>
+          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1976,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>SM5 1세대 칩을 직접 밝힌 자료 없음 — 닛산 동일 플랫폼 기준 추정(실물 키 확인 필요) / SM5용 별도 리모컨(447MHz TFWB1J635, 칩 없음) 존재 — 적용 세대 미확인</t>
+          <t>SM5 1세대 칩을 직접 밝힌 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 동일 플랫폼 기준 추정(실물 키 확인 필요) / SM5용 별도 리모컨(447MHz TFWB1J635, 칩 없음) 존재 — 적용 세대 미확인</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2032,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>SM5 1세대 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2088,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>SM5 1세대 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2144,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>SM5 1세대 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2200,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>SM5 1세대 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2316,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 1세대와 연식 겹침</t>
+          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 1세대와 연식 겹침 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2376,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
+          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2436,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 0156·T002 상호 호환 안 됨</t>
+          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 0156·T002 상호 호환 안 됨 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2496,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
+          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2556,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
+          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2616,7 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
+          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2642,14 +2631,14 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2657,9 +2646,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -2675,19 +2664,19 @@
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>danawa(뉴 SM5 L43 2010.1.18 출시), smautomall(뉴SM5 L43 스마트카드 리모컨+비상키, VIN별 상이), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>플랫폼 동일 차종 르노 래티튜드(X43) 기준 칩·카드 / 트림에 따라 스마트카드·리모컨키 상이(VIN 확인)</t>
+          <t>danawa(뉴 SM5 L43 2010.1.18 출시), smautomall(뉴SM5 L43 스마트카드 리모컨+비상키, VIN별 상이), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -2702,14 +2691,14 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2717,9 +2706,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -2735,17 +2724,21 @@
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(래티튜드 2011-2015 4버튼 키카드 433MHz ID46 Hitag2), carusedpart.co.kr(신형 SM5 순정 스마트키), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>reidsremotes.com.au(래티튜드 2011-2015 4버튼 키카드 433MHz ID46 Hitag2), carusedpart.co.kr(신형 SM5 순정 스마트키), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2758,14 +2751,14 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2773,9 +2766,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -2791,17 +2784,21 @@
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), danawa(뉴 SM5 PH1 ~2012.11), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), danawa(뉴 SM5 PH1 ~2012.11), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2814,14 +2811,14 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2829,9 +2826,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -2847,17 +2844,21 @@
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>amazon.fr(PCF7952 VA2 4버튼 카드), eurocarkeyshop(4버튼 카드 케이스), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>amazon.fr(PCF7952 VA2 4버튼 카드), eurocarkeyshop(4버튼 카드 케이스), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2870,14 +2871,14 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2885,9 +2886,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -2903,17 +2904,21 @@
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2), carinterior.alibaba(2007-2014 매직카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2), carinterior.alibaba(2007-2014 매직카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2926,14 +2931,14 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2941,9 +2946,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -2959,19 +2964,19 @@
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>danawa(SM5 노바 2015.1.5 출시), reidsremotes.com.au(래티튜드 ~2015 ID46), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>카드 칩은 래티튜드 2011-2015 자료 기준</t>
+          <t>danawa(SM5 노바 2015.1.5 출시), reidsremotes.com.au(래티튜드 ~2015 ID46), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -2986,14 +2991,14 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -3003,7 +3008,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -3026,12 +3031,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>namu.wiki(2016 PE+ → 클래식 트림), danawa(SM5 노바 제원), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
+          <t>namu.wiki(2016 PE+ → 클래식 트림), danawa(SM5 노바 제원), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>래티튜드 자료가 2015까지라 2016~ 칩은 직접 확인 안 됨</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -3046,14 +3051,14 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -3063,7 +3068,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -3086,12 +3091,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>namu.wiki(SM5 클래식 단일 트림), youtube(SM5 스마트카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
+          <t>namu.wiki(SM5 클래식 단일 트림), youtube(SM5 스마트카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>래티튜드 자료가 2015까지라 2016~ 칩은 직접 확인 안 됨</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -3106,14 +3111,14 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -3123,7 +3128,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -3146,12 +3151,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>carwiki.co.kr(SM5 노바 2019년형), namu.wiki(SM5 3세대), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
+          <t>carwiki.co.kr(SM5 노바 2019년형), namu.wiki(SM5 3세대), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>래티튜드 자료가 2015까지라 2016~ 칩은 직접 확인 안 됨</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -3166,14 +3171,14 @@
           <t>2019(단종)</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3183,7 +3188,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -3206,12 +3211,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>namu.wiki(SM5 2019.12.31 판매 종료, 2020.1.1 생산 종료, SM5 아듀), carwiki.co.kr(SM5 2019년형), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM)</t>
+          <t>namu.wiki(SM5 2019.12.31 판매 종료, 2020.1.1 생산 종료, SM5 아듀), carwiki.co.kr(SM5 2019년형), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>원본 목록 2020은 생산 종료일(2020.1.1) — 2020년식 없음 / 래티튜드 자료가 2015까지라 2016~ 칩은 직접 확인 안 됨</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이) / 2019.12 판매 종료</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3231,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3286,12 +3291,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3342,12 +3347,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3398,12 +3403,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3454,12 +3459,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3514,12 +3519,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3570,12 +3575,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3626,12 +3631,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3641,7 +3646,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
@@ -3659,21 +3664,17 @@
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2017-2023 ID4A 285977147R), wikipedia(르노코리아 SM6 2016-2025)</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="inlineStr">
-        <is>
-          <t>탈리스만 유럽 판매 종료(2022) 이후 연식 — 칩은 이전 연식 기준, 직접 확인 안 됨</t>
-        </is>
-      </c>
+          <t>keyshop-online.com(2017-2023 ID4A 285977147R), wikipedia(르노코리아 SM6 2016-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3686,12 +3687,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3701,7 +3702,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
@@ -3719,21 +3720,17 @@
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>carisyou.com(2024 뉴 SM6), keyshop-online.com(ID4A VA2 433MHz)</t>
-        </is>
-      </c>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>탈리스만 유럽 판매 종료(2022) 이후 연식 — 칩은 이전 연식 기준, 직접 확인 안 됨</t>
-        </is>
-      </c>
+          <t>carisyou.com(2024 뉴 SM6), keyshop-online.com(ID4A VA2 433MHz), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3746,12 +3743,12 @@
           <t>2025(단종)</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -3786,12 +3783,12 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>daum/newsis(SM6 2025.3.13 단산, 2025.12 판매 종료), gpkorea.com(SM6·QM6 동시 단종)</t>
+          <t>daum/newsis(SM6 2025.3.13 단산, 2025.12 판매 종료), gpkorea.com(SM6·QM6 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>탈리스만 유럽 판매 종료(2022) 이후 연식 — 칩은 이전 연식 기준, 직접 확인 안 됨</t>
+          <t>2025.3 단산·2025.12 판매 종료 / 순정 카드 자료가 2024년식까지 — 2025년식은 동일 카드로 추정</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3848,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 2004.12 출시</t>
+          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 2004.12 출시 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3908,7 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3968,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4028,7 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4088,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4148,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4208,7 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정</t>
+          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4226,14 +4223,14 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -4243,7 +4240,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>1세대: ID46 추정(닛산 계열) / 2세대: ID46(PCF7952, Hitag2)</t>
+          <t>1세대: ID46 추정(닛산 계열) / 2세대: ID46(PCF7952) 또는 삼성 AES(PCF7945M) 카드</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -4286,14 +4283,14 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4301,9 +4298,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -4319,19 +4316,19 @@
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>carwiki.co.kr(올 뉴 SM7 2012년형), pechanara.com(올뉴 SM7 L47 스마트카드 리모컨+보조키 11~14년)</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준</t>
+          <t>carwiki.co.kr(올 뉴 SM7 2012년형), pechanara.com(올뉴 SM7 L47 스마트카드 리모컨+보조키 11~14년), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -4346,14 +4343,14 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -4361,9 +4358,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -4379,19 +4376,19 @@
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>carisyou.com(2013 뉴 SM7 L47), reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2 카드)</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준</t>
+          <t>carisyou.com(2013 뉴 SM7 L47), reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2 카드), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -4406,14 +4403,14 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -4421,9 +4418,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -4439,19 +4436,19 @@
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>pechanara.com(L47 스마트카드 11~14), danawa(SM7 노바 2014.9.2 출시)</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준</t>
+          <t>pechanara.com(L47 스마트카드 11~14), danawa(SM7 노바 2014.9.2 출시), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -4466,14 +4463,14 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -4481,9 +4478,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -4499,19 +4496,19 @@
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>danawa(SM7 노바 L47 제원), mr-key.com(래티튜드 2009-2015 285975779R PCF7952A)</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준</t>
+          <t>danawa(SM7 노바 L47 제원), mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -4526,14 +4523,14 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -4543,7 +4540,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -4566,12 +4563,12 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>encar.com(SM7 노바), reidsremotes.com.au(래티튜드 ~2015 ID46)</t>
+          <t>encar.com(SM7 노바), reidsremotes.com.au(래티튜드 ~2015 ID46), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준 / 래티튜드 자료가 2015까지 — 2016~ 칩 직접 확인 안 됨(삼성용 AES 카드 존재)</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -4586,14 +4583,14 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -4603,7 +4600,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -4626,12 +4623,12 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>danawa(SM7 노바), auto-keys.eu(르노삼성 4버튼 433MHz PCF7952A VA2 BCM 키)</t>
+          <t>danawa(SM7 노바), auto-keys.eu(르노삼성 4버튼 433MHz PCF7952A VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준 / 래티튜드 자료가 2015까지 — 2016~ 칩 직접 확인 안 됨(삼성용 AES 카드 존재)</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -4646,14 +4643,14 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -4663,7 +4660,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -4686,12 +4683,12 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>carisyou.com(2019 뉴 SM7 노바), auto-keys.eu(삼성 PCF7953 AES VA2 BCM 키)</t>
+          <t>carisyou.com(2019 뉴 SM7 노바), auto-keys.eu(삼성 PCF7953 AES VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준 / 래티튜드 자료가 2015까지 — 2016~ 칩 직접 확인 안 됨(삼성용 AES 카드 존재)</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
         </is>
       </c>
     </row>
@@ -4706,14 +4703,14 @@
           <t>2019(단종)</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -4723,7 +4720,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -4746,12 +4743,12 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>ko.wikipedia(SM7 노바 2014.9-2020.2 생산), carisyou.com(2019 SM7 노바)</t>
+          <t>ko.wikipedia(SM7 노바 2014.9-2020.2 생산), carisyou.com(2019 SM7 노바), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2세대(L47) — 칩은 래티튜드(X43) 기준 / 래티튜드 자료가 2015까지 — 2016~ 칩 직접 확인 안 됨(삼성용 AES 카드 존재) / 2020.2 생산 종료</t>
+          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이) / 2020.2 생산 종료</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4763,12 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4826,12 +4823,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4886,12 +4883,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4942,12 +4939,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4998,12 +4995,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5054,12 +5051,12 @@
           <t>2019(단종)</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5114,12 +5111,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5174,12 +5171,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5230,12 +5227,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5286,12 +5283,12 @@
           <t>2023(단종)</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5359,7 +5356,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
@@ -5382,7 +5379,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(QM5 2007.11.19 생산·2007.12.10 판매 개시), autokeys.us(콜레오스 NSN14 스마트키 = 삼성 QM5, PCF7952A 433.92MHz), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>wikipedia(QM5 2007.11.19 생산·2007.12.10 판매 개시), autokeys.us(콜레오스 NSN14 스마트키 = 삼성 QM5, PCF7952A 433.92MHz), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -5419,7 +5416,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -5442,7 +5439,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>amazon.co.uk(콜레오스 2008-2011 4버튼 카드 PCF7952), namu.wiki(인텔리전트 스마트카드 기본 적용), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>amazon.co.uk(콜레오스 2008-2011 4버튼 카드 PCF7952), namu.wiki(인텔리전트 스마트카드 기본 적용), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
@@ -5475,7 +5472,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
@@ -5498,7 +5495,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>car-keys-online.com(콜레오스 H45 2007-2015 Hitag2 PCF7952/PCF7941, 285970036R), ebay.co.uk(285970036R), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>car-keys-online.com(콜레오스 H45 2007-2015 Hitag2 PCF7952/PCF7941, 285970036R), ebay.co.uk(285970036R), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -5535,7 +5532,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -5558,7 +5555,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>amazon.es(콜레오스 2008-2011 PCF7952), wikipedia(2011.6 뉴 QM5 페이스리프트), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>amazon.es(콜레오스 2008-2011 PCF7952), wikipedia(2011.6 뉴 QM5 페이스리프트), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
@@ -5574,14 +5571,14 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5591,7 +5588,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
@@ -5614,12 +5611,12 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(콜레오스 2008-2016 ID46 NSN14 비상키), smautomall(QM5/뉴QM5 스마트카드 인텔리전트 적용모델), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>reidsremotes.com.au(콜레오스 2008-2016 ID46 NSN14 비상키), smautomall(QM5/뉴QM5 스마트카드 인텔리전트 적용모델), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>auto-keys.eu에 QM5용 AES(PCF7953) VA2 스마트키도 있음 — 적용 연식 미확인(후기형 가능성)</t>
+          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
         </is>
       </c>
     </row>
@@ -5634,14 +5631,14 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -5651,7 +5648,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -5674,12 +5671,12 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>remotesnkeys.com(콜레오스 2008-2016 ID46 433MHz), wikipedia(2013.4 2014년형 2.0 가솔린), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>remotesnkeys.com(콜레오스 2008-2016 ID46 433MHz), wikipedia(2013.4 2014년형 2.0 가솔린), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>auto-keys.eu에 QM5용 AES(PCF7953) VA2 스마트키도 있음 — 적용 연식 미확인(후기형 가능성)</t>
+          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
         </is>
       </c>
     </row>
@@ -5694,14 +5691,14 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5711,7 +5708,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
@@ -5734,12 +5731,12 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>carisyou.com(2014 QM5 네오), wikipedia(2014.1.20 QM5 네오 출시), ebay(콜레오스 2009-2016 PCF7952), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>carisyou.com(2014 QM5 네오), wikipedia(2014.1.20 QM5 네오 출시), ebay(콜레오스 2009-2016 PCF7952), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>auto-keys.eu에 QM5용 AES(PCF7953) VA2 스마트키도 있음 — 적용 연식 미확인(후기형 가능성)</t>
+          <t>2014.1 QM5 네오 / QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
         </is>
       </c>
     </row>
@@ -5754,14 +5751,14 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -5771,7 +5768,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
@@ -5794,12 +5791,12 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>carisyou.com(2015 QM5 네오), reidsremotes.com.au(콜레오스 2008-2016 ID46), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>carisyou.com(2015 QM5 네오), reidsremotes.com.au(콜레오스 2008-2016 ID46), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>auto-keys.eu에 QM5용 AES(PCF7953) VA2 스마트키도 있음 — 적용 연식 미확인(후기형 가능성)</t>
+          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
         </is>
       </c>
     </row>
@@ -5814,14 +5811,14 @@
           <t>2016(단종)</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -5831,7 +5828,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2)</t>
+          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
@@ -5854,12 +5851,12 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>danawa(QM5 네오 2014.01-2016.09), remotesnkeys.com(콜레오스 2008-2016 ID46 PCF7952A), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R)</t>
+          <t>danawa(QM5 네오 2014.01-2016.09), remotesnkeys.com(콜레오스 2008-2016 ID46 PCF7952A), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>가솔린 2016.7 생산 종료 / auto-keys.eu에 QM5용 AES(PCF7953) VA2 스마트키도 있음 — 적용 연식 미확인(후기형 가능성)</t>
+          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요 / 가솔린 2016.7 생산 종료</t>
         </is>
       </c>
     </row>
@@ -5874,12 +5871,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5934,12 +5931,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5990,12 +5987,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6046,12 +6043,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6102,12 +6099,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6158,12 +6155,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6214,12 +6211,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6270,12 +6267,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6310,7 +6307,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>keyshop-online.com(~2023 ID4A), autokeystore.com(콜레오스2 NCF29A1M)</t>
+          <t>keyshop-online.com(~2023 ID4A), autokeystore.com(콜레오스2 NCF29A1M), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr"/>
@@ -6326,12 +6323,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6341,7 +6338,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
@@ -6359,19 +6356,19 @@
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="4" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>gpkorea.com(QM6 판매 지속, 2025 단종), keyshop-online.com(ID4A VA2)</t>
-        </is>
-      </c>
-      <c r="N100" s="4" t="inlineStr">
-        <is>
-          <t>원본 목록 종료 2024 — 실제 판매는 2025.12까지 / 자료 연식 범위(~2023) 밖 — 칩 직접 확인 안 됨</t>
+          <t>gpkorea.com(QM6 판매 지속, 2025 단종), keyshop-online.com(ID4A VA2), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>원본 목록 종료 2024 — 실제 판매는 2025.12까지</t>
         </is>
       </c>
     </row>
@@ -6386,12 +6383,12 @@
           <t>2025(단종)</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6426,12 +6423,12 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>dailycar.co.kr/gpkorea.com(SM6·QM6 2025.12 동시 단종)</t>
+          <t>dailycar.co.kr/gpkorea.com(SM6·QM6 2025.12 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>자료 연식 범위(~2023) 밖 — 칩 직접 확인 안 됨</t>
+          <t>2025.12 단종 / 순정 카드 자료가 2024년식까지 — 2025년식은 동일 카드로 추정</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6443,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6463,19 +6460,19 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>ID4A(Hitag AES) 또는 ID47(Hitag3) 추정(지리 싱웨L/몬자로 기준)</t>
+          <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>HU100 추정(지리 기준)</t>
+          <t>HU100 (지리 스마트키 기준)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>지리 계열 4버튼 스마트키(품번 미확인)</t>
+          <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
@@ -6486,12 +6483,12 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(그랑 콜레오스 2024 국내 생산, 지리 싱웨L 기반 CMA 플랫폼), keyshop-online.com(지리 OEM 스마트키 ID4A HU100 433MHz)</t>
+          <t>wikipedia(그랑 콜레오스 2024 국내 생산, 지리 싱웨L 기반 CMA 플랫폼), keyshop-online.com(지리 OEM 스마트키 ID4A HU100 433MHz), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>그랑 콜레오스 키 칩을 직접 밝힌 자료 없음 — 지리 싱웨L(몬자로) 스마트키 자료(ID4A / Hitag3 혼재) 기준 추정, 실물 확인 필요 / 2024 하반기 출시</t>
+          <t>그랑 콜레오스 전용 자료 없음 — 원형 차종 지리 싱웨L(몬자로) 순정 키가 Hitag AES(4A)·DST AES(8A) 두 종류로 판매됨, 실물 확인 필요 / 2024 하반기 출시</t>
         </is>
       </c>
     </row>
@@ -6506,12 +6503,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6523,19 +6520,19 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>ID4A(Hitag AES) 또는 ID47(Hitag3) 추정(지리 싱웨L/몬자로 기준)</t>
+          <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>HU100 추정(지리 기준)</t>
+          <t>HU100 (지리 스마트키 기준)</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>지리 계열 4버튼 스마트키(품번 미확인)</t>
+          <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
@@ -6546,12 +6543,12 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>carisyou.com(2025 그랑 콜레오스 하이브리드), tlkeys.com(지리 순정 스마트키), keyshop-online.com(지리 ID4A)</t>
+          <t>carisyou.com(2025 그랑 콜레오스 하이브리드), tlkeys.com(지리 순정 스마트키), keyshop-online.com(지리 ID4A), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>그랑 콜레오스 키 칩을 직접 밝힌 자료 없음 — 지리 싱웨L(몬자로) 스마트키 자료(ID4A / Hitag3 혼재) 기준 추정, 실물 확인 필요</t>
+          <t>그랑 콜레오스 전용 자료 없음 — 원형 차종 지리 싱웨L(몬자로) 순정 키가 Hitag AES(4A)·DST AES(8A) 두 종류로 판매됨, 실물 확인 필요</t>
         </is>
       </c>
     </row>
@@ -6566,12 +6563,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6583,19 +6580,19 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>ID4A(Hitag AES) 또는 ID47(Hitag3) 추정(지리 싱웨L/몬자로 기준)</t>
+          <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>HU100 추정(지리 기준)</t>
+          <t>HU100 (지리 스마트키 기준)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>지리 계열 4버튼 스마트키(품번 미확인)</t>
+          <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
@@ -6606,12 +6603,12 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>renault.co.kr(그랑 콜레오스 판매 중), wikipedia(싱웨L/몬자로)</t>
+          <t>renault.co.kr(그랑 콜레오스 판매 중), wikipedia(싱웨L/몬자로), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>그랑 콜레오스 키 칩을 직접 밝힌 자료 없음 — 지리 싱웨L(몬자로) 스마트키 자료(ID4A / Hitag3 혼재) 기준 추정, 실물 확인 필요</t>
+          <t>그랑 콜레오스 전용 자료 없음 — 원형 차종 지리 싱웨L(몬자로) 순정 키가 Hitag AES(4A)·DST AES(8A) 두 종류로 판매됨, 실물 확인 필요</t>
         </is>
       </c>
     </row>
@@ -6626,12 +6623,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6686,12 +6683,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6742,12 +6739,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6798,12 +6795,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6854,12 +6851,12 @@
           <t>2024(단종)</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6914,12 +6911,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6929,7 +6926,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
@@ -6942,24 +6939,24 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
+          <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>ko.wikipedia(2024.4.3 르노 아르카나 차명 통일), renault.co.kr(아르카나 버튼시동 스마트카드 기본)</t>
-        </is>
-      </c>
-      <c r="N110" s="2" t="inlineStr">
-        <is>
-          <t>XM3와 동일 차량(차명만 변경)</t>
+          <t>ko.wikipedia(2024.4.3 르노 아르카나 차명 통일), renault.co.kr(아르카나 버튼시동 스마트카드 기본), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>XM3와 동일 차량(차명만 변경) / 2024 리네이밍 후 르노 신형 로고 적용 — 285979827R 카드는 신형 로고 차량에 안 맞는다는 판매처 안내 있음, 칩(Hitag AES)은 동일 계열로 보이나 카드 품번 확인 필요</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6971,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6989,7 +6986,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
@@ -7002,22 +6999,26 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
+          <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="L111" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>ko.wikipedia(1.3 터보 2025.4 생산 중지), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
-        </is>
-      </c>
-      <c r="N111" s="2" t="inlineStr"/>
+          <t>ko.wikipedia(1.3 터보 2025.4 생산 중지), keytectools.com(르노 Hitag AES ID4A 2018-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>2024 리네이밍 후 르노 신형 로고 적용 — 285979827R 카드는 신형 로고 차량에 안 맞는다는 판매처 안내 있음, 칩(Hitag AES)은 동일 계열로 보이나 카드 품번 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7030,12 +7031,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -7058,7 +7059,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
+          <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
@@ -7070,274 +7071,390 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>renault.co.kr(아르카나 판매 중), keytectools.com(르노 ID4A ~2025)</t>
+          <t>renault.co.kr(아르카나 판매 중), keytectools.com(르노 ID4A ~2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>2026년식 키 자료 없음 — 이전 연식 기준</t>
+          <t>2024 리네이밍 후 르노 신형 로고 적용 — 285979827R 카드는 신형 로고 차량에 안 맞는다는 판매처 안내 있음, 칩(Hitag AES)은 동일 계열로 보이나 카드 품번 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>트위지</t>
+          <t>조에 (Zoe)</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="C113" s="7" t="inlineStr"/>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr"/>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>VA2</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>285979827R (클리오5·캡처2·조에 공용)</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 있음(모듈 명칭 확인 불가)</t>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>etnews.com(트위지 2017.6 출시 1550만원), carisyou.com(2017 트위지), mycarly.com(2012 트위지 이모빌라이저 문제 사례)</t>
-        </is>
-      </c>
-      <c r="N113" s="8" t="inlineStr">
-        <is>
-          <t>원본 목록 2013은 유럽 출시 — 국내는 2017.6 출시 / 트위지 키 칩을 밝힌 자료 없음</t>
+          <t>ko.wikipedia/motoya.co.kr(조에 2020.8.18 국내 출시), car-keys-online.com(클리오·캡처·조에 순정 키카드 285979827R)</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>국내 판매분은 조에 2세대 페이스리프트(ZE50) — 1기형 조에(2012-2019)는 285975779R ID46 카드</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>트위지</t>
+          <t>조에 (Zoe)</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr"/>
-      <c r="D114" s="7" t="inlineStr"/>
-      <c r="E114" s="7" t="inlineStr"/>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>VA2</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>285979827R (클리오5·캡처2·조에 공용)</t>
+        </is>
+      </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 있음(모듈 명칭 확인 불가)</t>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>danawa(트위지 제원), mycarly.com(트위지 이모빌라이저·트랜스폰더)</t>
-        </is>
-      </c>
-      <c r="N114" s="8" t="inlineStr">
-        <is>
-          <t>트위지 키 칩 자료 없음</t>
-        </is>
-      </c>
+          <t>economist.co.kr(2021년형 재고 소진), keystation.co.uk(르노 2016-2021 NCF29A1M Hitag AES 4A)</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>트위지</t>
+          <t>조에 (Zoe)</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr"/>
-      <c r="D115" s="7" t="inlineStr"/>
-      <c r="E115" s="7" t="inlineStr"/>
-      <c r="F115" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2022(단종)</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>VA2</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>285979827R (클리오5·캡처2·조에 공용)</t>
+        </is>
+      </c>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 있음(모듈 명칭 확인 불가)</t>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>ko.wikipedia(2019.10 동신모텍 부산 생산 이전, 카고 삭제), danawa(트위지)</t>
-        </is>
-      </c>
-      <c r="N115" s="8" t="inlineStr">
-        <is>
-          <t>트위지 키 칩 자료 없음</t>
+          <t>economist.co.kr(2022 판매 중단·단종 수순), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>2022 수입 중단 — 원본 목록 2023까지는 재고 판매</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>트위지</t>
+          <t>클리오 (Clio)</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr"/>
-      <c r="D116" s="7" t="inlineStr"/>
-      <c r="E116" s="7" t="inlineStr"/>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>VA2</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
+        </is>
+      </c>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 있음(모듈 명칭 확인 불가)</t>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>evrunning.com(2020 트위지 라이프), encar.com(트위지 홈쇼핑 판매)</t>
-        </is>
-      </c>
-      <c r="N116" s="8" t="inlineStr">
-        <is>
-          <t>원본 목록 종료 2020 — 실제 국내 판매는 2022.6까지</t>
+          <t>hankookilbo.com(르노 클리오 2018.5 국내 출시), honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>국내 판매분은 4세대 페이스리프트(터키 생산, 1.5 dCi) — 원본 목록 2020-2023은 사실과 다름(5세대 국내 미출시)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>트위지</t>
+          <t>클리오 (Clio)</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr"/>
-      <c r="D117" s="7" t="inlineStr"/>
-      <c r="E117" s="7" t="inlineStr"/>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2019(단종)</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>VA2</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
+        </is>
+      </c>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 있음(모듈 명칭 확인 불가)</t>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>namu.wiki(트위지 국내 판매), koreausedcars.co.kr(트위지 시세)</t>
-        </is>
-      </c>
-      <c r="N117" s="8" t="inlineStr">
-        <is>
-          <t>트위지 키 칩 자료 없음</t>
+          <t>ko.wikipedia(클리오 4세대 국내 2018.5~2019말 판매, 5세대 미출시), keyfirst.eu(클리오4 2012-2019 285971998R VA2), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>2019년 말 판매 종료, 이후 조에가 대체</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>트위지</t>
+          <t>마스터 (LCV)</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr"/>
-      <c r="D118" s="7" t="inlineStr"/>
-      <c r="E118" s="7" t="inlineStr"/>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>VA6</t>
+        </is>
+      </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 있음(모듈 명칭 확인 불가)</t>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>namu.wiki(2022.6 국내 판매 종료), auto.daum.net(트위지 1세대)</t>
-        </is>
-      </c>
-      <c r="N118" s="8" t="inlineStr">
-        <is>
-          <t>트위지 키 칩 자료 없음</t>
+          <t>namu.wiki(마스터 밴 2018.10.15 공개·국내 출시), autoecupart.net(PCF7961M 4A 433MHz 3버튼 — 마스터3 등), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>원본 목록 2019~ — 밴은 2018.10 먼저 출시</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>조에 (Zoe)</t>
+          <t>마스터 (LCV)</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -7347,57 +7464,53 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>VA2</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>285979827R (클리오5·캡처2·조에 공용)</t>
-        </is>
-      </c>
+          <t>VA6</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+        </is>
+      </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>ko.wikipedia/motoya.co.kr(조에 2020.8.18 국내 출시), car-keys-online.com(클리오·캡처·조에 순정 키카드 285979827R)</t>
-        </is>
-      </c>
-      <c r="N119" s="2" t="inlineStr">
-        <is>
-          <t>국내 판매분은 조에 2세대 페이스리프트(ZE50) — 1기형 조에(2012-2019)는 285975779R ID46 카드</t>
-        </is>
-      </c>
+          <t>cvinfo.com/automorning.com(마스터 버스 2019.6.3 출시, 무선 리모컨키), onlyda.com(르노 순정 3버튼 PCF7961M Hitag AES 4A 434MHz), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>조에 (Zoe)</t>
+          <t>마스터 (LCV)</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -7407,53 +7520,57 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>VA2</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>285979827R (클리오5·캡처2·조에 공용)</t>
-        </is>
-      </c>
+          <t>VA6</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+        </is>
+      </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>economist.co.kr(2021년형 재고 소진), keystation.co.uk(르노 2016-2021 NCF29A1M Hitag AES 4A)</t>
-        </is>
-      </c>
-      <c r="N120" s="2" t="inlineStr"/>
+          <t>carisyou.com(부분변경 르노 마스터 밴·버스 출시), onlyda.com(르노·다치아 PCF7961M 4A VA2), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>마스터3 페이즈3(2019~) — 2020년식 VA6+PCF7947 사용 사례 있음</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>조에 (Zoe)</t>
+          <t>마스터 (LCV)</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -7461,59 +7578,59 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>VA2</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>285979827R (클리오5·캡처2·조에 공용)</t>
-        </is>
-      </c>
+          <t>VA6</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>economist.co.kr(2022 판매 중단·단종 수순), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
-        </is>
-      </c>
-      <c r="N121" s="2" t="inlineStr">
-        <is>
-          <t>2022 수입 중단 — 원본 목록 2023까지는 재고 판매</t>
+          <t>carnoon.co.kr(뉴 마스터 가격·제원), cndiykey.com(르노 3버튼 PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>클리오 (Clio)</t>
+          <t>마스터 (LCV)</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -7521,59 +7638,59 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>VA2</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
+          <t>VA6</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>hankookilbo.com(르노 클리오 2018.5 국내 출시), honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
-        </is>
-      </c>
-      <c r="N122" s="2" t="inlineStr">
-        <is>
-          <t>국내 판매분은 4세대 페이스리프트(터키 생산, 1.5 dCi) — 원본 목록 2020-2023은 사실과 다름(5세대 국내 미출시)</t>
+          <t>namu.wiki(마스터 버스 2022년형 끝으로 단종), autoecupart.net(PCF7961M 4A 마스터3), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>클리오 (Clio)</t>
+          <t>마스터 (LCV)</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -7581,37 +7698,37 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>VA2</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
+          <t>VA6</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>ko.wikipedia(클리오 4세대 국내 2018.5~2019말 판매, 5세대 미출시), keyfirst.eu(클리오4 2012-2019 285971998R VA2), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
-        </is>
-      </c>
-      <c r="N123" s="2" t="inlineStr">
-        <is>
-          <t>2019년 말 판매 종료, 이후 조에가 대체</t>
+          <t>namu.wiki(2023 수입 불안정 68대 판매), onlyda.com(PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -7623,17 +7740,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -7643,35 +7760,35 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>VA2 추정</t>
+          <t>VA6</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>BCM 추정</t>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>namu.wiki(마스터 밴 2018.10.15 공개·국내 출시), autoecupart.net(PCF7961M 4A 433MHz 3버튼 — 마스터3 등)</t>
+          <t>carnoon.co.kr(뉴 마스터 2024년형 2.3 밴), motormag.co.kr(2024.5.13 700대 특별 판매), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>원본 목록 2019~ — 밴은 2018.10 먼저 출시 / 마스터3 국내판 키 칩 직접 자료 없음, 르노 3버튼 PCF7961M(4A) 자료 기준 추정</t>
+          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
@@ -7683,17 +7800,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2025(단종)</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -7703,400 +7820,40 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
+          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>VA2 추정</t>
+          <t>VA6</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
+          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>BCM 추정</t>
+          <t>UCH</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>cvinfo.com/automorning.com(마스터 버스 2019.6.3 출시, 무선 리모컨키), onlyda.com(르노 순정 3버튼 PCF7961M Hitag AES 4A 434MHz)</t>
+          <t>namu.wiki(700대 한정 2025.9까지 판매), moter.kr(신형 마스터 4세대), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
-          <t>국내판 키 칩 직접 자료 없음 — 르노 PCF7961M(4A) 리모컨 자료 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>마스터 (LCV)</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>VA2 추정</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>BCM 추정</t>
-        </is>
-      </c>
-      <c r="M126" s="2" t="inlineStr">
-        <is>
-          <t>carisyou.com(부분변경 르노 마스터 밴·버스 출시), onlyda.com(르노·다치아 PCF7961M 4A VA2)</t>
-        </is>
-      </c>
-      <c r="N126" s="4" t="inlineStr">
-        <is>
-          <t>국내판 키 칩 직접 자료 없음 — 르노 PCF7961M(4A) 리모컨 자료 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>마스터 (LCV)</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>VA2 추정</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>BCM 추정</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>carnoon.co.kr(뉴 마스터 가격·제원), cndiykey.com(르노 3버튼 PCF7961M 4A)</t>
-        </is>
-      </c>
-      <c r="N127" s="4" t="inlineStr">
-        <is>
-          <t>국내판 키 칩 직접 자료 없음 — 르노 PCF7961M(4A) 리모컨 자료 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>마스터 (LCV)</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>VA2 추정</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>BCM 추정</t>
-        </is>
-      </c>
-      <c r="M128" s="2" t="inlineStr">
-        <is>
-          <t>namu.wiki(마스터 버스 2022년형 끝으로 단종), autoecupart.net(PCF7961M 4A 마스터3)</t>
-        </is>
-      </c>
-      <c r="N128" s="4" t="inlineStr">
-        <is>
-          <t>국내판 키 칩 직접 자료 없음 — 르노 PCF7961M(4A) 리모컨 자료 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>마스터 (LCV)</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>VA2 추정</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>BCM 추정</t>
-        </is>
-      </c>
-      <c r="M129" s="2" t="inlineStr">
-        <is>
-          <t>namu.wiki(2023 수입 불안정 68대 판매), onlyda.com(PCF7961M 4A)</t>
-        </is>
-      </c>
-      <c r="N129" s="4" t="inlineStr">
-        <is>
-          <t>국내판 키 칩 직접 자료 없음 — 르노 PCF7961M(4A) 리모컨 자료 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>마스터 (LCV)</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>VA2 추정</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>BCM 추정</t>
-        </is>
-      </c>
-      <c r="M130" s="2" t="inlineStr">
-        <is>
-          <t>carnoon.co.kr(뉴 마스터 2024년형 2.3 밴), motormag.co.kr(2024.5.13 700대 특별 판매)</t>
-        </is>
-      </c>
-      <c r="N130" s="4" t="inlineStr">
-        <is>
-          <t>국내판 키 칩 직접 자료 없음 — 르노 PCF7961M(4A) 리모컨 자료 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>마스터 (LCV)</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>2025(단종)</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7961M, Hitag AES) 추정</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>VA2 추정</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>리모컨 폴딩키(품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>BCM 추정</t>
-        </is>
-      </c>
-      <c r="M131" s="2" t="inlineStr">
-        <is>
-          <t>namu.wiki(700대 한정 2025.9까지 판매), moter.kr(신형 마스터 4세대)</t>
-        </is>
-      </c>
-      <c r="N131" s="4" t="inlineStr">
-        <is>
-          <t>3세대 한정 판매 2025.9 종료 — 4세대 국내 출시 미확인</t>
+          <t>3세대 한정 판매 2025.9 종료 — 4세대 국내 출시 미확인 / 자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N131"/>
+  <autoFilter ref="A1:N125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8107,149 +7864,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr"/>
+      <c r="A2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(SM5 1세대 1998년 출시분도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적고 비고에 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 트위지 2017~2022, 마스터 밴 2018~).</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적고 비고에 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 마스터 밴 2018~).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 르노 계열은 UCH(메간3/플루언스/래티튜드 세대) → BCM(클리오4·캡처 이후 Hitag AES 세대), 닛산 기반 구형 삼성 차종은 NATS(르노삼성 12자리 코드)로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>- 카드형 스마트키(르노 카드)는 '카드키(부품번호)' 칸에 적었습니다. 부품번호는 동일 플랫폼 르노 차종의 순정 번호(285975779R, 285977147R 등)이며 국내 순정 품번은 대부분 확인되지 않았습니다 — 르노코리아 부품은 VIN(KNMA…)별로 상이.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색에서 직접 나온 경우에만 적었고 나머지는 공란입니다(기아 파일 규칙). 키웨이는 카드 비상키 블레이드 기준(VA2/NSN14 등)입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49 → X/△/O. 실제 적용 전 장비로 재확인하세요.</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49·ID8A → X/△/O, 구형(ID46)·신형(AES) 칩이 병기된 행 → △/△/O(기아 파일 혼재 행 규칙). 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 원문 페이지를 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>- 빨간색: 확인 불가 — 그대로 신뢰해서 작업하지 마세요(트위지).</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
-        </is>
-      </c>
+      <c r="A14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>※ 조사하며 확인된 주요 사항</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>※ 조사하며 확인된 주요 사항</t>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>- [재조사] SM3 CF는 르노삼성이 생산한 닛산 알메라 클래식(러시아)·써니(중동)와 같은 차라 ID46 PCF7936·NSN14로 확인했습니다. SM3 1세대는 같은 차체라 동일 가능성이 높으나 직접 자료는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>- SM3 1세대·CF, SM5 1·2세대, SM7 1세대(닛산 기반)는 칩을 직접 밝힌 자료를 찾지 못했습니다. 닛산 동일 플랫폼(블루버드 실피·맥시마·티아나) 기준 추정입니다.</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>- SM5 1·2세대, SM7 1세대는 한국어·러시아·중남미·중동 자료를 다시 찾았지만 칩을 밝힌 자료가 없어 닛산 기준 추정(주황)으로 남겼습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>- [재조사] SM5 3세대·SM7 2세대는 래티튜드용 ID46 카드와 삼성 전용 AES(PCF7945M, 434MHz) 카드가 함께 판매되어 두 칩을 병기했습니다(주황). 285975779R 카드도 후기 순정품에 PCF7953M(4A) 사양이 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>- [재조사] 마스터3는 ID46 PCF7947, 블레이드 VA6 리모컨키입니다(이전 초안의 ID4A 추정은 오류). 그랑 콜레오스는 지리 몬자로 순정 키(Hitag AES 4A / DST AES 8A) 기준입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>- SM5 2세대·SM7 1세대 카드형 스마트키: 0156 타입(2005~2007)과 T002 타입(2008~, 뉴아트·임프레션)은 서로 호환되지 않습니다. FCC TFWB1J637(312.4MHz).</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>- SM3 2세대(플루언스), SM5 3세대·SM7 2세대(래티튜드): ID46 PCF7952 카드 285975779R, VA2, UCH. 2011년경부터 UCH 소프트웨어 변경으로 OBD 등록 제한 자료 있음.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>- QM5(콜레오스 H45): ID46 PCF7952 카드 285979045R(핸즈프리)/285970036R(비핸즈프리), 비상키 NSN14 또는 VA2 두 종류. QM5용 AES(PCF7953) 카드도 존재(적용 연식 미확인).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>- QM3·클리오4: 285971998R(핸즈프리 PCF7953M 4A) / 285974100R(비핸즈프리). SM6·QM6: 285977147R(PCF7953M/NCF29A1M 4A). 캡처2·조에·XM3·아르카나: 285979827R/285973979R(NCF29A1M 4A).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>- 그랑 콜레오스는 지리 싱웨L(몬자로) 기반으로, 키 칩 자료가 없어 지리 자료 기준 추정입니다.</t>
         </is>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'르노 트랜스폰더 DB'!$A$1:$N$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'르노 트랜스폰더 DB'!$A$1:$O$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -518,14 +518,15 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -561,40 +562,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>키종류</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>키블레이드(부품번호)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>키블레이드(키웨이)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>카드키(부품번호)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>스마트키(부품번호)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>폴딩키(부품번호)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>이모빌라이저 시스템</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -631,28 +637,33 @@
           <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>wikipedia(SM3 2002.9.2 판매 개시, 블루버드 실피 G10 기반), abkeys.com(닛산 4D-60 NSN14 1999+), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음 / 닛산 일본판 초기형은 4D60 사례 있어 실물 확인 필요</t>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -687,28 +698,33 @@
           <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>gskeyae.com(2003+ 닛산 NSN14 PCF7936 ID46), kecool.com(ICC: 르노삼성 SM3·SM5·SM7 12자리 코드), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음</t>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -743,28 +759,33 @@
           <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>abkeys.com(닛산 NSN14 PCF7936 ID46 2003+), nissanforums.com(블루버드 실피 2004 이그니션), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음</t>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -799,28 +820,33 @@
           <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>NSN14 (동일 차체 CF 확인값)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>gskeyae.com(2003+ NSN14 ID46), namu.wiki(2005.8 뉴 제너레이션 페이스리프트), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>1세대(2002-2005) 직접 자료는 없음 — 같은 차체 페이스리프트(CF)가 ID46·NSN14로 확인되어 동일 가능성 높음</t>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -855,30 +881,31 @@
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>danawa(SM3 뉴 제너레이션 N17 제원), namu.wiki(2005.8 뉴 제너레이션 출시), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인 / 1세대와 연식 겹침</t>
-        </is>
-      </c>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -911,30 +938,31 @@
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>clien.net(구형 SM3 리모컨키 CR2032), abkeys.com(닛산 NSN14 PCF7936 ID46 2003+), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
-        </is>
-      </c>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -967,30 +995,31 @@
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(2007 SM3 뉴제너레이션), gskeyae.com(2003+ NSN14 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
-        </is>
-      </c>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1023,30 +1052,31 @@
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>danawa(SM3 뉴 제너레이션), interpark(뉴SM3 리모컨 폴딩키 케이스), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
-        </is>
-      </c>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1079,30 +1109,31 @@
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>wikipedia(2009.11 2세대 판매 개시, 구형 병행), gskeyae.com(NSN14 ID46), ko.wikipedia(SM3 CE 2009.7.13 출시), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인 / 2세대(L38)와 병행 판매</t>
-        </is>
-      </c>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1135,30 +1166,31 @@
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>dailycar.co.kr(SM3 CE 2009.7 출시, 신·구형 병행 판매), abkeys.com(NSN14 PCF7936 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인 / 2세대(L38)와 병행 판매</t>
-        </is>
-      </c>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1191,30 +1223,31 @@
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>ko.wikipedia(SM3 CE 2011.3.31 단종), gskeyae.com(2003-2020 닛산 NSN14 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>르노삼성 생산 닛산 알메라 클래식(러시아)·써니(중동)와 동일 차량 — 해당 차종 자료로 칩·키웨이 확인</t>
-        </is>
-      </c>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1247,34 +1280,35 @@
           <t>ID46(PCF7952, Hitag2)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>wikipedia(SM3 L38 2009.11 판매 개시), renaultkoream.com e-guide(인텔리전트 스마트카드: 도어·트렁크·시동), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>국내 2009.11 판매 개시(원본 목록 2012년은 실제 출시보다 늦음) / 칩은 동일 플랫폼 플루언스·메간3 기준</t>
-        </is>
-      </c>
+      <c r="O13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1307,30 +1341,35 @@
           <t>ID46(PCF7952, Hitag2)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>amazon.co.uk(ID46-PCF7952A 카드키 메간3/플루언스), mr-key.com(PCF7952 ID46 카드키), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1363,34 +1402,35 @@
           <t>ID46(PCF7952, Hitag2)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>mk3.com(메간3·플루언스 카드키 285975779R PCF7952), keyfirst.eu(플루언스 2008-2016 카드키 VA2), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2011년경부터 UCH 소프트웨어 변경(OBD 키 등록 제한)</t>
-        </is>
-      </c>
+      <c r="O15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1423,30 +1463,35 @@
           <t>ID46(PCF7952, Hitag2)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>tlkeys.com(285975779R 2012-2016 PCF7952A), abkeys.com(플루언스 2008+ 285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1479,34 +1524,35 @@
           <t>ID46(PCF7952, Hitag2)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>gskeyae.com(285975779R), keyfirst.eu(플루언스 2008-2016 VA2 ID46 PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>SM3 Z.E.(전기차 2013~) 동일 카드키</t>
-        </is>
-      </c>
+      <c r="O17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1539,30 +1585,35 @@
           <t>ID46(PCF7952, Hitag2)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>abkeys.com(285975779R), kigoauto.com(PCF7952 285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1595,32 +1646,37 @@
           <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>ebay(플루언스 2012-2016 ID46 PCF7952A 카드키), hankyung.com(2016년형 SM3 네오 2015.4), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>같은 품번 카드가 PCF7952(Hitag2)·PCF7953M(AES) 두 사양으로 유통 — 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -1655,32 +1711,37 @@
           <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>ebay(플루언스 2012-2016 카드키), keyshop-online.com(플루언스 VA2 ID46), hankyung.com(2016년형 SM3 네오), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>같은 품번 카드가 PCF7952(Hitag2)·PCF7953M(AES) 두 사양으로 유통 — 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -1715,32 +1776,37 @@
           <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>clien.net(SM3 스마트카드), abkeys.com(285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>같은 품번 카드가 PCF7952(Hitag2)·PCF7953M(AES) 두 사양으로 유통 — 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -1775,32 +1841,37 @@
           <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>renaultkoream.com e-guide(SM3 인텔리전트 스마트카드), mk3.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>같은 품번 카드가 PCF7952(Hitag2)·PCF7953M(AES) 두 사양으로 유통 — 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -1835,32 +1906,37 @@
           <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>wikipedia(SM3 2019 내연기관 생산 종료), remkeys.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함 / 2019 내연기관 생산 종료</t>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>같은 품번 카드가 PCF7952(Hitag2)·PCF7953M(AES) 두 사양으로 유통 — 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -1895,32 +1971,37 @@
           <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>wikipedia(SM3 2003-2020), remkeys.com(285975779R PCF7952 433MHz), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>같은 품번 285975779R이 PCF7952(Hitag2)와 PCF7953M(AES 4A) 두 사양으로 유통 — 후기형 전환 시점 자료 없음, 카드로 칩 확인 필요 / Abrites RR018은 메간3 2015+를 신형 목록에 포함</t>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>같은 품번 카드가 PCF7952(Hitag2)·PCF7953M(AES) 두 사양으로 유통 — 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -1955,28 +2036,33 @@
           <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>amazon(1999-2006 닛산 맥시마 등 N102T 4D60), wikipedia(SM5 = 닛산 맥시마 A32 기반)</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>SM5 1세대 칩을 직접 밝힌 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 동일 플랫폼 기준 추정(실물 키 확인 필요) / SM5용 별도 리모컨(447MHz TFWB1J635, 칩 없음) 존재 — 적용 세대 미확인</t>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>칩 직접 자료 없음 — 닛산 맥시마(A33) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2011,28 +2097,33 @@
           <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>maxima.org(2001-2003 NATS), kecool.com(ICC IMMO 계산기: 르노삼성 SM3·SM5·SM7 12자리 코드 NATS)</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>칩 직접 자료 없음 — 닛산 맥시마(A33) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2067,28 +2158,33 @@
           <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>remotesandkeys.com(2002 맥시마 NI02T 4D60), carisyou.com(2002 SM5 제원)</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>칩 직접 자료 없음 — 닛산 맥시마(A33) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2123,28 +2219,33 @@
           <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>xecutive(맥시마 2000-2003 트랜스폰더키), namu.wiki(2003.9.1 페이스리프트 NPQ)</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>칩 직접 자료 없음 — 닛산 맥시마(A33) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2179,28 +2280,33 @@
           <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>royalkeysupply.com(1999-2004 맥시마 NI02T 4D60), gparts.co.kr(2004 SM520 부품)</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>SM5 1세대 칩 직접 자료 없음(재조사: 국내 커뮤니티·칠레 SQ5·러시아 자료 모두 없음) — 닛산 맥시마 기준 추정</t>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>칩 직접 자료 없음 — 닛산 맥시마(A33) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2235,28 +2341,33 @@
           <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>abkeys.com(닛산 4D-60 NSN14 1999+), namu.wiki(NPQ 2003.9-2005.3, 2세대 2005.1.25 출시)</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>2세대와 연식 겹침</t>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>칩 직접 자료 없음 — 닛산 맥시마(A33) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2291,32 +2402,37 @@
           <t>ID46 추정(닛산 티아나 J31 기준)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 0156 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(뉴 SM5 EX1 2005.1.25 출시, 국산 중형 최초 스마트 카드키), awesomemotors.kr(05~07년 SM7·뉴SM5 스마트키 0156 타입), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 1세대와 연식 겹침 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2351,32 +2467,37 @@
           <t>ID46 추정(닛산 티아나 J31 기준)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 0156 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(0156 타입: 뉴아트·임프레션 호환 안 됨), autoecupart.net(티아나 2005-2008 스마트키 ID46), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2411,32 +2532,37 @@
           <t>ID46 추정(닛산 티아나 J31 기준)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 0156 타입(2007.7 이전) / T002 타입(뉴 임프레션), FCC TFWB1J637(312.4MHz 3버튼)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(2007.7.2 뉴 임프레션 페이스리프트), awesomemotors.kr(0156 05~07년), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 0156·T002 상호 호환 안 됨 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2471,32 +2597,37 @@
           <t>ID46 추정(닛산 티아나 J31 기준)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 T002 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002: SM7 뉴아트·SM5 임프레션, 2008 이상), carusedpart.co.kr(뉴SM5 순정 스마트키 TFWB1J637), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2531,32 +2662,37 @@
           <t>ID46 추정(닛산 티아나 J31 기준)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 T002 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002 2008 이상), danawa(SM5 뉴 임프레션 EX1/DF LE플러스 이상 스마트키), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2591,32 +2727,37 @@
           <t>ID46 추정(닛산 티아나 J31 기준)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 T002 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>cnautokey.net(SM5·SM7 스마트키 312.4MHz TFWB1J637), namu.wiki(뉴 임프레션 2007.7-2010), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>카드형 스마트키는 트림별 옵션(하위 트림은 리모컨키) / 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -2651,32 +2792,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>danawa(뉴 SM5 L43 2010.1.18 출시), smautomall(뉴SM5 L43 스마트카드 리모컨+비상키, VIN별 상이), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2711,32 +2857,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(래티튜드 2011-2015 4버튼 키카드 433MHz ID46 Hitag2), carusedpart.co.kr(신형 SM5 순정 스마트키), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2922,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), danawa(뉴 SM5 PH1 ~2012.11), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2831,32 +2987,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>amazon.fr(PCF7952 VA2 4버튼 카드), eurocarkeyshop(4버튼 카드 케이스), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2891,32 +3052,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2), carinterior.alibaba(2007-2014 매직카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -2951,32 +3117,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>danawa(SM5 노바 2015.1.5 출시), reidsremotes.com.au(래티튜드 ~2015 ID46), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -3011,32 +3182,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(2016 PE+ → 클래식 트림), danawa(SM5 노바 제원), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -3071,32 +3247,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(SM5 클래식 단일 트림), youtube(SM5 스마트카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -3131,32 +3312,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>carwiki.co.kr(SM5 노바 2019년형), namu.wiki(SM5 3세대), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -3191,32 +3377,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(SM5 2019.12.31 판매 종료, 2020.1.1 생산 종료, SM5 아듀), carwiki.co.kr(SM5 2019년형), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이) / 2019.12 판매 종료</t>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -3251,34 +3442,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>keyecu.com(탈리스만 2016-2019 PCF7953 285977147R), v.daum.net(SM6 2016 출시 월 3000대)</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>플랫폼 동일 르노 탈리스만 기준 / 원본 목록 "현재" → 2025년 단종 확인</t>
-        </is>
-      </c>
+      <c r="O47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3311,30 +3503,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>mk3.com(메간4·탈리스만 2015-2019 PCF7953M Hitag AES 4A, KR5IK4CH-01), keyshop-online.com(2017-2023 285977147R ID4A VA2)</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3367,30 +3564,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>f-key.com(OEM 카드 433MHz 4A PCF7953 탈리스만 2016-2019), keycardservices.co.uk(탈리스만 2015-2018 PCF7953M)</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3423,30 +3625,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>onlyda.com(탈리스만 2016+ 285977147R Hitag AES PCF7953M ID4A), abrites.com(RR018 탈리스만 2019+ 키 등록)</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3479,34 +3686,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>wikipedia(탈리스만 2020.2 페이스리프트), carkeyswithease.com(285977147R), smautomall(뉴SM6 스마트카드 원격시동 타입)</t>
         </is>
       </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>2020.7 뉴 SM6 — 원격시동 타입 스마트카드 별도(VIN 확인)</t>
-        </is>
-      </c>
+      <c r="O51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3539,30 +3747,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>hickleys.com(탈리스만 2016-2022 285977147R PCF7953M ID4A), smautomall(SM6/뉴SM6 스마트카드 리모컨+비상키)</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3595,30 +3808,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>abkeys.com(메간4·탈리스만 2016+ Hitag AES 285977147R), auto-keys.eu(메간4·탈리스만 Hitag AES NCF29A1M VA2 BCM)</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3651,30 +3869,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>keyshop-online.com(2017-2023 ID4A 285977147R), wikipedia(르노코리아 SM6 2016-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3707,30 +3930,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(2024 뉴 SM6), keyshop-online.com(ID4A VA2 433MHz), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3763,32 +3991,37 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>daum/newsis(SM6 2025.3.13 단산, 2025.12 판매 종료), gpkorea.com(SM6·QM6 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
-        <is>
-          <t>2025.3 단산·2025.12 판매 종료 / 순정 카드 자료가 2024년식까지 — 2025년식은 동일 카드로 추정</t>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>순정 카드 자료가 2024년식까지 — 동일 카드로 추정</t>
         </is>
       </c>
     </row>
@@ -3823,32 +4056,37 @@
           <t>ID46 추정(닛산 티아나 J31 계열)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 0156 타입</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>wikipedia(SM7 2004.11.30 공개, 2004.12.1 판매 개시), namu.wiki(2004.12부터 SM5·SM7 스마트카드 옵션), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
-        <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 2004.12 출시 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3883,32 +4121,37 @@
           <t>ID46 추정(닛산 티아나 J31 계열)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 0156 타입</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(05~07년 SM7·뉴SM5 스마트키 0156), namu.wiki(SM7 1세대 노브형 스마트키), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N58" s="4" t="inlineStr">
-        <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -3943,32 +4186,37 @@
           <t>ID46 추정(닛산 티아나 J31 계열)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 0156 타입</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(0156: 뉴아트·임프레션 호환 안 됨), cafe.daum(부천 SM7 카드키 복사), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4003,32 +4251,37 @@
           <t>ID46 추정(닛산 티아나 J31 계열)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 0156 타입</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(SM7 넌아트 0156 타입), cnautokey.net(SM5·SM7 312.4MHz TFWB1J637), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N60" s="4" t="inlineStr">
-        <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4063,32 +4316,37 @@
           <t>ID46 추정(닛산 티아나 J31 계열)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 T002 타입(뉴아트)</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002: SM7 뉴아트·SM5 임프레션, 2008 이상), carisyou.com(SM7 뉴아트 카드형 스마트키, 노브 회전식), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
-        <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4123,32 +4381,37 @@
           <t>ID46 추정(닛산 티아나 J31 계열)</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 T002 타입(뉴아트)</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>wikicar.co.kr(SM7 뉴아트 2010년형 2009.10), awesomemotors.kr(T002), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
-        <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4183,32 +4446,37 @@
           <t>ID46 추정(닛산 티아나 J31 계열)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>NSN14 (닛산 기준 추정)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 T002 타입(뉴아트)</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002 2008 이상), cafe.daum(SM7 임프레션 카드키 복사), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
-        <is>
-          <t>1세대(EX2, 닛산 티아나 J31 기반) 칩 직접 자료 없음 — 닛산 기준 추정 / 재조사: 수출명 르노 사프란(중동·멕시코) 자료는 래티튜드 계열 카드(285975779R)와 섞여 구분 불가, 국내 0156·T002 카드의 칩 자료 없음</t>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4243,32 +4511,37 @@
           <t>1세대: ID46 추정(닛산 계열) / 2세대: ID46(PCF7952) 또는 삼성 AES(PCF7945M) 카드</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>막대키,카드키</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>NSN14 추정(1세대) / VA2(2세대)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>카드형 스마트키 T002 타입(뉴아트, 2011.7 이전 생산) / 2세대: 285975779R(래티튜드 공용)</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>NATS(1세대, 2011.7 이전 생산) / UCH(BCM)(2세대 L47, 2011.8 이후 생산)</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>wikipedia(2세대 2011.8 판매 개시), awesomemotors.kr(T002), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t>2011.8 2세대(L47, 래티튜드 기반) 출시 — 1세대 칩은 추정</t>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4303,32 +4576,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>carwiki.co.kr(올 뉴 SM7 2012년형), pechanara.com(올뉴 SM7 L47 스마트카드 리모컨+보조키 11~14년), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4363,32 +4641,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(2013 뉴 SM7 L47), reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2 카드), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N66" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4423,32 +4706,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>pechanara.com(L47 스마트카드 11~14), danawa(SM7 노바 2014.9.2 출시), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4483,32 +4771,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>danawa(SM7 노바 L47 제원), mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4836,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>encar.com(SM7 노바), reidsremotes.com.au(래티튜드 ~2015 ID46), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4603,32 +4901,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>danawa(SM7 노바), auto-keys.eu(르노삼성 4버튼 433MHz PCF7952A VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4663,32 +4966,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(2019 뉴 SM7 노바), auto-keys.eu(삼성 PCF7953 AES VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이)</t>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4723,32 +5031,37 @@
           <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="4" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr">
         <is>
           <t>UCH(BCM)</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>ko.wikipedia(SM7 노바 2014.9-2020.2 생산), carisyou.com(2019 SM7 노바), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
-        <is>
-          <t>래티튜드 기준 ID46 카드와 삼성 전용 AES 카드가 함께 판매됨 — 적용 연식 구분 자료 없음, 카드 뒷면 품번/장비로 칩 확인 필요 / 2011 전후 UCH 변경(OBD PIN 읽기 방식 상이) / 2020.2 생산 종료</t>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4783,34 +5096,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처1 키카드 2013-2020 285971998R), clien.net(QM3 스마트키 추가 구입 15만5천원), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>르노 캡처 1세대 수입(스페인 생산) — 원본 목록 2014~ / 2013.12 출시</t>
-        </is>
-      </c>
+      <c r="O73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4843,34 +5157,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), autokeys.us(285971998R 클리오4·캡처), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>플립키형(PCF7961M 4A, CWTWB1G767)도 캡처1에 존재 — 국내 QM3는 카드형</t>
-        </is>
-      </c>
+      <c r="O74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4903,30 +5218,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>tlkeys.com(285971998R 2012-2016 Hitag AES), imim.kr(QM3 스마트키 르노삼성), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4959,30 +5279,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>eurocarkeyshop.com(클리오·캡처 키리스 카드 285971998R), wikipedia(캡처 2017.5 페이스리프트), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5015,30 +5340,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처1 2013-2020 VA2 433.92MHz 4A PCF7953M), accessfobs.co.uk(클리오·캡처 핸즈프리 카드 PCF7953), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5071,34 +5401,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처1 ~2020), auto-keys.eu(클리오4/삼성 PCF7953 VA2 BCM 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>캡처 2세대(2020~)로 교체</t>
-        </is>
-      </c>
+      <c r="O78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5131,34 +5462,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>etoday.co.kr/daum(르노 캡처 2020.5.13 국내 출시, QM3 후속), keyfirst.eu(캡처2 2019-2022 호환 키카드)</t>
         </is>
       </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>르노 캡처 2세대(스페인 생산) 수입</t>
-        </is>
-      </c>
+      <c r="O79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5191,30 +5523,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>keystation.co.uk(캡처·클리오·아르카나 2016-2021 NCF29A1M Hitag AES 4A, CIT-1/VA2/VA6), car-keys-online.com(클리오5/캡처2/아르카나 285979827R)</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5247,30 +5584,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>keystation.co.uk(캡처 2019-2024 ID4A 285979827R), namu.wiki(캡처 2세대 국내 판매)</t>
         </is>
       </c>
-      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5303,30 +5645,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처2 2019-2023 카드), car-keys-online.com(285979827R 신형 H-24985)</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5359,34 +5706,35 @@
           <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>wikipedia(QM5 2007.11.19 생산·2007.12.10 판매 개시), autokeys.us(콜레오스 NSN14 스마트키 = 삼성 QM5, PCF7952A 433.92MHz), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>원본 목록 2007은 판매 개시(2007.12) — 2008년식부터 기록 / 르노 콜레오스(H45, 닛산 X-트레일 플랫폼)와 동일 키</t>
-        </is>
-      </c>
+      <c r="O83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5419,30 +5767,35 @@
           <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>amazon.co.uk(콜레오스 2008-2011 4버튼 카드 PCF7952), namu.wiki(인텔리전트 스마트카드 기본 적용), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5475,34 +5828,35 @@
           <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>car-keys-online.com(콜레오스 H45 2007-2015 Hitag2 PCF7952/PCF7941, 285970036R), ebay.co.uk(285970036R), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>인텔리전트(핸즈프리) 미적용 트림은 비핸즈프리 카드(PCF7941)</t>
-        </is>
-      </c>
+      <c r="O85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5535,30 +5889,35 @@
           <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>amazon.es(콜레오스 2008-2011 PCF7952), wikipedia(2011.6 뉴 QM5 페이스리프트), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5591,32 +5950,37 @@
           <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="4" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="4" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(콜레오스 2008-2016 ID46 NSN14 비상키), smautomall(QM5/뉴QM5 스마트카드 인텔리전트 적용모델), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
-      <c r="N87" s="4" t="inlineStr">
-        <is>
-          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>Hitag2·AES 카드 두 종류 판매 — AES 전환 연식 자료 없음</t>
         </is>
       </c>
     </row>
@@ -5651,32 +6015,37 @@
           <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>remotesnkeys.com(콜레오스 2008-2016 ID46 433MHz), wikipedia(2013.4 2014년형 2.0 가솔린), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
-      <c r="N88" s="4" t="inlineStr">
-        <is>
-          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>Hitag2·AES 카드 두 종류 판매 — AES 전환 연식 자료 없음</t>
         </is>
       </c>
     </row>
@@ -5711,32 +6080,37 @@
           <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="4" t="inlineStr">
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="4" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(2014 QM5 네오), wikipedia(2014.1.20 QM5 네오 출시), ebay(콜레오스 2009-2016 PCF7952), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
-      <c r="N89" s="4" t="inlineStr">
-        <is>
-          <t>2014.1 QM5 네오 / QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>Hitag2·AES 카드 두 종류 판매 — AES 전환 연식 자료 없음</t>
         </is>
       </c>
     </row>
@@ -5771,32 +6145,37 @@
           <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="4" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(2015 QM5 네오), reidsremotes.com.au(콜레오스 2008-2016 ID46), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
-      <c r="N90" s="4" t="inlineStr">
-        <is>
-          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요</t>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>Hitag2·AES 카드 두 종류 판매 — AES 전환 연식 자료 없음</t>
         </is>
       </c>
     </row>
@@ -5831,32 +6210,37 @@
           <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>NSN14 또는 VA2 (차량별 상이)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="4" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr">
         <is>
           <t>BCM(닛산 NATS 계열)</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>danawa(QM5 네오 2014.01-2016.09), remotesnkeys.com(콜레오스 2008-2016 ID46 PCF7952A), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
-      <c r="N91" s="4" t="inlineStr">
-        <is>
-          <t>QM5용 순정 카드가 Hitag2(PCF7952A/PCF7941A)와 AES(PCF7953) 두 종류로 판매됨 — AES 전환 연식 확인 자료 없음(콜레오스 2014-2016 AES 자료 1건), 카드로 확인 필요 / 가솔린 2016.7 생산 종료</t>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>Hitag2·AES 카드 두 종류 판매 — AES 전환 연식 자료 없음</t>
         </is>
       </c>
     </row>
@@ -5891,34 +6275,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>wikipedia(QM6 2016.9 출시 = 콜레오스 2세대), keystation.co.uk(콜레오스 2016-2021 NCF29A1M Hitag AES 4A)</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>르노 콜레오스 2세대(HZG) 기준</t>
-        </is>
-      </c>
+      <c r="O92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5951,30 +6336,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>norman-keys.com(2017 콜레오스 OEM 카드 433MHz 4A), carkeyshop.co.uk(콜레오스·메간4·탈리스만 카드 PCF7953M)</t>
         </is>
       </c>
-      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6007,30 +6397,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>keyshop-online.com(2017-2023 메간4·탈리스만·콜레오스 ID4A VA2 285977147R), pechanara.com(QM6 스마트카드)</t>
         </is>
       </c>
-      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6063,30 +6458,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr">
+      <c r="N95" s="2" t="inlineStr">
         <is>
           <t>autokeystore.com(메간4·콜레오스2 핸즈프리 카드 KR5IK4CH-01 NCF29A1M), dalkomhae.com(QM6 스마트키)</t>
         </is>
       </c>
-      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6119,30 +6519,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="N96" s="2" t="inlineStr">
         <is>
           <t>keystation.co.uk(콜레오스 2016-2021 NCF29A1M), carkeymaster.kr(QM6 스마트키 분실)</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6175,30 +6580,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr">
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>keystation.co.uk(콜레오스 ~2021 4A), keyshop-online.com(2017-2023 ID4A)</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6231,30 +6641,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>keyshop-online.com(2017-2023 콜레오스 ID4A 285977147R), teamblind.com(QM6 스마트키 분실)</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6287,30 +6702,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>keyshop-online.com(~2023 ID4A), autokeystore.com(콜레오스2 NCF29A1M), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6343,34 +6763,35 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>gpkorea.com(QM6 판매 지속, 2025 단종), keyshop-online.com(ID4A VA2), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>원본 목록 종료 2024 — 실제 판매는 2025.12까지</t>
-        </is>
-      </c>
+      <c r="O100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6403,32 +6824,37 @@
           <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="4" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="N101" s="2" t="inlineStr">
         <is>
           <t>dailycar.co.kr/gpkorea.com(SM6·QM6 2025.12 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr">
-        <is>
-          <t>2025.12 단종 / 순정 카드 자료가 2024년식까지 — 2025년식은 동일 카드로 추정</t>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>순정 카드 자료가 2024년식까지 — 동일 카드로 추정</t>
         </is>
       </c>
     </row>
@@ -6463,32 +6889,37 @@
           <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>HU100 (지리 스마트키 기준)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="4" t="inlineStr">
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr">
         <is>
           <t>확인 불가(지리 CMA 계열)</t>
         </is>
       </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t>wikipedia(그랑 콜레오스 2024 국내 생산, 지리 싱웨L 기반 CMA 플랫폼), keyshop-online.com(지리 OEM 스마트키 ID4A HU100 433MHz), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
-      <c r="N102" s="4" t="inlineStr">
-        <is>
-          <t>그랑 콜레오스 전용 자료 없음 — 원형 차종 지리 싱웨L(몬자로) 순정 키가 Hitag AES(4A)·DST AES(8A) 두 종류로 판매됨, 실물 확인 필요 / 2024 하반기 출시</t>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>전용 자료 없음 — 원형 지리 몬자로 키가 ID4A·ID8A 두 종류</t>
         </is>
       </c>
     </row>
@@ -6523,32 +6954,37 @@
           <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>HU100 (지리 스마트키 기준)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="4" t="inlineStr">
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="4" t="inlineStr">
         <is>
           <t>확인 불가(지리 CMA 계열)</t>
         </is>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(2025 그랑 콜레오스 하이브리드), tlkeys.com(지리 순정 스마트키), keyshop-online.com(지리 ID4A), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
-      <c r="N103" s="4" t="inlineStr">
-        <is>
-          <t>그랑 콜레오스 전용 자료 없음 — 원형 차종 지리 싱웨L(몬자로) 순정 키가 Hitag AES(4A)·DST AES(8A) 두 종류로 판매됨, 실물 확인 필요</t>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>전용 자료 없음 — 원형 지리 몬자로 키가 ID4A·ID8A 두 종류</t>
         </is>
       </c>
     </row>
@@ -6583,32 +7019,37 @@
           <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>HU100 (지리 스마트키 기준)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr">
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr">
         <is>
           <t>확인 불가(지리 CMA 계열)</t>
         </is>
       </c>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t>renault.co.kr(그랑 콜레오스 판매 중), wikipedia(싱웨L/몬자로), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
-      <c r="N104" s="4" t="inlineStr">
-        <is>
-          <t>그랑 콜레오스 전용 자료 없음 — 원형 차종 지리 싱웨L(몬자로) 순정 키가 Hitag AES(4A)·DST AES(8A) 두 종류로 판매됨, 실물 확인 필요</t>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>전용 자료 없음 — 원형 지리 몬자로 키가 ID4A·ID8A 두 종류</t>
         </is>
       </c>
     </row>
@@ -6643,34 +7084,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr">
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr">
+      <c r="N105" s="2" t="inlineStr">
         <is>
           <t>wikipedia(XM3 2020.3 출시, 부산 생산 LJL), smautomall(XM3 스마트카드 리모컨+비상키, VIN별 상이), teamblind.com(2020.10식 XM3 스마트키)</t>
         </is>
       </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>르노 아르카나(LJL) 국내 생산판 — 칩은 아르카나 기준</t>
-        </is>
-      </c>
+      <c r="O105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6703,30 +7145,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>car-keys-online.com(아르카나 2021-2023 285979827R), keystation.co.uk(아르카나·캡처·클리오 NCF29A1M 4A)</t>
         </is>
       </c>
-      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6759,30 +7206,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>keystation.co.uk(아르카나 ID4A CIT-1/VA2/VA6), danawa(XM3 LJL)</t>
         </is>
       </c>
-      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6815,30 +7267,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>car-keys-online.com(OEM 키카드 클리오5/아르카나/캡처2 신형 H-24985 285979827R), carinfoyou.com(2024 XM3)</t>
         </is>
       </c>
-      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6871,34 +7328,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>ko.wikipedia(2024.4.3 국내명 르노 아르카나로 통일), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>2024.4 아르카나로 차명 변경(차량 동일)</t>
-        </is>
-      </c>
+      <c r="O109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6931,32 +7389,37 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
         <is>
           <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>ko.wikipedia(2024.4.3 르노 아르카나 차명 통일), renault.co.kr(아르카나 버튼시동 스마트카드 기본), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
-      <c r="N110" s="4" t="inlineStr">
-        <is>
-          <t>XM3와 동일 차량(차명만 변경) / 2024 리네이밍 후 르노 신형 로고 적용 — 285979827R 카드는 신형 로고 차량에 안 맞는다는 판매처 안내 있음, 칩(Hitag AES)은 동일 계열로 보이나 카드 품번 확인 필요</t>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
         </is>
       </c>
     </row>
@@ -6991,32 +7454,37 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>ko.wikipedia(1.3 터보 2025.4 생산 중지), keytectools.com(르노 Hitag AES ID4A 2018-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
-      <c r="N111" s="4" t="inlineStr">
-        <is>
-          <t>2024 리네이밍 후 르노 신형 로고 적용 — 285979827R 카드는 신형 로고 차량에 안 맞는다는 판매처 안내 있음, 칩(Hitag AES)은 동일 계열로 보이나 카드 품번 확인 필요</t>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
         </is>
       </c>
     </row>
@@ -7051,32 +7519,37 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>VA2 (VA6 병기 자료 있음)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="4" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>renault.co.kr(아르카나 판매 중), keytectools.com(르노 ID4A ~2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
-      <c r="N112" s="4" t="inlineStr">
-        <is>
-          <t>2024 리네이밍 후 르노 신형 로고 적용 — 285979827R 카드는 신형 로고 차량에 안 맞는다는 판매처 안내 있음, 칩(Hitag AES)은 동일 계열로 보이나 카드 품번 확인 필요</t>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
         </is>
       </c>
     </row>
@@ -7111,34 +7584,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>285979827R (클리오5·캡처2·조에 공용)</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>ko.wikipedia/motoya.co.kr(조에 2020.8.18 국내 출시), car-keys-online.com(클리오·캡처·조에 순정 키카드 285979827R)</t>
         </is>
       </c>
-      <c r="N113" s="2" t="inlineStr">
-        <is>
-          <t>국내 판매분은 조에 2세대 페이스리프트(ZE50) — 1기형 조에(2012-2019)는 285975779R ID46 카드</t>
-        </is>
-      </c>
+      <c r="O113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7171,30 +7645,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>285979827R (클리오5·캡처2·조에 공용)</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>economist.co.kr(2021년형 재고 소진), keystation.co.uk(르노 2016-2021 NCF29A1M Hitag AES 4A)</t>
         </is>
       </c>
-      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7227,34 +7706,35 @@
           <t>ID4A(NCF29A1M, Hitag AES)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t>285979827R (클리오5·캡처2·조에 공용)</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M115" s="2" t="inlineStr">
+      <c r="N115" s="2" t="inlineStr">
         <is>
           <t>economist.co.kr(2022 판매 중단·단종 수순), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
         </is>
       </c>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>2022 수입 중단 — 원본 목록 2023까지는 재고 판매</t>
-        </is>
-      </c>
+      <c r="O115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7287,34 +7767,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>hankookilbo.com(르노 클리오 2018.5 국내 출시), honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N116" s="2" t="inlineStr">
-        <is>
-          <t>국내 판매분은 4세대 페이스리프트(터키 생산, 1.5 dCi) — 원본 목록 2020-2023은 사실과 다름(5세대 국내 미출시)</t>
-        </is>
-      </c>
+      <c r="O116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7347,34 +7828,35 @@
           <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>카드키</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr">
         <is>
           <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr">
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr">
+      <c r="N117" s="2" t="inlineStr">
         <is>
           <t>ko.wikipedia(클리오 4세대 국내 2018.5~2019말 판매, 5세대 미출시), keyfirst.eu(클리오4 2012-2019 285971998R VA2), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="N117" s="2" t="inlineStr">
-        <is>
-          <t>2019년 말 판매 종료, 이후 조에가 대체</t>
-        </is>
-      </c>
+      <c r="O117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7407,34 +7889,35 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="M118" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(마스터 밴 2018.10.15 공개·국내 출시), autoecupart.net(PCF7961M 4A 433MHz 3버튼 — 마스터3 등), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N118" s="2" t="inlineStr">
-        <is>
-          <t>원본 목록 2019~ — 밴은 2018.10 먼저 출시</t>
-        </is>
-      </c>
+      <c r="O118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7467,30 +7950,35 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L119" s="2" t="inlineStr">
+      <c r="M119" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr">
+      <c r="N119" s="2" t="inlineStr">
         <is>
           <t>cvinfo.com/automorning.com(마스터 버스 2019.6.3 출시, 무선 리모컨키), onlyda.com(르노 순정 3버튼 PCF7961M Hitag AES 4A 434MHz), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7523,34 +8011,35 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L120" s="2" t="inlineStr">
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>carisyou.com(부분변경 르노 마스터 밴·버스 출시), onlyda.com(르노·다치아 PCF7961M 4A VA2), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N120" s="2" t="inlineStr">
-        <is>
-          <t>마스터3 페이즈3(2019~) — 2020년식 VA6+PCF7947 사용 사례 있음</t>
-        </is>
-      </c>
+      <c r="O120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7583,32 +8072,37 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr">
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L121" s="4" t="inlineStr">
+      <c r="M121" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr">
+      <c r="N121" s="2" t="inlineStr">
         <is>
           <t>carnoon.co.kr(뉴 마스터 가격·제원), cndiykey.com(르노 3버튼 PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
         </is>
       </c>
     </row>
@@ -7643,32 +8137,37 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L122" s="4" t="inlineStr">
+      <c r="M122" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(마스터 버스 2022년형 끝으로 단종), autoecupart.net(PCF7961M 4A 마스터3), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N122" s="4" t="inlineStr">
-        <is>
-          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
         </is>
       </c>
     </row>
@@ -7703,32 +8202,37 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L123" s="4" t="inlineStr">
+      <c r="M123" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M123" s="2" t="inlineStr">
+      <c r="N123" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(2023 수입 불안정 68대 판매), onlyda.com(PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N123" s="4" t="inlineStr">
-        <is>
-          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
         </is>
       </c>
     </row>
@@ -7763,32 +8267,37 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L124" s="4" t="inlineStr">
+      <c r="M124" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr">
+      <c r="N124" s="2" t="inlineStr">
         <is>
           <t>carnoon.co.kr(뉴 마스터 2024년형 2.3 밴), motormag.co.kr(2024.5.13 700대 특별 판매), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N124" s="4" t="inlineStr">
-        <is>
-          <t>자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
         </is>
       </c>
     </row>
@@ -7823,37 +8332,42 @@
           <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="2" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
         <is>
           <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
         </is>
       </c>
-      <c r="L125" s="4" t="inlineStr">
+      <c r="M125" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr">
+      <c r="N125" s="2" t="inlineStr">
         <is>
           <t>namu.wiki(700대 한정 2025.9까지 판매), moter.kr(신형 마스터 4세대), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="N125" s="4" t="inlineStr">
-        <is>
-          <t>3세대 한정 판매 2025.9 종료 — 4세대 국내 출시 미확인 / 자료 연식 범위(~2020) 밖 — 페이즈3 이후 칩 변경 여부 직접 확인 안 됨</t>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N125"/>
+  <autoFilter ref="A1:O125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7864,7 +8378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -7890,66 +8404,70 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(SM5 1세대 1998년 출시분도 2000년식부터).</t>
+          <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적고 비고에 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 마스터 밴 2018~).</t>
+          <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>- '이모빌라이저 시스템': 르노 계열은 UCH(메간3/플루언스/래티튜드 세대) → BCM(클리오4·캡처 이후 Hitag AES 세대), 닛산 기반 구형 삼성 차종은 NATS(르노삼성 12자리 코드)로 적었습니다.</t>
+          <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>- 카드형 스마트키(르노 카드)는 '카드키(부품번호)' 칸에 적었습니다. 부품번호는 동일 플랫폼 르노 차종의 순정 번호(285975779R, 285977147R 등)이며 국내 순정 품번은 대부분 확인되지 않았습니다 — 르노코리아 부품은 VIN(KNMA…)별로 상이.</t>
+          <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(SM5 1세대 1998년 출시분도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>- '키블레이드(부품번호)'는 해당 연식 검색에서 직접 나온 경우에만 적었고 나머지는 공란입니다(기아 파일 규칙). 키웨이는 카드 비상키 블레이드 기준(VA2/NSN14 등)입니다.</t>
+          <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 마스터 밴 2018~).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49·ID8A → X/△/O, 구형(ID46)·신형(AES) 칩이 병기된 행 → △/△/O(기아 파일 혼재 행 규칙). 실제 적용 전 장비로 재확인하세요.</t>
+          <t>- '이모빌라이저 시스템': 르노 계열은 UCH(메간3/플루언스/래티튜드 세대) → BCM(클리오4·캡처 이후 Hitag AES 세대), 닛산 기반 구형 삼성 차종은 NATS(르노삼성 12자리 코드)로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 원문 페이지를 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
+          <t>- 카드형 스마트키(르노 카드)는 '카드키(부품번호)' 칸에 적었습니다. 부품번호는 동일 플랫폼 르노 차종의 순정 번호(285975779R, 285977147R 등)이며 국내 순정 품번은 대부분 확인되지 않았습니다 — 르노코리아 부품은 VIN(KNMA…)별로 상이.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>- '키블레이드(부품번호)'는 해당 연식 검색에서 직접 나온 경우에만 적었고 나머지는 공란입니다(기아 파일 규칙). 키웨이는 카드 비상키 블레이드 기준(VA2/NSN14 등)입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>※ 색상</t>
+          <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49·ID8A → X/△/O, 구형(ID46)·신형(AES) 칩이 병기된 행 → △/△/O(기아 파일 혼재 행 규칙). 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
+          <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 원문 페이지를 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
@@ -7959,68 +8477,85 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>※ 조사하며 확인된 주요 사항</t>
+          <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>- [재조사] SM3 CF는 르노삼성이 생산한 닛산 알메라 클래식(러시아)·써니(중동)와 같은 차라 ID46 PCF7936·NSN14로 확인했습니다. SM3 1세대는 같은 차체라 동일 가능성이 높으나 직접 자료는 없습니다.</t>
+          <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>- SM5 1·2세대, SM7 1세대는 한국어·러시아·중남미·중동 자료를 다시 찾았지만 칩을 밝힌 자료가 없어 닛산 기준 추정(주황)으로 남겼습니다.</t>
-        </is>
-      </c>
+      <c r="A17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>- [재조사] SM5 3세대·SM7 2세대는 래티튜드용 ID46 카드와 삼성 전용 AES(PCF7945M, 434MHz) 카드가 함께 판매되어 두 칩을 병기했습니다(주황). 285975779R 카드도 후기 순정품에 PCF7953M(4A) 사양이 있습니다.</t>
+          <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>- [재조사] 마스터3는 ID46 PCF7947, 블레이드 VA6 리모컨키입니다(이전 초안의 ID4A 추정은 오류). 그랑 콜레오스는 지리 몬자로 순정 키(Hitag AES 4A / DST AES 8A) 기준입니다.</t>
+          <t>- [재조사] SM3 CF는 르노삼성이 생산한 닛산 알메라 클래식(러시아)·써니(중동)와 같은 차라 ID46 PCF7936·NSN14로 확인했습니다. SM3 1세대는 같은 차체라 동일 가능성이 높으나 직접 자료는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>- SM5 2세대·SM7 1세대 카드형 스마트키: 0156 타입(2005~2007)과 T002 타입(2008~, 뉴아트·임프레션)은 서로 호환되지 않습니다. FCC TFWB1J637(312.4MHz).</t>
+          <t>- SM5 1·2세대, SM7 1세대는 한국어·러시아·중남미·중동 자료를 다시 찾았지만 칩을 밝힌 자료가 없어 닛산 기준 추정(주황)으로 남겼습니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>- SM3 2세대(플루언스), SM5 3세대·SM7 2세대(래티튜드): ID46 PCF7952 카드 285975779R, VA2, UCH. 2011년경부터 UCH 소프트웨어 변경으로 OBD 등록 제한 자료 있음.</t>
+          <t>- [재조사] SM5 3세대·SM7 2세대는 래티튜드용 ID46 카드와 삼성 전용 AES(PCF7945M, 434MHz) 카드가 함께 판매되어 두 칩을 병기했습니다(주황). 285975779R 카드도 후기 순정품에 PCF7953M(4A) 사양이 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>- QM5(콜레오스 H45): ID46 PCF7952 카드 285979045R(핸즈프리)/285970036R(비핸즈프리), 비상키 NSN14 또는 VA2 두 종류. QM5용 AES(PCF7953) 카드도 존재(적용 연식 미확인).</t>
+          <t>- [재조사] 마스터3는 ID46 PCF7947, 블레이드 VA6 리모컨키입니다(이전 초안의 ID4A 추정은 오류). 그랑 콜레오스는 지리 몬자로 순정 키(Hitag AES 4A / DST AES 8A) 기준입니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>- QM3·클리오4: 285971998R(핸즈프리 PCF7953M 4A) / 285974100R(비핸즈프리). SM6·QM6: 285977147R(PCF7953M/NCF29A1M 4A). 캡처2·조에·XM3·아르카나: 285979827R/285973979R(NCF29A1M 4A).</t>
+          <t>- SM5 2세대·SM7 1세대 카드형 스마트키: 0156 타입(2005~2007)과 T002 타입(2008~, 뉴아트·임프레션)은 서로 호환되지 않습니다. FCC TFWB1J637(312.4MHz).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>- SM3 2세대(플루언스), SM5 3세대·SM7 2세대(래티튜드): ID46 PCF7952 카드 285975779R, VA2, UCH. 2011년경부터 UCH 소프트웨어 변경으로 OBD 등록 제한 자료 있음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>- QM5(콜레오스 H45): ID46 PCF7952 카드 285979045R(핸즈프리)/285970036R(비핸즈프리), 비상키 NSN14 또는 VA2 두 종류. QM5용 AES(PCF7953) 카드도 존재(적용 연식 미확인).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>- QM3·클리오4: 285971998R(핸즈프리 PCF7953M 4A) / 285974100R(비핸즈프리). SM6·QM6: 285977147R(PCF7953M/NCF29A1M 4A). 캡처2·조에·XM3·아르카나: 285979827R/285973979R(NCF29A1M 4A).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>- 그랑 콜레오스는 지리 싱웨L(몬자로) 기반으로, 키 칩 자료가 없어 지리 자료 기준 추정입니다.</t>
         </is>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -124,16 +124,16 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -142,7 +142,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,7 +529,7 @@
     <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>모델명</t>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,6 +149,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -545,77 +548,77 @@
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>모델명</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>연식</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>XT27A/A66 호환</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>XT27B 호환</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>XT57B 호환</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>칩코드 (예: ID46(PCF7936))</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>키종류</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>키블레이드(부품번호)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>키블레이드(키웨이)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>카드키(부품번호)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>스마트키(부품번호)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>폴딩키(부품번호)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>이모빌라이저 시스템</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -627,12 +630,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>SM3 (1세대, N17)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
@@ -654,29 +657,29 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+          <t>ID46(PCF7936)[추정]</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (동일 차체 CF 확인값)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="I2" s="9" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>NSN14</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr"/>
+      <c r="M2" s="9" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>wikipedia(SM3 2002.9.2 판매 개시, 블루버드 실피 G10 기반), abkeys.com(닛산 4D-60 NSN14 1999+), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
@@ -693,12 +696,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>SM3 (1세대, N17)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
@@ -720,29 +723,29 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+          <t>ID46(PCF7936)[추정]</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (동일 차체 CF 확인값)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="I3" s="9" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>NSN14</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr"/>
+      <c r="M3" s="9" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>gskeyae.com(2003+ 닛산 NSN14 PCF7936 ID46), kecool.com(ICC: 르노삼성 SM3·SM5·SM7 12자리 코드), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
@@ -759,12 +762,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>SM3 (1세대, N17)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
@@ -786,29 +789,29 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+          <t>ID46(PCF7936)[추정]</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (동일 차체 CF 확인값)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="I4" s="9" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>NSN14</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr"/>
+      <c r="M4" s="9" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>abkeys.com(닛산 NSN14 PCF7936 ID46 2003+), nissanforums.com(블루버드 실피 2004 이그니션), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
@@ -825,12 +828,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>SM3 (1세대, N17)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>2005(단종)</t>
         </is>
@@ -852,29 +855,29 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936) 추정 — 동일 차체 후기형(CF, 알메라 클래식) ID46 확인</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+          <t>ID46(PCF7936)[추정]</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (동일 차체 CF 확인값)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>NSN14</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>gskeyae.com(2003+ NSN14 ID46), namu.wiki(2005.8 뉴 제너레이션 페이스리프트), [재조사] autokeymaster.ru(동일 차체 알메라 클래식 NSN14 PCF7936), digital-kaos.co.uk(한국산 써니=SM3 ID46)</t>
         </is>
@@ -891,12 +894,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SM3 뉴 제너레이션 (1세대 페이스리프트, CF)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
@@ -916,36 +919,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>danawa(SM3 뉴 제너레이션 N17 제원), namu.wiki(2005.8 뉴 제너레이션 출시), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -953,12 +956,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>SM3 뉴 제너레이션 (1세대 페이스리프트, CF)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
@@ -978,36 +981,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>clien.net(구형 SM3 리모컨키 CR2032), abkeys.com(닛산 NSN14 PCF7936 ID46 2003+), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -1015,12 +1018,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>SM3 뉴 제너레이션 (1세대 페이스리프트, CF)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
@@ -1040,36 +1043,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr"/>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(2007 SM3 뉴제너레이션), gskeyae.com(2003+ NSN14 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="P8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1077,12 +1080,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>SM3 뉴 제너레이션 (1세대 페이스리프트, CF)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
@@ -1102,36 +1105,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr"/>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>danawa(SM3 뉴 제너레이션), interpark(뉴SM3 리모컨 폴딩키 케이스), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1139,12 +1142,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>SM3 뉴 제너레이션 (1세대 페이스리프트, CF)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
@@ -1164,36 +1167,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>wikipedia(2009.11 2세대 판매 개시, 구형 병행), gskeyae.com(NSN14 ID46), ko.wikipedia(SM3 CE 2009.7.13 출시), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1201,12 +1204,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>SM3 뉴 제너레이션 (1세대 페이스리프트, CF)</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
@@ -1226,36 +1229,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr"/>
+      <c r="M11" s="9" t="inlineStr"/>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>dailycar.co.kr(SM3 CE 2009.7 출시, 신·구형 병행 판매), abkeys.com(NSN14 PCF7936 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1263,12 +1266,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>SM3 뉴 제너레이션 (1세대 페이스리프트, CF)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>2011(단종)</t>
         </is>
@@ -1288,36 +1291,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>NSN14</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="9" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>ko.wikipedia(SM3 CE 2011.3.31 단종), gskeyae.com(2003-2020 닛산 NSN14 ID46), [재조사] digital-kaos.co.uk(한국산 닛산 써니 2008=SM3 CF: ID46 트랜스폰더, 이모빌라이저 대시보드), autokeymaster.ru(닛산 알메라 클래식 B10RS 2006.01-2012.11 순정키 NSN14 PCF7936 433MHz), originalkey.ru(알메라 클래식 2006-2012 PCF7936), svedit.ru(알메라 클래식 B10/SM3 히타치 SH7055 ECU 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1325,12 +1328,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
@@ -1350,40 +1353,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952)</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr"/>
+      <c r="M13" s="9" t="inlineStr"/>
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>wikipedia(SM3 L38 2009.11 판매 개시), renaultkoream.com e-guide(인텔리전트 스마트카드: 도어·트렁크·시동), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1391,12 +1394,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
@@ -1416,40 +1419,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr"/>
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>amazon.co.uk(ID46-PCF7952A 카드키 메간3/플루언스), mr-key.com(PCF7952 ID46 카드키), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -1457,12 +1460,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
@@ -1482,40 +1485,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr"/>
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>mk3.com(메간3·플루언스 카드키 285975779R PCF7952), keyfirst.eu(플루언스 2008-2016 카드키 VA2), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -1523,12 +1526,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
@@ -1548,40 +1551,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952)</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr"/>
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" s="9" t="inlineStr">
         <is>
           <t>tlkeys.com(285975779R 2012-2016 PCF7952A), abkeys.com(플루언스 2008+ 285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -1589,12 +1592,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
@@ -1614,40 +1617,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952)</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr"/>
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>gskeyae.com(285975779R), keyfirst.eu(플루언스 2008-2016 VA2 ID46 PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -1655,12 +1658,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
@@ -1680,40 +1683,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952)</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="9" t="inlineStr"/>
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" s="9" t="inlineStr">
         <is>
           <t>abkeys.com(285975779R), kigoauto.com(PCF7952 285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경)</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -1721,12 +1724,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
@@ -1748,33 +1751,33 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7953M)[후기 일부]</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr"/>
+      <c r="M19" s="9" t="inlineStr"/>
       <c r="N19" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>ebay(플루언스 2012-2016 ID46 PCF7952A 카드키), hankyung.com(2016년형 SM3 네오 2015.4), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
@@ -1791,12 +1794,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -1818,33 +1821,33 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7953M)[후기 일부]</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" s="9" t="inlineStr">
         <is>
           <t>ebay(플루언스 2012-2016 카드키), keyshop-online.com(플루언스 VA2 ID46), hankyung.com(2016년형 SM3 네오), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
@@ -1861,12 +1864,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -1888,33 +1891,33 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7953M)[후기 일부]</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr"/>
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr"/>
       <c r="N21" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>clien.net(SM3 스마트카드), abkeys.com(285975779R), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
@@ -1931,12 +1934,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -1958,33 +1961,33 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7953M)[후기 일부]</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" s="9" t="inlineStr">
         <is>
           <t>renaultkoream.com e-guide(SM3 인텔리전트 스마트카드), mk3.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
@@ -2001,12 +2004,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
@@ -2028,33 +2031,33 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7953M)[후기 일부]</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr"/>
       <c r="N23" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>wikipedia(SM3 2019 내연기관 생산 종료), remkeys.com(285975779R PCF7952), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
@@ -2071,12 +2074,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>SM3 (2세대, 플루언스 기반)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>2020(단종)</t>
         </is>
@@ -2098,33 +2101,33 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) — 후기 순정 285975779R 중 PCF7953M(4A, AES) 사양 존재</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7953M)[후기 일부]</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (플루언스/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" s="9" t="inlineStr">
         <is>
           <t>wikipedia(SM3 2003-2020), remkeys.com(285975779R PCF7952 433MHz), renault-immo-tools/immo-tools.lt(메간3·씨닉3·플루언스 X95 UCH, 2011~ 소프트웨어 변경), [재조사] tlkeys.com(285975779R 순정 PCF7953M 4A 사양), autoremotecontrols.com(메간3·플루언스 285977505/285975779R PCF7952)</t>
         </is>
@@ -2141,12 +2144,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>SM5 (1세대)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
@@ -2168,29 +2171,29 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+          <t>ID60(4D60)[추정]</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준)</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr"/>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[닛산 기준]</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr"/>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>amazon(1999-2006 닛산 맥시마 등 N102T 4D60), wikipedia(SM5 = 닛산 맥시마 A32 기반)</t>
         </is>
@@ -2207,12 +2210,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>SM5 (1세대)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
@@ -2234,29 +2237,29 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+          <t>ID60(4D60)[추정]</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준)</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[닛산 기준]</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
         <is>
           <t>maxima.org(2001-2003 NATS), kecool.com(ICC IMMO 계산기: 르노삼성 SM3·SM5·SM7 12자리 코드 NATS)</t>
         </is>
@@ -2273,12 +2276,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>SM5 (1세대)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
@@ -2300,29 +2303,29 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+          <t>ID60(4D60)[추정]</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준)</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr"/>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[닛산 기준]</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr"/>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>remotesandkeys.com(2002 맥시마 NI02T 4D60), carisyou.com(2002 SM5 제원)</t>
         </is>
@@ -2339,12 +2342,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>SM5 (1세대)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
@@ -2366,29 +2369,29 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+          <t>ID60(4D60)[추정]</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준)</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[닛산 기준]</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
         <is>
           <t>xecutive(맥시마 2000-2003 트랜스폰더키), namu.wiki(2003.9.1 페이스리프트 NPQ)</t>
         </is>
@@ -2405,12 +2408,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>SM5 (1세대)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
@@ -2432,29 +2435,29 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+          <t>ID60(4D60)[추정]</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준)</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr"/>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[닛산 기준]</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr"/>
+      <c r="L29" s="9" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr"/>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
         <is>
           <t>royalkeysupply.com(1999-2004 맥시마 NI02T 4D60), gparts.co.kr(2004 SM520 부품)</t>
         </is>
@@ -2471,12 +2474,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>SM5 (1세대)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>2005(단종)</t>
         </is>
@@ -2498,29 +2501,29 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>ID60(4D60) 추정(닛산 맥시마/세피로 A33 기준)</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+          <t>ID60(4D60)[추정]</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준)</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[닛산 기준]</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="9" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
         <is>
           <t>abkeys.com(닛산 4D-60 NSN14 1999+), namu.wiki(NPQ 2003.9-2005.3, 2세대 2005.1.25 출시)</t>
         </is>
@@ -2537,12 +2540,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>SM5 (2세대)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
@@ -2564,33 +2567,29 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 기준)</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 0156 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr"/>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(뉴 SM5 EX1 2005.1.25 출시, 국산 중형 최초 스마트 카드키), awesomemotors.kr(05~07년 SM7·뉴SM5 스마트키 0156 타입), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
@@ -2607,12 +2606,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>SM5 (2세대)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
@@ -2634,33 +2633,29 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 기준)</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 0156 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(0156 타입: 뉴아트·임프레션 호환 안 됨), autoecupart.net(티아나 2005-2008 스마트키 ID46), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
@@ -2677,12 +2672,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>SM5 (2세대)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
@@ -2704,33 +2699,29 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 기준)</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 0156 타입(2007.7 이전) / T002 타입(뉴 임프레션), FCC TFWB1J637(312.4MHz 3버튼)</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="I33" s="9" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr"/>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(2007.7.2 뉴 임프레션 페이스리프트), awesomemotors.kr(0156 05~07년), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
@@ -2747,12 +2738,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>SM5 (2세대)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
@@ -2774,33 +2765,29 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 기준)</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 T002 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002: SM7 뉴아트·SM5 임프레션, 2008 이상), carusedpart.co.kr(뉴SM5 순정 스마트키 TFWB1J637), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
@@ -2817,12 +2804,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>SM5 (2세대)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
@@ -2844,33 +2831,29 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 기준)</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 T002 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="inlineStr"/>
+      <c r="M35" s="9" t="inlineStr"/>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002 2008 이상), danawa(SM5 뉴 임프레션 EX1/DF LE플러스 이상 스마트키), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
@@ -2887,12 +2870,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>SM5 (2세대)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>2010(단종)</t>
         </is>
@@ -2914,33 +2897,29 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 기준)</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 T002 타입, FCC TFWB1J637(312.4MHz 3버튼)</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
         <is>
           <t>cnautokey.net(SM5·SM7 스마트키 312.4MHz TFWB1J637), namu.wiki(뉴 임프레션 2007.7-2010), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
@@ -2957,12 +2936,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
@@ -2984,33 +2963,33 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr"/>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
         <is>
           <t>danawa(뉴 SM5 L43 2010.1.18 출시), smautomall(뉴SM5 L43 스마트카드 리모컨+비상키, VIN별 상이), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3027,12 +3006,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
@@ -3054,33 +3033,33 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr"/>
+      <c r="M38" s="9" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O38" s="9" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(래티튜드 2011-2015 4버튼 키카드 433MHz ID46 Hitag2), carusedpart.co.kr(신형 SM5 순정 스마트키), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3097,12 +3076,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
@@ -3124,33 +3103,33 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr"/>
+      <c r="M39" s="9" t="inlineStr"/>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O39" s="9" t="inlineStr">
         <is>
           <t>mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), danawa(뉴 SM5 PH1 ~2012.11), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3167,12 +3146,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
@@ -3194,33 +3173,33 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O40" s="9" t="inlineStr">
         <is>
           <t>amazon.fr(PCF7952 VA2 4버튼 카드), eurocarkeyshop(4버튼 카드 케이스), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3237,12 +3216,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
@@ -3264,33 +3243,33 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr"/>
+      <c r="M41" s="9" t="inlineStr"/>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O41" s="9" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2), carinterior.alibaba(2007-2014 매직카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3307,12 +3286,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
@@ -3334,33 +3313,33 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr"/>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr"/>
+      <c r="M42" s="9" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O42" s="9" t="inlineStr">
         <is>
           <t>danawa(SM5 노바 2015.1.5 출시), reidsremotes.com.au(래티튜드 ~2015 ID46), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3377,12 +3356,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -3404,33 +3383,33 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(2016 PE+ → 클래식 트림), danawa(SM5 노바 제원), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3447,12 +3426,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -3474,33 +3453,33 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(SM5 클래식 단일 트림), youtube(SM5 스마트카드), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3517,12 +3496,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -3544,33 +3523,33 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr"/>
+      <c r="M45" s="9" t="inlineStr"/>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O45" s="9" t="inlineStr">
         <is>
           <t>carwiki.co.kr(SM5 노바 2019년형), namu.wiki(SM5 3세대), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3587,12 +3566,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>SM5 (3세대, 뉴 SM5)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>2019(단종)</t>
         </is>
@@ -3614,33 +3593,33 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="I46" s="9" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr"/>
+      <c r="M46" s="9" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(SM5 2019.12.31 판매 종료, 2020.1.1 생산 종료, SM5 아듀), carwiki.co.kr(SM5 2019년형), carinterior.alibaba/renolink(래티튜드 2010+ 키카드 등록·BCM 초기화, UCH=BCM), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -3657,12 +3636,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -3682,40 +3661,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr"/>
+      <c r="M47" s="9" t="inlineStr"/>
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="O47" s="9" t="inlineStr">
         <is>
           <t>keyecu.com(탈리스만 2016-2019 PCF7953 285977147R), v.daum.net(SM6 2016 출시 월 3000대)</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
+      <c r="P47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -3723,12 +3702,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -3748,40 +3727,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr"/>
+      <c r="M48" s="9" t="inlineStr"/>
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O48" s="9" t="inlineStr">
         <is>
           <t>mk3.com(메간4·탈리스만 2015-2019 PCF7953M Hitag AES 4A, KR5IK4CH-01), keyshop-online.com(2017-2023 285977147R ID4A VA2)</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="P48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -3789,12 +3768,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -3814,40 +3793,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr"/>
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr"/>
+      <c r="M49" s="9" t="inlineStr"/>
+      <c r="N49" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="O49" s="9" t="inlineStr">
         <is>
           <t>f-key.com(OEM 카드 433MHz 4A PCF7953 탈리스만 2016-2019), keycardservices.co.uk(탈리스만 2015-2018 PCF7953M)</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="P49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -3855,12 +3834,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
@@ -3880,40 +3859,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr"/>
+      <c r="M50" s="9" t="inlineStr"/>
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" s="9" t="inlineStr">
         <is>
           <t>onlyda.com(탈리스만 2016+ 285977147R Hitag AES PCF7953M ID4A), abrites.com(RR018 탈리스만 2019+ 키 등록)</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="P50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -3921,12 +3900,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -3946,40 +3925,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr"/>
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr"/>
+      <c r="M51" s="9" t="inlineStr"/>
+      <c r="N51" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="O51" s="9" t="inlineStr">
         <is>
           <t>wikipedia(탈리스만 2020.2 페이스리프트), carkeyswithease.com(285977147R), smautomall(뉴SM6 스마트카드 원격시동 타입)</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="P51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
@@ -3987,12 +3966,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4012,40 +3991,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr"/>
+      <c r="M52" s="9" t="inlineStr"/>
+      <c r="N52" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" s="9" t="inlineStr">
         <is>
           <t>hickleys.com(탈리스만 2016-2022 285977147R PCF7953M ID4A), smautomall(SM6/뉴SM6 스마트카드 리모컨+비상키)</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr"/>
+      <c r="P52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -4053,12 +4032,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -4078,40 +4057,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr"/>
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr"/>
+      <c r="M53" s="9" t="inlineStr"/>
+      <c r="N53" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="O53" s="9" t="inlineStr">
         <is>
           <t>abkeys.com(메간4·탈리스만 2016+ Hitag AES 285977147R), auto-keys.eu(메간4·탈리스만 Hitag AES NCF29A1M VA2 BCM)</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr"/>
+      <c r="P53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
@@ -4119,12 +4098,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -4144,40 +4123,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr"/>
+      <c r="N54" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="O54" s="9" t="inlineStr">
         <is>
           <t>keyshop-online.com(2017-2023 ID4A 285977147R), wikipedia(르노코리아 SM6 2016-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr"/>
+      <c r="P54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -4185,12 +4164,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4210,40 +4189,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr"/>
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr"/>
+      <c r="M55" s="9" t="inlineStr"/>
+      <c r="N55" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
+      <c r="O55" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(2024 뉴 SM6), keyshop-online.com(ID4A VA2 433MHz), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr"/>
+      <c r="P55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
@@ -4251,12 +4230,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>SM6</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>2025(단종)</t>
         </is>
@@ -4278,33 +4257,33 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="I56" s="9" t="inlineStr"/>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (탈리스만/메간4 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr"/>
+      <c r="M56" s="9" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" s="9" t="inlineStr">
         <is>
           <t>daum/newsis(SM6 2025.3.13 단산, 2025.12 판매 종료), gpkorea.com(SM6·QM6 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
@@ -4321,12 +4300,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
@@ -4348,33 +4327,29 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 계열)</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 0156 타입</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="n"/>
+      <c r="L57" s="9" t="inlineStr"/>
+      <c r="M57" s="9" t="inlineStr"/>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O57" s="9" t="inlineStr">
         <is>
           <t>wikipedia(SM7 2004.11.30 공개, 2004.12.1 판매 개시), namu.wiki(2004.12부터 SM5·SM7 스마트카드 옵션), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4391,12 +4366,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
@@ -4418,33 +4393,29 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 계열)</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 0156 타입</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="I58" s="9" t="inlineStr"/>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="n"/>
+      <c r="L58" s="9" t="inlineStr"/>
+      <c r="M58" s="9" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O58" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(05~07년 SM7·뉴SM5 스마트키 0156), namu.wiki(SM7 1세대 노브형 스마트키), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4461,12 +4432,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
@@ -4488,33 +4459,29 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 계열)</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 0156 타입</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="n"/>
+      <c r="L59" s="9" t="inlineStr"/>
+      <c r="M59" s="9" t="inlineStr"/>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O59" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(0156: 뉴아트·임프레션 호환 안 됨), cafe.daum(부천 SM7 카드키 복사), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4531,12 +4498,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
@@ -4558,33 +4525,29 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 계열)</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 0156 타입</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="n"/>
+      <c r="L60" s="9" t="inlineStr"/>
+      <c r="M60" s="9" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O60" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(SM7 넌아트 0156 타입), cnautokey.net(SM5·SM7 312.4MHz TFWB1J637), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4601,12 +4564,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
@@ -4628,33 +4591,29 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 계열)</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 T002 타입(뉴아트)</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="n"/>
+      <c r="L61" s="9" t="inlineStr"/>
+      <c r="M61" s="9" t="inlineStr"/>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O61" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002: SM7 뉴아트·SM5 임프레션, 2008 이상), carisyou.com(SM7 뉴아트 카드형 스마트키, 노브 회전식), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4671,12 +4630,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
@@ -4698,33 +4657,29 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 계열)</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 T002 타입(뉴아트)</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="n"/>
+      <c r="L62" s="9" t="inlineStr"/>
+      <c r="M62" s="9" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O62" s="9" t="inlineStr">
         <is>
           <t>wikicar.co.kr(SM7 뉴아트 2010년형 2009.10), awesomemotors.kr(T002), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4741,12 +4696,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
@@ -4768,33 +4723,29 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>ID46 추정(닛산 티아나 J31 계열)</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+          <t>ID46[추정]</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 (닛산 기준 추정)</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 T002 타입(뉴아트)</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[추정]</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="n"/>
+      <c r="L63" s="9" t="inlineStr"/>
+      <c r="M63" s="9" t="inlineStr"/>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>NATS(닛산 계열, 르노삼성 12자리 코드)</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
+          <t>NATS</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
         <is>
           <t>awesomemotors.kr(T002 2008 이상), cafe.daum(SM7 임프레션 카드키 복사), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4811,12 +4762,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
@@ -4838,33 +4789,33 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>1세대: ID46 추정(닛산 계열) / 2세대: ID46(PCF7952) 또는 삼성 AES(PCF7945M) 카드</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+          <t>ID46[1세대, 추정], ID46(PCF7952)[2세대], ID4A(PCF7945M)[2세대, 카드키]</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
         <is>
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 추정(1세대) / VA2(2세대)</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>카드형 스마트키 T002 타입(뉴아트, 2011.7 이전 생산) / 2세대: 285975779R(래티튜드 공용)</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
+      <c r="I64" s="9" t="inlineStr"/>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[1세대, 추정], VA2[2세대]</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[2세대, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr"/>
+      <c r="M64" s="9" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>NATS(1세대, 2011.7 이전 생산) / UCH(BCM)(2세대 L47, 2011.8 이후 생산)</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
+          <t>NATS[1세대, 2011.7 이전 생산], UCH[2세대, 2011.8 이후 생산]</t>
+        </is>
+      </c>
+      <c r="O64" s="9" t="inlineStr">
         <is>
           <t>wikipedia(2세대 2011.8 판매 개시), awesomemotors.kr(T002), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
@@ -4881,12 +4832,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
@@ -4908,33 +4859,33 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O65" s="9" t="inlineStr">
         <is>
           <t>carwiki.co.kr(올 뉴 SM7 2012년형), pechanara.com(올뉴 SM7 L47 스마트카드 리모컨+보조키 11~14년), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -4951,12 +4902,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
@@ -4978,33 +4929,33 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr"/>
+      <c r="M66" s="9" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O66" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(2013 뉴 SM7 L47), reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2 카드), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -5021,12 +4972,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
@@ -5048,33 +4999,33 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="I67" s="9" t="inlineStr"/>
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr"/>
+      <c r="M67" s="9" t="inlineStr"/>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O67" s="9" t="inlineStr">
         <is>
           <t>pechanara.com(L47 스마트카드 11~14), danawa(SM7 노바 2014.9.2 출시), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -5091,12 +5042,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
@@ -5118,33 +5069,33 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="I68" s="9" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O68" s="9" t="inlineStr">
         <is>
           <t>danawa(SM7 노바 L47 제원), mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -5161,12 +5112,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -5188,33 +5139,33 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
         <is>
           <t>encar.com(SM7 노바), reidsremotes.com.au(래티튜드 ~2015 ID46), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -5231,12 +5182,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -5258,33 +5209,33 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="I70" s="9" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr"/>
+      <c r="M70" s="9" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
         <is>
           <t>danawa(SM7 노바), auto-keys.eu(르노삼성 4버튼 433MHz PCF7952A VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -5301,12 +5252,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -5328,33 +5279,33 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(2019 뉴 SM7 노바), auto-keys.eu(삼성 PCF7953 AES VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -5371,12 +5322,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>SM7</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>2019(단종)</t>
         </is>
@@ -5398,33 +5349,33 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952, Hitag2) / 삼성 전용 AES 카드(PCF7945M, 4A, 434MHz) 병존</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="I72" s="9" t="inlineStr"/>
+      <c r="J72" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>285975779R (래티튜드/메간3 공용, 국내 순정 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>285975779R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr"/>
+      <c r="M72" s="9" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>UCH(BCM)</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
         <is>
           <t>ko.wikipedia(SM7 노바 2014.9-2020.2 생산), carisyou.com(2019 SM7 노바), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
@@ -5441,12 +5392,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>QM3 (1세대)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
@@ -5466,40 +5417,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O73" s="2" t="inlineStr">
+      <c r="O73" s="9" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처1 키카드 2013-2020 285971998R), clien.net(QM3 스마트키 추가 구입 15만5천원), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr"/>
+      <c r="P73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -5507,12 +5458,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>QM3 (1세대)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
@@ -5532,40 +5483,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="I74" s="9" t="inlineStr"/>
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr"/>
+      <c r="M74" s="9" t="inlineStr"/>
+      <c r="N74" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="O74" s="9" t="inlineStr">
         <is>
           <t>honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), autokeys.us(285971998R 클리오4·캡처), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr"/>
+      <c r="P74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
@@ -5573,12 +5524,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>QM3 (1세대)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -5598,40 +5549,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="I75" s="9" t="inlineStr"/>
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O75" s="2" t="inlineStr">
+      <c r="O75" s="9" t="inlineStr">
         <is>
           <t>tlkeys.com(285971998R 2012-2016 Hitag AES), imim.kr(QM3 스마트키 르노삼성), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
+      <c r="P75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
@@ -5639,12 +5590,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>QM3 (1세대)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -5664,40 +5615,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="I76" s="9" t="inlineStr"/>
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr"/>
+      <c r="M76" s="9" t="inlineStr"/>
+      <c r="N76" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O76" s="9" t="inlineStr">
         <is>
           <t>eurocarkeyshop.com(클리오·캡처 키리스 카드 285971998R), wikipedia(캡처 2017.5 페이스리프트), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr"/>
+      <c r="P76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
@@ -5705,12 +5656,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>QM3 (1세대)</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -5730,40 +5681,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="I77" s="9" t="inlineStr"/>
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr"/>
+      <c r="N77" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O77" s="9" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처1 2013-2020 VA2 433.92MHz 4A PCF7953M), accessfobs.co.uk(클리오·캡처 핸즈프리 카드 PCF7953), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr"/>
+      <c r="P77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
@@ -5771,12 +5722,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>QM3 (1세대)</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>2019(단종)</t>
         </is>
@@ -5796,40 +5747,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr"/>
+      <c r="M78" s="9" t="inlineStr"/>
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="O78" s="9" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처1 ~2020), auto-keys.eu(클리오4/삼성 PCF7953 VA2 BCM 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr"/>
+      <c r="P78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
@@ -5837,12 +5788,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>캡처 (QM3 후속 수입)</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -5862,40 +5813,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>285979827R, 285973979R</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr"/>
+      <c r="M79" s="9" t="inlineStr"/>
+      <c r="N79" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O79" s="2" t="inlineStr">
+      <c r="O79" s="9" t="inlineStr">
         <is>
           <t>etoday.co.kr/daum(르노 캡처 2020.5.13 국내 출시, QM3 후속), keyfirst.eu(캡처2 2019-2022 호환 키카드)</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr"/>
+      <c r="P79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
@@ -5903,12 +5854,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>캡처 (QM3 후속 수입)</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -5928,40 +5879,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>285979827R, 285973979R</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O80" s="9" t="inlineStr">
         <is>
           <t>keystation.co.uk(캡처·클리오·아르카나 2016-2021 NCF29A1M Hitag AES 4A, CIT-1/VA2/VA6), car-keys-online.com(클리오5/캡처2/아르카나 285979827R)</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr"/>
+      <c r="P80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
@@ -5969,12 +5920,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>캡처 (QM3 후속 수입)</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -5994,40 +5945,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="I81" s="9" t="inlineStr"/>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>285979827R, 285973979R</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr"/>
+      <c r="M81" s="9" t="inlineStr"/>
+      <c r="N81" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O81" s="2" t="inlineStr">
+      <c r="O81" s="9" t="inlineStr">
         <is>
           <t>keystation.co.uk(캡처 2019-2024 ID4A 285979827R), namu.wiki(캡처 2세대 국내 판매)</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr"/>
+      <c r="P81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
@@ -6035,12 +5986,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>캡처 (QM3 후속 수입)</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>2023(단종)</t>
         </is>
@@ -6060,40 +6011,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (클리오5·캡처2·아르카나 공용)</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>285979827R, 285973979R</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O82" s="9" t="inlineStr">
         <is>
           <t>keyfirst.eu(캡처2 2019-2023 카드), car-keys-online.com(285979827R 신형 H-24985)</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr"/>
+      <c r="P82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
@@ -6101,12 +6052,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
@@ -6126,40 +6077,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952A)[키리스], ID46(PCF7941A)[비키리스]</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="I83" s="9" t="inlineStr"/>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr"/>
+      <c r="M83" s="9" t="inlineStr"/>
+      <c r="N83" s="9" t="inlineStr">
+        <is>
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O83" s="9" t="inlineStr">
         <is>
           <t>wikipedia(QM5 2007.11.19 생산·2007.12.10 판매 개시), autokeys.us(콜레오스 NSN14 스마트키 = 삼성 QM5, PCF7952A 433.92MHz), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr"/>
+      <c r="P83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
@@ -6167,12 +6118,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
@@ -6192,40 +6143,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952A)[키리스], ID46(PCF7941A)[비키리스]</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
+      <c r="I84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr"/>
+      <c r="M84" s="9" t="inlineStr"/>
+      <c r="N84" s="9" t="inlineStr">
+        <is>
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O84" s="9" t="inlineStr">
         <is>
           <t>amazon.co.uk(콜레오스 2008-2011 4버튼 카드 PCF7952), namu.wiki(인텔리전트 스마트카드 기본 적용), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr"/>
+      <c r="P84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
@@ -6233,12 +6184,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
@@ -6258,40 +6209,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952A)[키리스], ID46(PCF7941A)[비키리스]</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="I85" s="9" t="inlineStr"/>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L85" s="9" t="inlineStr"/>
+      <c r="M85" s="9" t="inlineStr"/>
+      <c r="N85" s="9" t="inlineStr">
+        <is>
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O85" s="9" t="inlineStr">
         <is>
           <t>car-keys-online.com(콜레오스 H45 2007-2015 Hitag2 PCF7952/PCF7941, 285970036R), ebay.co.uk(285970036R), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr"/>
+      <c r="P85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
@@ -6299,12 +6250,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
@@ -6324,40 +6275,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A 키리스 / PCF7941A 비키리스, Hitag2)</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952A)[키리스], ID46(PCF7941A)[비키리스]</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="I86" s="9" t="inlineStr"/>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr"/>
+      <c r="M86" s="9" t="inlineStr"/>
+      <c r="N86" s="9" t="inlineStr">
+        <is>
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O86" s="9" t="inlineStr">
         <is>
           <t>amazon.es(콜레오스 2008-2011 PCF7952), wikipedia(2011.6 뉴 QM5 페이스리프트), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr"/>
+      <c r="P86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
@@ -6365,12 +6316,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
@@ -6392,33 +6343,33 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
+          <t>ID46(PCF7952A), ID46(PCF7941A), ID4A(PCF7953)[후기형, 추정]</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O87" s="9" t="inlineStr">
         <is>
           <t>reidsremotes.com.au(콜레오스 2008-2016 ID46 NSN14 비상키), smautomall(QM5/뉴QM5 스마트카드 인텔리전트 적용모델), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
@@ -6435,12 +6386,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
@@ -6462,33 +6413,33 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
+          <t>ID46(PCF7952A), ID46(PCF7941A), ID4A(PCF7953)[후기형, 추정]</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
+      <c r="I88" s="9" t="inlineStr"/>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L88" s="9" t="inlineStr"/>
+      <c r="M88" s="9" t="inlineStr"/>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O88" s="9" t="inlineStr">
         <is>
           <t>remotesnkeys.com(콜레오스 2008-2016 ID46 433MHz), wikipedia(2013.4 2014년형 2.0 가솔린), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
@@ -6505,12 +6456,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
@@ -6532,33 +6483,33 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
+          <t>ID46(PCF7952A), ID46(PCF7941A), ID4A(PCF7953)[후기형, 추정]</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
+      <c r="I89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O89" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(2014 QM5 네오), wikipedia(2014.1.20 QM5 네오 출시), ebay(콜레오스 2009-2016 PCF7952), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
@@ -6575,12 +6526,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
@@ -6602,33 +6553,33 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
+          <t>ID46(PCF7952A), ID46(PCF7941A), ID4A(PCF7953)[후기형, 추정]</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
+      <c r="I90" s="9" t="inlineStr"/>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K90" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L90" s="9" t="inlineStr"/>
+      <c r="M90" s="9" t="inlineStr"/>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O90" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(2015 QM5 네오), reidsremotes.com.au(콜레오스 2008-2016 ID46), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
@@ -6645,12 +6596,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>QM5</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>2016(단종)</t>
         </is>
@@ -6672,33 +6623,33 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952A/PCF7941A, Hitag2) 또는 ID4A(PCF7953 AES, 후기형 추정)</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
+          <t>ID46(PCF7952A), ID46(PCF7941A), ID4A(PCF7953)[후기형, 추정]</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>NSN14 또는 VA2 (차량별 상이)</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>285979045R(핸즈프리) / 285970036R(비핸즈프리, PCF7941)</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>BCM(닛산 NATS 계열)</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+          <t>BCM[NATS 계열]</t>
+        </is>
+      </c>
+      <c r="O91" s="9" t="inlineStr">
         <is>
           <t>danawa(QM5 네오 2014.01-2016.09), remotesnkeys.com(콜레오스 2008-2016 ID46 PCF7952A), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
@@ -6715,12 +6666,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" s="9" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -6740,40 +6691,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="I92" s="9" t="inlineStr"/>
+      <c r="J92" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="K92" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L92" s="9" t="inlineStr"/>
+      <c r="M92" s="9" t="inlineStr"/>
+      <c r="N92" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O92" s="2" t="inlineStr">
+      <c r="O92" s="9" t="inlineStr">
         <is>
           <t>wikipedia(QM6 2016.9 출시 = 콜레오스 2세대), keystation.co.uk(콜레오스 2016-2021 NCF29A1M Hitag AES 4A)</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr"/>
+      <c r="P92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
@@ -6781,12 +6732,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -6806,40 +6757,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="I93" s="9" t="inlineStr"/>
+      <c r="J93" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L93" s="9" t="inlineStr"/>
+      <c r="M93" s="9" t="inlineStr"/>
+      <c r="N93" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O93" s="2" t="inlineStr">
+      <c r="O93" s="9" t="inlineStr">
         <is>
           <t>norman-keys.com(2017 콜레오스 OEM 카드 433MHz 4A), carkeyshop.co.uk(콜레오스·메간4·탈리스만 카드 PCF7953M)</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr"/>
+      <c r="P93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
@@ -6847,12 +6798,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -6872,40 +6823,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="I94" s="9" t="inlineStr"/>
+      <c r="J94" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L94" s="9" t="inlineStr"/>
+      <c r="M94" s="9" t="inlineStr"/>
+      <c r="N94" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr">
+      <c r="O94" s="9" t="inlineStr">
         <is>
           <t>keyshop-online.com(2017-2023 메간4·탈리스만·콜레오스 ID4A VA2 285977147R), pechanara.com(QM6 스마트카드)</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr"/>
+      <c r="P94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
@@ -6913,12 +6864,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
@@ -6938,40 +6889,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="I95" s="9" t="inlineStr"/>
+      <c r="J95" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L95" s="9" t="inlineStr"/>
+      <c r="M95" s="9" t="inlineStr"/>
+      <c r="N95" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O95" s="2" t="inlineStr">
+      <c r="O95" s="9" t="inlineStr">
         <is>
           <t>autokeystore.com(메간4·콜레오스2 핸즈프리 카드 KR5IK4CH-01 NCF29A1M), dalkomhae.com(QM6 스마트키)</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr"/>
+      <c r="P95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
@@ -6979,12 +6930,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -7004,40 +6955,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="I96" s="9" t="inlineStr"/>
+      <c r="J96" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="K96" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O96" s="2" t="inlineStr">
+      <c r="O96" s="9" t="inlineStr">
         <is>
           <t>keystation.co.uk(콜레오스 2016-2021 NCF29A1M), carkeymaster.kr(QM6 스마트키 분실)</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr"/>
+      <c r="P96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
@@ -7045,12 +6996,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -7070,40 +7021,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="I97" s="9" t="inlineStr"/>
+      <c r="J97" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr"/>
+      <c r="M97" s="9" t="inlineStr"/>
+      <c r="N97" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O97" s="9" t="inlineStr">
         <is>
           <t>keystation.co.uk(콜레오스 ~2021 4A), keyshop-online.com(2017-2023 ID4A)</t>
         </is>
       </c>
-      <c r="P97" s="2" t="inlineStr"/>
+      <c r="P97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
@@ -7111,12 +7062,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="9" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -7136,40 +7087,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr"/>
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
+      <c r="O98" s="9" t="inlineStr">
         <is>
           <t>keyshop-online.com(2017-2023 콜레오스 ID4A 285977147R), teamblind.com(QM6 스마트키 분실)</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr"/>
+      <c r="P98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
@@ -7177,12 +7128,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -7202,40 +7153,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr"/>
+      <c r="J99" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L99" s="9" t="inlineStr"/>
+      <c r="M99" s="9" t="inlineStr"/>
+      <c r="N99" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O99" s="9" t="inlineStr">
         <is>
           <t>keyshop-online.com(~2023 ID4A), autokeystore.com(콜레오스2 NCF29A1M), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="P99" s="2" t="inlineStr"/>
+      <c r="P99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -7243,12 +7194,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -7268,40 +7219,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O100" s="2" t="inlineStr">
+      <c r="O100" s="9" t="inlineStr">
         <is>
           <t>gpkorea.com(QM6 판매 지속, 2025 단종), keyshop-online.com(ID4A VA2), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr"/>
+      <c r="P100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
@@ -7309,12 +7260,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>QM6</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>2025(단종)</t>
         </is>
@@ -7336,33 +7287,33 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>ID4A(PCF7953M/NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="I101" s="9" t="inlineStr"/>
+      <c r="J101" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>285977147R (콜레오스2/메간4/탈리스만 공용, KR5IK4CH-01) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="inlineStr"/>
+      <c r="M101" s="9" t="inlineStr"/>
       <c r="N101" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O101" s="2" t="inlineStr">
+      <c r="O101" s="9" t="inlineStr">
         <is>
           <t>dailycar.co.kr/gpkorea.com(SM6·QM6 2025.12 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
@@ -7379,12 +7330,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>그랑 콜레오스</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="9" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -7406,33 +7357,29 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
+          <t>ID4A, ID8A</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
         <is>
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>HU100 (지리 스마트키 기준)</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>HU100[지리 스마트키 기준]</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="9" t="n"/>
+      <c r="M102" s="9" t="inlineStr"/>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(지리 CMA 계열)</t>
-        </is>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="O102" s="9" t="inlineStr">
         <is>
           <t>wikipedia(그랑 콜레오스 2024 국내 생산, 지리 싱웨L 기반 CMA 플랫폼), keyshop-online.com(지리 OEM 스마트키 ID4A HU100 433MHz), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
@@ -7449,12 +7396,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>그랑 콜레오스</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -7476,33 +7423,29 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
+          <t>ID4A, ID8A</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
         <is>
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>HU100 (지리 스마트키 기준)</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+      <c r="I103" s="9" t="inlineStr"/>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>HU100[지리 스마트키 기준]</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="9" t="inlineStr"/>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(지리 CMA 계열)</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="O103" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(2025 그랑 콜레오스 하이브리드), tlkeys.com(지리 순정 스마트키), keyshop-online.com(지리 ID4A), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
@@ -7519,12 +7462,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>그랑 콜레오스</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -7546,33 +7489,29 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>ID4A(Hitag AES) 또는 ID8A(DST AES) — 지리 몬자로 기준</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
+          <t>ID4A, ID8A</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
         <is>
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>HU100 (지리 스마트키 기준)</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>지리 몬자로 계열 4버튼 434MHz 스마트키(국내 품번 미확인)</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+      <c r="I104" s="9" t="inlineStr"/>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>HU100[지리 스마트키 기준]</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="inlineStr"/>
+      <c r="L104" s="9" t="n"/>
+      <c r="M104" s="9" t="inlineStr"/>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>확인 불가(지리 CMA 계열)</t>
-        </is>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="O104" s="9" t="inlineStr">
         <is>
           <t>renault.co.kr(그랑 콜레오스 판매 중), wikipedia(싱웨L/몬자로), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
@@ -7589,12 +7528,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>XM3</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -7614,40 +7553,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr">
+      <c r="I105" s="9" t="inlineStr"/>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[해외 공용 품번], 285973979R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O105" s="2" t="inlineStr">
+      <c r="O105" s="9" t="inlineStr">
         <is>
           <t>wikipedia(XM3 2020.3 출시, 부산 생산 LJL), smautomall(XM3 스마트카드 리모컨+비상키, VIN별 상이), teamblind.com(2020.10식 XM3 스마트키)</t>
         </is>
       </c>
-      <c r="P105" s="2" t="inlineStr"/>
+      <c r="P105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
@@ -7655,12 +7594,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="9" t="inlineStr">
         <is>
           <t>XM3</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -7680,40 +7619,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr">
+      <c r="I106" s="9" t="inlineStr"/>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[해외 공용 품번], 285973979R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L106" s="9" t="inlineStr"/>
+      <c r="M106" s="9" t="inlineStr"/>
+      <c r="N106" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O106" s="2" t="inlineStr">
+      <c r="O106" s="9" t="inlineStr">
         <is>
           <t>car-keys-online.com(아르카나 2021-2023 285979827R), keystation.co.uk(아르카나·캡처·클리오 NCF29A1M 4A)</t>
         </is>
       </c>
-      <c r="P106" s="2" t="inlineStr"/>
+      <c r="P106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
@@ -7721,12 +7660,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="9" t="inlineStr">
         <is>
           <t>XM3</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -7746,40 +7685,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr">
+      <c r="I107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[해외 공용 품번], 285973979R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O107" s="2" t="inlineStr">
+      <c r="O107" s="9" t="inlineStr">
         <is>
           <t>keystation.co.uk(아르카나 ID4A CIT-1/VA2/VA6), danawa(XM3 LJL)</t>
         </is>
       </c>
-      <c r="P107" s="2" t="inlineStr"/>
+      <c r="P107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
@@ -7787,12 +7726,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="9" t="inlineStr">
         <is>
           <t>XM3</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -7812,40 +7751,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="I108" s="9" t="inlineStr"/>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[해외 공용 품번], 285973979R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L108" s="9" t="inlineStr"/>
+      <c r="M108" s="9" t="inlineStr"/>
+      <c r="N108" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O108" s="2" t="inlineStr">
+      <c r="O108" s="9" t="inlineStr">
         <is>
           <t>car-keys-online.com(OEM 키카드 클리오5/아르카나/캡처2 신형 H-24985 285979827R), carinfoyou.com(2024 XM3)</t>
         </is>
       </c>
-      <c r="P108" s="2" t="inlineStr"/>
+      <c r="P108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
@@ -7853,12 +7792,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>XM3</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>2024(단종)</t>
         </is>
@@ -7878,40 +7817,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>285979827R / 285973979R (아르카나·클리오5·캡처2 공용) — 국내 순정 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="I109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[해외 공용 품번], 285973979R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O109" s="2" t="inlineStr">
+      <c r="O109" s="9" t="inlineStr">
         <is>
           <t>ko.wikipedia(2024.4.3 국내명 르노 아르카나로 통일), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr"/>
+      <c r="P109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -7919,12 +7858,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" s="9" t="inlineStr">
         <is>
           <t>아르카나 (XM3 국내 리네이밍)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -7946,33 +7885,33 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
+      <c r="I110" s="9" t="inlineStr"/>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[구형 로고]</t>
+        </is>
+      </c>
+      <c r="L110" s="9" t="inlineStr"/>
+      <c r="M110" s="9" t="inlineStr"/>
       <c r="N110" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O110" s="2" t="inlineStr">
+      <c r="O110" s="9" t="inlineStr">
         <is>
           <t>ko.wikipedia(2024.4.3 르노 아르카나 차명 통일), renault.co.kr(아르카나 버튼시동 스마트카드 기본), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
@@ -7989,12 +7928,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="9" t="inlineStr">
         <is>
           <t>아르카나 (XM3 국내 리네이밍)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" s="9" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -8016,33 +7955,33 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr"/>
+      <c r="I111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[구형 로고]</t>
+        </is>
+      </c>
+      <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
       <c r="N111" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O111" s="2" t="inlineStr">
+      <c r="O111" s="9" t="inlineStr">
         <is>
           <t>ko.wikipedia(1.3 터보 2025.4 생산 중지), keytectools.com(르노 Hitag AES ID4A 2018-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
@@ -8059,12 +7998,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="9" t="inlineStr">
         <is>
           <t>아르카나 (XM3 국내 리네이밍)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" s="9" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -8086,33 +8025,33 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>VA2 (VA6 병기 자료 있음)</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>285979827R(구형 로고 차량) — 신형 로고 차량용 품번 미확인</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
+      <c r="I112" s="9" t="inlineStr"/>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>VA2, VA6[일부 자료]</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>285979827R[구형 로고]</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="inlineStr"/>
+      <c r="M112" s="9" t="inlineStr"/>
       <c r="N112" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O112" s="2" t="inlineStr">
+      <c r="O112" s="9" t="inlineStr">
         <is>
           <t>renault.co.kr(아르카나 판매 중), keytectools.com(르노 ID4A ~2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
@@ -8129,12 +8068,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>조에 (Zoe)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -8154,40 +8093,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="I113" s="9" t="inlineStr"/>
+      <c r="J113" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>285979827R (클리오5·캡처2·조에 공용)</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="K113" s="9" t="inlineStr">
+        <is>
+          <t>285979827R</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="inlineStr"/>
+      <c r="M113" s="9" t="inlineStr"/>
+      <c r="N113" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O113" s="2" t="inlineStr">
+      <c r="O113" s="9" t="inlineStr">
         <is>
           <t>ko.wikipedia/motoya.co.kr(조에 2020.8.18 국내 출시), car-keys-online.com(클리오·캡처·조에 순정 키카드 285979827R)</t>
         </is>
       </c>
-      <c r="P113" s="2" t="inlineStr"/>
+      <c r="P113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
@@ -8195,12 +8134,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" s="9" t="inlineStr">
         <is>
           <t>조에 (Zoe)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -8220,40 +8159,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="I114" s="9" t="inlineStr"/>
+      <c r="J114" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>285979827R (클리오5·캡처2·조에 공용)</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>285979827R</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="inlineStr"/>
+      <c r="M114" s="9" t="inlineStr"/>
+      <c r="N114" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O114" s="9" t="inlineStr">
         <is>
           <t>economist.co.kr(2021년형 재고 소진), keystation.co.uk(르노 2016-2021 NCF29A1M Hitag AES 4A)</t>
         </is>
       </c>
-      <c r="P114" s="2" t="inlineStr"/>
+      <c r="P114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
@@ -8261,12 +8200,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>조에 (Zoe)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>2022(단종)</t>
         </is>
@@ -8286,40 +8225,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="I115" s="9" t="inlineStr"/>
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>285979827R (클리오5·캡처2·조에 공용)</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr"/>
-      <c r="M115" s="2" t="inlineStr"/>
-      <c r="N115" s="2" t="inlineStr">
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>285979827R</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="inlineStr"/>
+      <c r="M115" s="9" t="inlineStr"/>
+      <c r="N115" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="O115" s="9" t="inlineStr">
         <is>
           <t>economist.co.kr(2022 판매 중단·단종 수순), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
         </is>
       </c>
-      <c r="P115" s="2" t="inlineStr"/>
+      <c r="P115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
@@ -8327,12 +8266,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="9" t="inlineStr">
         <is>
           <t>클리오 (Clio)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -8352,40 +8291,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="I116" s="9" t="inlineStr"/>
+      <c r="J116" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="inlineStr"/>
+      <c r="M116" s="9" t="inlineStr"/>
+      <c r="N116" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O116" s="9" t="inlineStr">
         <is>
           <t>hankookilbo.com(르노 클리오 2018.5 국내 출시), honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P116" s="2" t="inlineStr"/>
+      <c r="P116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
@@ -8393,12 +8332,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr">
         <is>
           <t>클리오 (Clio)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" s="9" t="inlineStr">
         <is>
           <t>2019(단종)</t>
         </is>
@@ -8418,40 +8357,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M/PCF7945M 핸즈프리 · PCF7961M 비핸즈프리, Hitag AES)</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
         <is>
           <t>카드키</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="I117" s="9" t="inlineStr"/>
+      <c r="J117" s="9" t="inlineStr">
         <is>
           <t>VA2</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>285971998R(핸즈프리, PCF7945M/PCF7953M 4A) / 285974100R(비핸즈프리, PCF7961)</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="2" t="inlineStr"/>
-      <c r="N117" s="2" t="inlineStr">
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
+      <c r="L117" s="9" t="inlineStr"/>
+      <c r="M117" s="9" t="inlineStr"/>
+      <c r="N117" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="O117" s="9" t="inlineStr">
         <is>
           <t>ko.wikipedia(클리오 4세대 국내 2018.5~2019말 판매, 5세대 미출시), keyfirst.eu(클리오4 2012-2019 285971998R VA2), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
-      <c r="P117" s="2" t="inlineStr"/>
+      <c r="P117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
@@ -8459,12 +8398,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -8484,40 +8423,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="I118" s="9" t="inlineStr"/>
+      <c r="J118" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
-        </is>
-      </c>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="K118" s="9" t="inlineStr"/>
+      <c r="L118" s="9" t="inlineStr"/>
+      <c r="M118" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="N118" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O118" s="2" t="inlineStr">
+      <c r="O118" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(마스터 밴 2018.10.15 공개·국내 출시), autoecupart.net(PCF7961M 4A 433MHz 3버튼 — 마스터3 등), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="P118" s="2" t="inlineStr"/>
+      <c r="P118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
@@ -8525,12 +8464,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
@@ -8550,40 +8489,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="I119" s="9" t="inlineStr"/>
+      <c r="J119" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
-        </is>
-      </c>
-      <c r="N119" s="2" t="inlineStr">
+      <c r="K119" s="9" t="inlineStr"/>
+      <c r="L119" s="9" t="inlineStr"/>
+      <c r="M119" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="N119" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O119" s="2" t="inlineStr">
+      <c r="O119" s="9" t="inlineStr">
         <is>
           <t>cvinfo.com/automorning.com(마스터 버스 2019.6.3 출시, 무선 리모컨키), onlyda.com(르노 순정 3버튼 PCF7961M Hitag AES 4A 434MHz), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="P119" s="2" t="inlineStr"/>
+      <c r="P119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
@@ -8591,12 +8530,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -8616,40 +8555,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="I120" s="9" t="inlineStr"/>
+      <c r="J120" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
-        </is>
-      </c>
-      <c r="N120" s="2" t="inlineStr">
+      <c r="K120" s="9" t="inlineStr"/>
+      <c r="L120" s="9" t="inlineStr"/>
+      <c r="M120" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="N120" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
-      <c r="O120" s="2" t="inlineStr">
+      <c r="O120" s="9" t="inlineStr">
         <is>
           <t>carisyou.com(부분변경 르노 마스터 밴·버스 출시), onlyda.com(르노·다치아 PCF7961M 4A VA2), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="P120" s="2" t="inlineStr"/>
+      <c r="P120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
@@ -8657,12 +8596,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -8684,25 +8623,25 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="I121" s="9" t="inlineStr"/>
+      <c r="J121" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+      <c r="K121" s="9" t="inlineStr"/>
+      <c r="L121" s="9" t="inlineStr"/>
+      <c r="M121" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
         </is>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -8710,7 +8649,7 @@
           <t>UCH</t>
         </is>
       </c>
-      <c r="O121" s="2" t="inlineStr">
+      <c r="O121" s="9" t="inlineStr">
         <is>
           <t>carnoon.co.kr(뉴 마스터 가격·제원), cndiykey.com(르노 3버튼 PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
@@ -8727,12 +8666,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" s="9" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -8754,25 +8693,25 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="I122" s="9" t="inlineStr"/>
+      <c r="J122" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+      <c r="K122" s="9" t="inlineStr"/>
+      <c r="L122" s="9" t="inlineStr"/>
+      <c r="M122" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
         </is>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -8780,7 +8719,7 @@
           <t>UCH</t>
         </is>
       </c>
-      <c r="O122" s="2" t="inlineStr">
+      <c r="O122" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(마스터 버스 2022년형 끝으로 단종), autoecupart.net(PCF7961M 4A 마스터3), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
@@ -8797,12 +8736,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -8824,25 +8763,25 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="I123" s="9" t="inlineStr"/>
+      <c r="J123" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr"/>
-      <c r="M123" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+      <c r="K123" s="9" t="inlineStr"/>
+      <c r="L123" s="9" t="inlineStr"/>
+      <c r="M123" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
         </is>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -8850,7 +8789,7 @@
           <t>UCH</t>
         </is>
       </c>
-      <c r="O123" s="2" t="inlineStr">
+      <c r="O123" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(2023 수입 불안정 68대 판매), onlyda.com(PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
@@ -8867,12 +8806,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" s="9" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -8894,25 +8833,25 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="I124" s="9" t="inlineStr"/>
+      <c r="J124" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+      <c r="K124" s="9" t="inlineStr"/>
+      <c r="L124" s="9" t="inlineStr"/>
+      <c r="M124" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
         </is>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -8920,7 +8859,7 @@
           <t>UCH</t>
         </is>
       </c>
-      <c r="O124" s="2" t="inlineStr">
+      <c r="O124" s="9" t="inlineStr">
         <is>
           <t>carnoon.co.kr(뉴 마스터 2024년형 2.3 밴), motormag.co.kr(2024.5.13 700대 특별 판매), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
@@ -8937,12 +8876,12 @@
           <t>르노(르노삼성)</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>마스터 (LCV)</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>2025(단종)</t>
         </is>
@@ -8964,25 +8903,25 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7947, Hitag2) — 마스터3용 PCF7961M(4A) 리모컨도 판매됨</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="I125" s="9" t="inlineStr"/>
+      <c r="J125" s="9" t="inlineStr">
         <is>
           <t>VA6</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="2" t="inlineStr">
-        <is>
-          <t>3버튼 리모컨키(PCF7947) — 참고 품번 7701209236 / 998102668R(르노·오펠·닛산 공용 3버튼)</t>
+      <c r="K125" s="9" t="inlineStr"/>
+      <c r="L125" s="9" t="inlineStr"/>
+      <c r="M125" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
         </is>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -8990,7 +8929,7 @@
           <t>UCH</t>
         </is>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O125" s="9" t="inlineStr">
         <is>
           <t>namu.wiki(700대 한정 2025.9까지 판매), moter.kr(신형 마스터 4세대), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
@@ -9013,24 +8952,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr"/>
+      <c r="A2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
@@ -9044,162 +8983,273 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(SM5 1세대 1998년 출시분도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 마스터 밴 2018~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 르노 계열은 UCH(메간3/플루언스/래티튜드 세대) → BCM(클리오4·캡처 이후 Hitag AES 세대), 닛산 기반 구형 삼성 차종은 NATS(르노삼성 12자리 코드)로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>- 카드형 스마트키(르노 카드)는 '카드키(부품번호)' 칸에 적었습니다. 부품번호는 동일 플랫폼 르노 차종의 순정 번호(285975779R, 285977147R 등)이며 국내 순정 품번은 대부분 확인되지 않았습니다 — 르노코리아 부품은 VIN(KNMA…)별로 상이.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색에서 직접 나온 경우에만 적었고 나머지는 공란입니다(기아 파일 규칙). 키웨이는 카드 비상키 블레이드 기준(VA2/NSN14 등)입니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49·ID8A → X/△/O, 구형(ID46)·신형(AES) 칩이 병기된 행 → △/△/O(기아 파일 혼재 행 규칙). 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 원문 페이지를 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr"/>
+      <c r="A18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>- [재조사] SM3 CF는 르노삼성이 생산한 닛산 알메라 클래식(러시아)·써니(중동)와 같은 차라 ID46 PCF7936·NSN14로 확인했습니다. SM3 1세대는 같은 차체라 동일 가능성이 높으나 직접 자료는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>- SM5 1·2세대, SM7 1세대는 한국어·러시아·중남미·중동 자료를 다시 찾았지만 칩을 밝힌 자료가 없어 닛산 기준 추정(주황)으로 남겼습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>- [재조사] SM5 3세대·SM7 2세대는 래티튜드용 ID46 카드와 삼성 전용 AES(PCF7945M, 434MHz) 카드가 함께 판매되어 두 칩을 병기했습니다(주황). 285975779R 카드도 후기 순정품에 PCF7953M(4A) 사양이 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>- [재조사] 마스터3는 ID46 PCF7947, 블레이드 VA6 리모컨키입니다(이전 초안의 ID4A 추정은 오류). 그랑 콜레오스는 지리 몬자로 순정 키(Hitag AES 4A / DST AES 8A) 기준입니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>- SM5 2세대·SM7 1세대 카드형 스마트키: 0156 타입(2005~2007)과 T002 타입(2008~, 뉴아트·임프레션)은 서로 호환되지 않습니다. FCC TFWB1J637(312.4MHz).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>- SM3 2세대(플루언스), SM5 3세대·SM7 2세대(래티튜드): ID46 PCF7952 카드 285975779R, VA2, UCH. 2011년경부터 UCH 소프트웨어 변경으로 OBD 등록 제한 자료 있음.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>- QM5(콜레오스 H45): ID46 PCF7952 카드 285979045R(핸즈프리)/285970036R(비핸즈프리), 비상키 NSN14 또는 VA2 두 종류. QM5용 AES(PCF7953) 카드도 존재(적용 연식 미확인).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>- QM3·클리오4: 285971998R(핸즈프리 PCF7953M 4A) / 285974100R(비핸즈프리). SM6·QM6: 285977147R(PCF7953M/NCF29A1M 4A). 캡처2·조에·XM3·아르카나: 285979827R/285973979R(NCF29A1M 4A).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>- 그랑 콜레오스는 지리 싱웨L(몬자로) 기반으로, 키 칩 자료가 없어 지리 자료 기준 추정입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>※ 칩 ID 코드 뜻</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -155,6 +155,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2565,9 +2568,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -2584,7 +2587,7 @@
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="inlineStr"/>
       <c r="M31" s="9" t="inlineStr"/>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="N31" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -2594,11 +2597,7 @@
           <t>namu.wiki(뉴 SM5 EX1 2005.1.25 출시, 국산 중형 최초 스마트 카드키), awesomemotors.kr(05~07년 SM7·뉴SM5 스마트키 0156 타입), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -2631,9 +2630,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -2650,7 +2649,7 @@
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="inlineStr"/>
       <c r="M32" s="9" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -2660,11 +2659,7 @@
           <t>awesomemotors.kr(0156 타입: 뉴아트·임프레션 호환 안 됨), autoecupart.net(티아나 2005-2008 스마트키 ID46), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -2697,9 +2692,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -2716,7 +2711,7 @@
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="inlineStr"/>
       <c r="M33" s="9" t="inlineStr"/>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N33" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -2726,11 +2721,7 @@
           <t>namu.wiki(2007.7.2 뉴 임프레션 페이스리프트), awesomemotors.kr(0156 05~07년), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -2763,9 +2754,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -2782,7 +2773,7 @@
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="inlineStr"/>
       <c r="M34" s="9" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -2792,11 +2783,7 @@
           <t>awesomemotors.kr(T002: SM7 뉴아트·SM5 임프레션, 2008 이상), carusedpart.co.kr(뉴SM5 순정 스마트키 TFWB1J637), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -2829,9 +2816,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -2848,7 +2835,7 @@
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="inlineStr"/>
       <c r="M35" s="9" t="inlineStr"/>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -2858,11 +2845,7 @@
           <t>awesomemotors.kr(T002 2008 이상), danawa(SM5 뉴 임프레션 EX1/DF LE플러스 이상 스마트키), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -2895,9 +2878,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -2914,7 +2897,7 @@
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="inlineStr"/>
       <c r="M36" s="9" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -2924,11 +2907,7 @@
           <t>cnautokey.net(SM5·SM7 스마트키 312.4MHz TFWB1J637), namu.wiki(뉴 임프레션 2007.7-2010), kecool.com(ICC: 르노삼성 SM5 12자리 코드)</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -4391,9 +4370,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -4410,7 +4389,7 @@
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="inlineStr"/>
       <c r="M58" s="9" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -4420,11 +4399,7 @@
           <t>awesomemotors.kr(05~07년 SM7·뉴SM5 스마트키 0156), namu.wiki(SM7 1세대 노브형 스마트키), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="P58" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -4457,9 +4432,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -4476,7 +4451,7 @@
       <c r="K59" s="9" t="n"/>
       <c r="L59" s="9" t="inlineStr"/>
       <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="N59" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -4486,11 +4461,7 @@
           <t>awesomemotors.kr(0156: 뉴아트·임프레션 호환 안 됨), cafe.daum(부천 SM7 카드키 복사), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="P59" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
@@ -4523,9 +4494,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -4542,7 +4513,7 @@
       <c r="K60" s="9" t="n"/>
       <c r="L60" s="9" t="inlineStr"/>
       <c r="M60" s="9" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -4552,11 +4523,7 @@
           <t>awesomemotors.kr(SM7 넌아트 0156 타입), cnautokey.net(SM5·SM7 312.4MHz TFWB1J637), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="P60" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
@@ -4589,9 +4556,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -4608,7 +4575,7 @@
       <c r="K61" s="9" t="n"/>
       <c r="L61" s="9" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="N61" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -4618,11 +4585,7 @@
           <t>awesomemotors.kr(T002: SM7 뉴아트·SM5 임프레션, 2008 이상), carisyou.com(SM7 뉴아트 카드형 스마트키, 노브 회전식), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="P61" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -4655,9 +4618,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
@@ -4674,7 +4637,7 @@
       <c r="K62" s="9" t="n"/>
       <c r="L62" s="9" t="inlineStr"/>
       <c r="M62" s="9" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -4684,11 +4647,7 @@
           <t>wikicar.co.kr(SM7 뉴아트 2010년형 2009.10), awesomemotors.kr(T002), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -4721,9 +4680,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -4740,7 +4699,7 @@
       <c r="K63" s="9" t="n"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="4" t="inlineStr">
+      <c r="N63" s="12" t="inlineStr">
         <is>
           <t>NATS</t>
         </is>
@@ -4750,11 +4709,7 @@
           <t>awesomemotors.kr(T002 2008 이상), cafe.daum(SM7 임프레션 카드키 복사), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="P63" s="4" t="inlineStr">
-        <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
-        </is>
-      </c>
+      <c r="P63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
@@ -4789,7 +4744,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>ID46[1세대, 추정], ID46(PCF7952)[2세대], ID4A(PCF7945M)[2세대, 카드키]</t>
+          <t>ID46(PCF7941)[1세대], ID46(PCF7952)[2세대], ID4A(PCF7945M)[2세대, 카드키]</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -4822,7 +4777,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
+          <t>2세대(2011.8~) ID46 카드와 삼성 전용 AES 카드 병존 — 적용 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8611,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
+          <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8681,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
+          <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8751,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
+          <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8821,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
+          <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8891,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>칩 자료가 2020년까지 — 이후 연식 추정</t>
+          <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
         </is>
       </c>
     </row>
@@ -8959,184 +8914,184 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr"/>
+      <c r="A2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(SM5 1세대 1998년 출시분도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 마스터 밴 2018~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 르노 계열은 UCH(메간3/플루언스/래티튜드 세대) → BCM(클리오4·캡처 이후 Hitag AES 세대), 닛산 기반 구형 삼성 차종은 NATS(르노삼성 12자리 코드)로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>- 카드형 스마트키(르노 카드)는 '카드키(부품번호)' 칸에 적었습니다. 부품번호는 동일 플랫폼 르노 차종의 순정 번호(285975779R, 285977147R 등)이며 국내 순정 품번은 대부분 확인되지 않았습니다 — 르노코리아 부품은 VIN(KNMA…)별로 상이.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색에서 직접 나온 경우에만 적었고 나머지는 공란입니다(기아 파일 규칙). 키웨이는 카드 비상키 블레이드 기준(VA2/NSN14 등)입니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49·ID8A → X/△/O, 구형(ID46)·신형(AES) 칩이 병기된 행 → △/△/O(기아 파일 혼재 행 규칙). 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 원문 페이지를 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr"/>
+      <c r="A15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr"/>
+      <c r="A18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>- [재조사] SM3 CF는 르노삼성이 생산한 닛산 알메라 클래식(러시아)·써니(중동)와 같은 차라 ID46 PCF7936·NSN14로 확인했습니다. SM3 1세대는 같은 차체라 동일 가능성이 높으나 직접 자료는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>- SM5 1·2세대, SM7 1세대는 한국어·러시아·중남미·중동 자료를 다시 찾았지만 칩을 밝힌 자료가 없어 닛산 기준 추정(주황)으로 남겼습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>- [재조사] SM5 3세대·SM7 2세대는 래티튜드용 ID46 카드와 삼성 전용 AES(PCF7945M, 434MHz) 카드가 함께 판매되어 두 칩을 병기했습니다(주황). 285975779R 카드도 후기 순정품에 PCF7953M(4A) 사양이 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>- [재조사] 마스터3는 ID46 PCF7947, 블레이드 VA6 리모컨키입니다(이전 초안의 ID4A 추정은 오류). 그랑 콜레오스는 지리 몬자로 순정 키(Hitag AES 4A / DST AES 8A) 기준입니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>- SM5 2세대·SM7 1세대 카드형 스마트키: 0156 타입(2005~2007)과 T002 타입(2008~, 뉴아트·임프레션)은 서로 호환되지 않습니다. FCC TFWB1J637(312.4MHz).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>- SM3 2세대(플루언스), SM5 3세대·SM7 2세대(래티튜드): ID46 PCF7952 카드 285975779R, VA2, UCH. 2011년경부터 UCH 소프트웨어 변경으로 OBD 등록 제한 자료 있음.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>- QM5(콜레오스 H45): ID46 PCF7952 카드 285979045R(핸즈프리)/285970036R(비핸즈프리), 비상키 NSN14 또는 VA2 두 종류. QM5용 AES(PCF7953) 카드도 존재(적용 연식 미확인).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>- QM3·클리오4: 285971998R(핸즈프리 PCF7953M 4A) / 285974100R(비핸즈프리). SM6·QM6: 285977147R(PCF7953M/NCF29A1M 4A). 캡처2·조에·XM3·아르카나: 285979827R/285973979R(NCF29A1M 4A).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>- 그랑 콜레오스는 지리 싱웨L(몬자로) 기반으로, 키 칩 자료가 없어 지리 자료 기준 추정입니다.</t>
         </is>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +158,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4727,14 +4730,14 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -4742,9 +4745,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7941)[1세대], ID46(PCF7952)[2세대], ID4A(PCF7945M)[2세대, 카드키]</t>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941)[1세대]</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -4752,22 +4755,18 @@
           <t>막대키,카드키</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr"/>
+      <c r="I64" s="9" t="n"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>NSN14[1세대, 추정], VA2[2세대]</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>285975779R[2세대, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="L64" s="9" t="inlineStr"/>
-      <c r="M64" s="9" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t>NATS[1세대, 2011.7 이전 생산], UCH[2세대, 2011.8 이후 생산]</t>
+          <t>NSN14[1세대, 추정]</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="n"/>
+      <c r="L64" s="9" t="n"/>
+      <c r="M64" s="9" t="n"/>
+      <c r="N64" s="12" t="inlineStr">
+        <is>
+          <t>NATS[1세대, 2011.7 이전 생산]</t>
         </is>
       </c>
       <c r="O64" s="9" t="inlineStr">
@@ -4775,11 +4774,7 @@
           <t>wikipedia(2세대 2011.8 판매 개시), awesomemotors.kr(T002), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
-      <c r="P64" s="4" t="inlineStr">
-        <is>
-          <t>2세대(2011.8~) ID46 카드와 삼성 전용 AES 카드 병존 — 적용 구분 자료 없음</t>
-        </is>
-      </c>
+      <c r="P64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
@@ -4794,7 +4789,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -4814,7 +4809,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
+          <t>ID46(PCF7952)[2세대], ID4A(PCF7945M)[2세대, 카드키]</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -4822,32 +4817,32 @@
           <t>카드키</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="n"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>VA2</t>
+          <t>VA2[2세대]</t>
         </is>
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>285975779R[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="L65" s="9" t="inlineStr"/>
-      <c r="M65" s="9" t="inlineStr"/>
+          <t>285975779R[2세대, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>UCH</t>
+          <t>UCH[2세대, 2011.8 이후 생산]</t>
         </is>
       </c>
       <c r="O65" s="9" t="inlineStr">
         <is>
-          <t>carwiki.co.kr(올 뉴 SM7 2012년형), pechanara.com(올뉴 SM7 L47 스마트카드 리모컨+보조키 11~14년), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>wikipedia(2세대 2011.8 판매 개시), awesomemotors.kr(T002), kecool.com(ICC: 르노삼성 SM7 12자리 코드)</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
+          <t>2세대(2011.8~) ID46 카드와 삼성 전용 AES 카드 병존 — 적용 구분 자료 없음</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4859,7 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -4912,7 +4907,7 @@
       </c>
       <c r="O66" s="9" t="inlineStr">
         <is>
-          <t>carisyou.com(2013 뉴 SM7 L47), reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2 카드), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>carwiki.co.kr(올 뉴 SM7 2012년형), pechanara.com(올뉴 SM7 L47 스마트카드 리모컨+보조키 11~14년), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -4934,7 +4929,7 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -4982,7 +4977,7 @@
       </c>
       <c r="O67" s="9" t="inlineStr">
         <is>
-          <t>pechanara.com(L47 스마트카드 11~14), danawa(SM7 노바 2014.9.2 출시), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>carisyou.com(2013 뉴 SM7 L47), reidsremotes.com.au(래티튜드 2011-2015 ID46 Hitag2 카드), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -5004,7 +4999,7 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -5052,7 +5047,7 @@
       </c>
       <c r="O68" s="9" t="inlineStr">
         <is>
-          <t>danawa(SM7 노바 L47 제원), mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>pechanara.com(L47 스마트카드 11~14), danawa(SM7 노바 2014.9.2 출시), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -5074,7 +5069,7 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -5122,7 +5117,7 @@
       </c>
       <c r="O69" s="9" t="inlineStr">
         <is>
-          <t>encar.com(SM7 노바), reidsremotes.com.au(래티튜드 ~2015 ID46), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>danawa(SM7 노바 L47 제원), mr-key.com(래티튜드 2009-2015 285975779R PCF7952A), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -5144,7 +5139,7 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -5192,7 +5187,7 @@
       </c>
       <c r="O70" s="9" t="inlineStr">
         <is>
-          <t>danawa(SM7 노바), auto-keys.eu(르노삼성 4버튼 433MHz PCF7952A VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>encar.com(SM7 노바), reidsremotes.com.au(래티튜드 ~2015 ID46), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
@@ -5214,7 +5209,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -5262,7 +5257,7 @@
       </c>
       <c r="O71" s="9" t="inlineStr">
         <is>
-          <t>carisyou.com(2019 뉴 SM7 노바), auto-keys.eu(삼성 PCF7953 AES VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>danawa(SM7 노바), auto-keys.eu(르노삼성 4버튼 433MHz PCF7952A VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
@@ -5284,7 +5279,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -5332,7 +5327,7 @@
       </c>
       <c r="O72" s="9" t="inlineStr">
         <is>
-          <t>ko.wikipedia(SM7 노바 2014.9-2020.2 생산), carisyou.com(2019 SM7 노바), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+          <t>carisyou.com(2019 뉴 SM7 노바), auto-keys.eu(삼성 PCF7953 AES VA2 BCM 키), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
@@ -5349,17 +5344,17 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>QM3 (1세대)</t>
+          <t>SM7</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>2019(단종)</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -5372,9 +5367,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952), ID4A(PCF7945M)[카드키]</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
@@ -5390,22 +5385,26 @@
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+          <t>285975779R[해외 공용 품번]</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr"/>
       <c r="M73" s="9" t="inlineStr"/>
-      <c r="N73" s="9" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>UCH</t>
         </is>
       </c>
       <c r="O73" s="9" t="inlineStr">
         <is>
-          <t>keyfirst.eu(캡처1 키카드 2013-2020 285971998R), clien.net(QM3 스마트키 추가 구입 15만5천원), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
-        </is>
-      </c>
-      <c r="P73" s="9" t="inlineStr"/>
+          <t>ko.wikipedia(SM7 노바 2014.9-2020.2 생산), carisyou.com(2019 SM7 노바), [재조사] f-key.com·cnautokey.net(삼성 SM5·SM7 스마트키 434MHz AES PCF7945M), ivaylov.com(르노 키 장비: SM5 2009-2011 / 2011+ 구분), abrites(SM3·SM5 2011 이후 OBD PIN 읽기 RR007), mhhauto(SM7 L47은 AVDI만 지원)</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>ID46 카드와 삼성 전용 AES 카드 병존 — 적용 연식 구분 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -5420,7 +5419,7 @@
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -5468,7 +5467,7 @@
       </c>
       <c r="O74" s="9" t="inlineStr">
         <is>
-          <t>honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), autokeys.us(285971998R 클리오4·캡처), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+          <t>keyfirst.eu(캡처1 키카드 2013-2020 285971998R), clien.net(QM3 스마트키 추가 구입 15만5천원), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P74" s="9" t="inlineStr"/>
@@ -5486,7 +5485,7 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -5534,7 +5533,7 @@
       </c>
       <c r="O75" s="9" t="inlineStr">
         <is>
-          <t>tlkeys.com(285971998R 2012-2016 Hitag AES), imim.kr(QM3 스마트키 르노삼성), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+          <t>honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), autokeys.us(285971998R 클리오4·캡처), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P75" s="9" t="inlineStr"/>
@@ -5552,7 +5551,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -5600,7 +5599,7 @@
       </c>
       <c r="O76" s="9" t="inlineStr">
         <is>
-          <t>eurocarkeyshop.com(클리오·캡처 키리스 카드 285971998R), wikipedia(캡처 2017.5 페이스리프트), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+          <t>tlkeys.com(285971998R 2012-2016 Hitag AES), imim.kr(QM3 스마트키 르노삼성), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P76" s="9" t="inlineStr"/>
@@ -5618,7 +5617,7 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -5666,7 +5665,7 @@
       </c>
       <c r="O77" s="9" t="inlineStr">
         <is>
-          <t>keyfirst.eu(캡처1 2013-2020 VA2 433.92MHz 4A PCF7953M), accessfobs.co.uk(클리오·캡처 핸즈프리 카드 PCF7953), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+          <t>eurocarkeyshop.com(클리오·캡처 키리스 카드 285971998R), wikipedia(캡처 2017.5 페이스리프트), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P77" s="9" t="inlineStr"/>
@@ -5684,7 +5683,7 @@
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -5732,7 +5731,7 @@
       </c>
       <c r="O78" s="9" t="inlineStr">
         <is>
-          <t>keyfirst.eu(캡처1 ~2020), auto-keys.eu(클리오4/삼성 PCF7953 VA2 BCM 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+          <t>keyfirst.eu(캡처1 2013-2020 VA2 433.92MHz 4A PCF7953M), accessfobs.co.uk(클리오·캡처 핸즈프리 카드 PCF7953), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P78" s="9" t="inlineStr"/>
@@ -5745,12 +5744,12 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>캡처 (QM3 후속 수입)</t>
+          <t>QM3 (1세대)</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019(단종)</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -5770,7 +5769,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)</t>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -5781,12 +5780,12 @@
       <c r="I79" s="9" t="inlineStr"/>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>VA2, VA6[일부 자료]</t>
+          <t>VA2</t>
         </is>
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>285979827R, 285973979R</t>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr"/>
@@ -5798,7 +5797,7 @@
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>etoday.co.kr/daum(르노 캡처 2020.5.13 국내 출시, QM3 후속), keyfirst.eu(캡처2 2019-2022 호환 키카드)</t>
+          <t>keyfirst.eu(캡처1 ~2020), auto-keys.eu(클리오4/삼성 PCF7953 VA2 BCM 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P79" s="9" t="inlineStr"/>
@@ -5816,7 +5815,7 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -5864,7 +5863,7 @@
       </c>
       <c r="O80" s="9" t="inlineStr">
         <is>
-          <t>keystation.co.uk(캡처·클리오·아르카나 2016-2021 NCF29A1M Hitag AES 4A, CIT-1/VA2/VA6), car-keys-online.com(클리오5/캡처2/아르카나 285979827R)</t>
+          <t>etoday.co.kr/daum(르노 캡처 2020.5.13 국내 출시, QM3 후속), keyfirst.eu(캡처2 2019-2022 호환 키카드)</t>
         </is>
       </c>
       <c r="P80" s="9" t="inlineStr"/>
@@ -5882,7 +5881,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -5930,7 +5929,7 @@
       </c>
       <c r="O81" s="9" t="inlineStr">
         <is>
-          <t>keystation.co.uk(캡처 2019-2024 ID4A 285979827R), namu.wiki(캡처 2세대 국내 판매)</t>
+          <t>keystation.co.uk(캡처·클리오·아르카나 2016-2021 NCF29A1M Hitag AES 4A, CIT-1/VA2/VA6), car-keys-online.com(클리오5/캡처2/아르카나 285979827R)</t>
         </is>
       </c>
       <c r="P81" s="9" t="inlineStr"/>
@@ -5948,7 +5947,7 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>2023(단종)</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -5996,7 +5995,7 @@
       </c>
       <c r="O82" s="9" t="inlineStr">
         <is>
-          <t>keyfirst.eu(캡처2 2019-2023 카드), car-keys-online.com(285979827R 신형 H-24985)</t>
+          <t>keystation.co.uk(캡처 2019-2024 ID4A 285979827R), namu.wiki(캡처 2세대 국내 판매)</t>
         </is>
       </c>
       <c r="P82" s="9" t="inlineStr"/>
@@ -6009,22 +6008,22 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>QM5</t>
+          <t>캡처 (QM3 후속 수입)</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023(단종)</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -6034,7 +6033,7 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7952A)[키리스], ID46(PCF7941A)[비키리스]</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
@@ -6045,24 +6044,24 @@
       <c r="I83" s="9" t="inlineStr"/>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
+          <t>VA2, VA6[일부 자료]</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
+          <t>285979827R, 285973979R</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr"/>
       <c r="M83" s="9" t="inlineStr"/>
       <c r="N83" s="9" t="inlineStr">
         <is>
-          <t>BCM[NATS 계열]</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O83" s="9" t="inlineStr">
         <is>
-          <t>wikipedia(QM5 2007.11.19 생산·2007.12.10 판매 개시), autokeys.us(콜레오스 NSN14 스마트키 = 삼성 QM5, PCF7952A 433.92MHz), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
+          <t>keyfirst.eu(캡처2 2019-2023 카드), car-keys-online.com(285979827R 신형 H-24985)</t>
         </is>
       </c>
       <c r="P83" s="9" t="inlineStr"/>
@@ -6080,7 +6079,7 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -6128,7 +6127,7 @@
       </c>
       <c r="O84" s="9" t="inlineStr">
         <is>
-          <t>amazon.co.uk(콜레오스 2008-2011 4버튼 카드 PCF7952), namu.wiki(인텔리전트 스마트카드 기본 적용), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
+          <t>wikipedia(QM5 2007.11.19 생산·2007.12.10 판매 개시), autokeys.us(콜레오스 NSN14 스마트키 = 삼성 QM5, PCF7952A 433.92MHz), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
       <c r="P84" s="9" t="inlineStr"/>
@@ -6146,7 +6145,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -6194,7 +6193,7 @@
       </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>car-keys-online.com(콜레오스 H45 2007-2015 Hitag2 PCF7952/PCF7941, 285970036R), ebay.co.uk(285970036R), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
+          <t>amazon.co.uk(콜레오스 2008-2011 4버튼 카드 PCF7952), namu.wiki(인텔리전트 스마트카드 기본 적용), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
       <c r="P85" s="9" t="inlineStr"/>
@@ -6212,7 +6211,7 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -6260,7 +6259,7 @@
       </c>
       <c r="O86" s="9" t="inlineStr">
         <is>
-          <t>amazon.es(콜레오스 2008-2011 PCF7952), wikipedia(2011.6 뉴 QM5 페이스리프트), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
+          <t>car-keys-online.com(콜레오스 H45 2007-2015 Hitag2 PCF7952/PCF7941, 285970036R), ebay.co.uk(285970036R), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
         </is>
       </c>
       <c r="P86" s="9" t="inlineStr"/>
@@ -6278,17 +6277,17 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -6296,9 +6295,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A), ID46(PCF7941A), ID4A(PCF7953)[후기형, 추정]</t>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952A)[키리스], ID46(PCF7941A)[비키리스]</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
@@ -6319,21 +6318,17 @@
       </c>
       <c r="L87" s="9" t="inlineStr"/>
       <c r="M87" s="9" t="inlineStr"/>
-      <c r="N87" s="4" t="inlineStr">
+      <c r="N87" s="9" t="inlineStr">
         <is>
           <t>BCM[NATS 계열]</t>
         </is>
       </c>
       <c r="O87" s="9" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(콜레오스 2008-2016 ID46 NSN14 비상키), smautomall(QM5/뉴QM5 스마트카드 인텔리전트 적용모델), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
-        </is>
-      </c>
-      <c r="P87" s="4" t="inlineStr">
-        <is>
-          <t>Hitag2·AES 카드 두 종류 판매 — AES 전환 연식 자료 없음</t>
-        </is>
-      </c>
+          <t>amazon.es(콜레오스 2008-2011 PCF7952), wikipedia(2011.6 뉴 QM5 페이스리프트), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A)</t>
+        </is>
+      </c>
+      <c r="P87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
@@ -6348,7 +6343,7 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -6396,7 +6391,7 @@
       </c>
       <c r="O88" s="9" t="inlineStr">
         <is>
-          <t>remotesnkeys.com(콜레오스 2008-2016 ID46 433MHz), wikipedia(2013.4 2014년형 2.0 가솔린), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
+          <t>reidsremotes.com.au(콜레오스 2008-2016 ID46 NSN14 비상키), smautomall(QM5/뉴QM5 스마트카드 인텔리전트 적용모델), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
@@ -6418,7 +6413,7 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -6466,7 +6461,7 @@
       </c>
       <c r="O89" s="9" t="inlineStr">
         <is>
-          <t>carisyou.com(2014 QM5 네오), wikipedia(2014.1.20 QM5 네오 출시), ebay(콜레오스 2009-2016 PCF7952), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
+          <t>remotesnkeys.com(콜레오스 2008-2016 ID46 433MHz), wikipedia(2013.4 2014년형 2.0 가솔린), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -6488,7 +6483,7 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -6536,7 +6531,7 @@
       </c>
       <c r="O90" s="9" t="inlineStr">
         <is>
-          <t>carisyou.com(2015 QM5 네오), reidsremotes.com.au(콜레오스 2008-2016 ID46), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
+          <t>carisyou.com(2014 QM5 네오), wikipedia(2014.1.20 QM5 네오 출시), ebay(콜레오스 2009-2016 PCF7952), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -6558,7 +6553,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>2016(단종)</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -6606,7 +6601,7 @@
       </c>
       <c r="O91" s="9" t="inlineStr">
         <is>
-          <t>danawa(QM5 네오 2014.01-2016.09), remotesnkeys.com(콜레오스 2008-2016 ID46 PCF7952A), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
+          <t>carisyou.com(2015 QM5 네오), reidsremotes.com.au(콜레오스 2008-2016 ID46), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
@@ -6623,17 +6618,17 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>QM6</t>
+          <t>QM5</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>2016(단종)</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -6646,9 +6641,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952A), ID46(PCF7941A), ID4A(PCF7953)[후기형, 추정]</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
@@ -6659,27 +6654,31 @@
       <c r="I92" s="9" t="inlineStr"/>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>VA2</t>
+          <t>NSN14[차량별 상이], VA2[차량별 상이]</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr">
         <is>
-          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+          <t>285979045R[핸즈프리], 285970036R[비핸즈프리]</t>
         </is>
       </c>
       <c r="L92" s="9" t="inlineStr"/>
       <c r="M92" s="9" t="inlineStr"/>
-      <c r="N92" s="9" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>BCM[NATS 계열]</t>
         </is>
       </c>
       <c r="O92" s="9" t="inlineStr">
         <is>
-          <t>wikipedia(QM6 2016.9 출시 = 콜레오스 2세대), keystation.co.uk(콜레오스 2016-2021 NCF29A1M Hitag AES 4A)</t>
-        </is>
-      </c>
-      <c r="P92" s="9" t="inlineStr"/>
+          <t>danawa(QM5 네오 2014.01-2016.09), remotesnkeys.com(콜레오스 2008-2016 ID46 PCF7952A), nissantechnicianinfo(닛산 인텔리전트키-BCM/NATS), autokeys.us(VA2·NSN14 두 종류 콜레오스/QM5 스마트키 PCF7952A), gskeyae.com(콜레오스·삼성 QM5 285979045R), [재조사] mk3.com(삼성 QM5 순정 카드 4버튼 433MHz PCF7941A / 콜레오스·QM5 키리스 PCF7952A), auto-keys.eu(삼성 QM5 순정 AES PCF7953 VA2 BCM), accio(콜레오스 2014-2016 PCF7953M 4A 자료)</t>
+        </is>
+      </c>
+      <c r="P92" s="4" t="inlineStr">
+        <is>
+          <t>Hitag2·AES 카드 두 종류 판매 — AES 전환 연식 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
@@ -6694,7 +6693,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -6742,7 +6741,7 @@
       </c>
       <c r="O93" s="9" t="inlineStr">
         <is>
-          <t>norman-keys.com(2017 콜레오스 OEM 카드 433MHz 4A), carkeyshop.co.uk(콜레오스·메간4·탈리스만 카드 PCF7953M)</t>
+          <t>wikipedia(QM6 2016.9 출시 = 콜레오스 2세대), keystation.co.uk(콜레오스 2016-2021 NCF29A1M Hitag AES 4A)</t>
         </is>
       </c>
       <c r="P93" s="9" t="inlineStr"/>
@@ -6760,7 +6759,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -6808,7 +6807,7 @@
       </c>
       <c r="O94" s="9" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2017-2023 메간4·탈리스만·콜레오스 ID4A VA2 285977147R), pechanara.com(QM6 스마트카드)</t>
+          <t>norman-keys.com(2017 콜레오스 OEM 카드 433MHz 4A), carkeyshop.co.uk(콜레오스·메간4·탈리스만 카드 PCF7953M)</t>
         </is>
       </c>
       <c r="P94" s="9" t="inlineStr"/>
@@ -6826,7 +6825,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -6874,7 +6873,7 @@
       </c>
       <c r="O95" s="9" t="inlineStr">
         <is>
-          <t>autokeystore.com(메간4·콜레오스2 핸즈프리 카드 KR5IK4CH-01 NCF29A1M), dalkomhae.com(QM6 스마트키)</t>
+          <t>keyshop-online.com(2017-2023 메간4·탈리스만·콜레오스 ID4A VA2 285977147R), pechanara.com(QM6 스마트카드)</t>
         </is>
       </c>
       <c r="P95" s="9" t="inlineStr"/>
@@ -6892,7 +6891,7 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -6940,7 +6939,7 @@
       </c>
       <c r="O96" s="9" t="inlineStr">
         <is>
-          <t>keystation.co.uk(콜레오스 2016-2021 NCF29A1M), carkeymaster.kr(QM6 스마트키 분실)</t>
+          <t>autokeystore.com(메간4·콜레오스2 핸즈프리 카드 KR5IK4CH-01 NCF29A1M), dalkomhae.com(QM6 스마트키)</t>
         </is>
       </c>
       <c r="P96" s="9" t="inlineStr"/>
@@ -6958,7 +6957,7 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -7006,7 +7005,7 @@
       </c>
       <c r="O97" s="9" t="inlineStr">
         <is>
-          <t>keystation.co.uk(콜레오스 ~2021 4A), keyshop-online.com(2017-2023 ID4A)</t>
+          <t>keystation.co.uk(콜레오스 2016-2021 NCF29A1M), carkeymaster.kr(QM6 스마트키 분실)</t>
         </is>
       </c>
       <c r="P97" s="9" t="inlineStr"/>
@@ -7024,7 +7023,7 @@
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -7072,7 +7071,7 @@
       </c>
       <c r="O98" s="9" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2017-2023 콜레오스 ID4A 285977147R), teamblind.com(QM6 스마트키 분실)</t>
+          <t>keystation.co.uk(콜레오스 ~2021 4A), keyshop-online.com(2017-2023 ID4A)</t>
         </is>
       </c>
       <c r="P98" s="9" t="inlineStr"/>
@@ -7090,7 +7089,7 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -7138,7 +7137,7 @@
       </c>
       <c r="O99" s="9" t="inlineStr">
         <is>
-          <t>keyshop-online.com(~2023 ID4A), autokeystore.com(콜레오스2 NCF29A1M), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
+          <t>keyshop-online.com(2017-2023 콜레오스 ID4A 285977147R), teamblind.com(QM6 스마트키 분실)</t>
         </is>
       </c>
       <c r="P99" s="9" t="inlineStr"/>
@@ -7156,7 +7155,7 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -7204,7 +7203,7 @@
       </c>
       <c r="O100" s="9" t="inlineStr">
         <is>
-          <t>gpkorea.com(QM6 판매 지속, 2025 단종), keyshop-online.com(ID4A VA2), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
+          <t>keyshop-online.com(~2023 ID4A), autokeystore.com(콜레오스2 NCF29A1M), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
       <c r="P100" s="9" t="inlineStr"/>
@@ -7222,7 +7221,7 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -7240,7 +7239,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="G101" s="9" t="inlineStr">
         <is>
           <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
         </is>
@@ -7263,21 +7262,17 @@
       </c>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="4" t="inlineStr">
+      <c r="N101" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="O101" s="9" t="inlineStr">
         <is>
-          <t>dailycar.co.kr/gpkorea.com(SM6·QM6 2025.12 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr">
-        <is>
-          <t>순정 카드 자료가 2024년식까지 — 동일 카드로 추정</t>
-        </is>
-      </c>
+          <t>gpkorea.com(QM6 판매 지속, 2025 단종), keyshop-online.com(ID4A VA2), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
+        </is>
+      </c>
+      <c r="P101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
@@ -7287,12 +7282,12 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>그랑 콜레오스</t>
+          <t>QM6</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -7312,36 +7307,40 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>ID4A, ID8A</t>
+          <t>ID4A(PCF7953M), ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>카드키</t>
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>HU100[지리 스마트키 기준]</t>
-        </is>
-      </c>
-      <c r="K102" s="9" t="inlineStr"/>
-      <c r="L102" s="9" t="n"/>
+          <t>VA2</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>285977147R[해외 공용 품번], FCC KR5IK4CH-01</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="inlineStr"/>
       <c r="M102" s="9" t="inlineStr"/>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O102" s="9" t="inlineStr">
         <is>
-          <t>wikipedia(그랑 콜레오스 2024 국내 생산, 지리 싱웨L 기반 CMA 플랫폼), keyshop-online.com(지리 OEM 스마트키 ID4A HU100 433MHz), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
+          <t>dailycar.co.kr/gpkorea.com(SM6·QM6 2025.12 동시 단종), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz)</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>전용 자료 없음 — 원형 지리 몬자로 키가 ID4A·ID8A 두 종류</t>
+          <t>순정 카드 자료가 2024년식까지 — 동일 카드로 추정</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7357,7 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -7402,7 +7401,7 @@
       </c>
       <c r="O103" s="9" t="inlineStr">
         <is>
-          <t>carisyou.com(2025 그랑 콜레오스 하이브리드), tlkeys.com(지리 순정 스마트키), keyshop-online.com(지리 ID4A), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
+          <t>wikipedia(그랑 콜레오스 2024 국내 생산, 지리 싱웨L 기반 CMA 플랫폼), keyshop-online.com(지리 OEM 스마트키 ID4A HU100 433MHz), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
@@ -7424,7 +7423,7 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -7468,7 +7467,7 @@
       </c>
       <c r="O104" s="9" t="inlineStr">
         <is>
-          <t>renault.co.kr(그랑 콜레오스 판매 중), wikipedia(싱웨L/몬자로), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
+          <t>carisyou.com(2025 그랑 콜레오스 하이브리드), tlkeys.com(지리 순정 스마트키), keyshop-online.com(지리 ID4A), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
@@ -7485,12 +7484,12 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>XM3</t>
+          <t>그랑 콜레오스</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -7508,40 +7507,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>ID4A(NCF29A1M)</t>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>ID4A, ID8A</t>
         </is>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>카드키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I105" s="9" t="inlineStr"/>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>VA2, VA6[일부 자료]</t>
-        </is>
-      </c>
-      <c r="K105" s="9" t="inlineStr">
-        <is>
-          <t>285979827R[해외 공용 품번], 285973979R[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="L105" s="9" t="inlineStr"/>
+          <t>HU100[지리 스마트키 기준]</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr"/>
+      <c r="L105" s="9" t="n"/>
       <c r="M105" s="9" t="inlineStr"/>
-      <c r="N105" s="9" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="O105" s="9" t="inlineStr">
         <is>
-          <t>wikipedia(XM3 2020.3 출시, 부산 생산 LJL), smautomall(XM3 스마트카드 리모컨+비상키, VIN별 상이), teamblind.com(2020.10식 XM3 스마트키)</t>
-        </is>
-      </c>
-      <c r="P105" s="9" t="inlineStr"/>
+          <t>renault.co.kr(그랑 콜레오스 판매 중), wikipedia(싱웨L/몬자로), [재조사] autokeymaster.ru(지리 몬자로 2022-2024 순정 스마트키 HITAG AES 434MHz / DST AES 8A 두 종류), huloda.com(2023 몬자로 순정 8A 433MHz), keyshop-online.com(지리 스마트키 HU100)</t>
+        </is>
+      </c>
+      <c r="P105" s="4" t="inlineStr">
+        <is>
+          <t>전용 자료 없음 — 원형 지리 몬자로 키가 ID4A·ID8A 두 종류</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
@@ -7556,7 +7555,7 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -7604,7 +7603,7 @@
       </c>
       <c r="O106" s="9" t="inlineStr">
         <is>
-          <t>car-keys-online.com(아르카나 2021-2023 285979827R), keystation.co.uk(아르카나·캡처·클리오 NCF29A1M 4A)</t>
+          <t>wikipedia(XM3 2020.3 출시, 부산 생산 LJL), smautomall(XM3 스마트카드 리모컨+비상키, VIN별 상이), teamblind.com(2020.10식 XM3 스마트키)</t>
         </is>
       </c>
       <c r="P106" s="9" t="inlineStr"/>
@@ -7622,7 +7621,7 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -7670,7 +7669,7 @@
       </c>
       <c r="O107" s="9" t="inlineStr">
         <is>
-          <t>keystation.co.uk(아르카나 ID4A CIT-1/VA2/VA6), danawa(XM3 LJL)</t>
+          <t>car-keys-online.com(아르카나 2021-2023 285979827R), keystation.co.uk(아르카나·캡처·클리오 NCF29A1M 4A)</t>
         </is>
       </c>
       <c r="P107" s="9" t="inlineStr"/>
@@ -7688,7 +7687,7 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -7736,7 +7735,7 @@
       </c>
       <c r="O108" s="9" t="inlineStr">
         <is>
-          <t>car-keys-online.com(OEM 키카드 클리오5/아르카나/캡처2 신형 H-24985 285979827R), carinfoyou.com(2024 XM3)</t>
+          <t>keystation.co.uk(아르카나 ID4A CIT-1/VA2/VA6), danawa(XM3 LJL)</t>
         </is>
       </c>
       <c r="P108" s="9" t="inlineStr"/>
@@ -7754,7 +7753,7 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -7802,7 +7801,7 @@
       </c>
       <c r="O109" s="9" t="inlineStr">
         <is>
-          <t>ko.wikipedia(2024.4.3 국내명 르노 아르카나로 통일), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
+          <t>car-keys-online.com(OEM 키카드 클리오5/아르카나/캡처2 신형 H-24985 285979827R), carinfoyou.com(2024 XM3)</t>
         </is>
       </c>
       <c r="P109" s="9" t="inlineStr"/>
@@ -7815,12 +7814,12 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>아르카나 (XM3 국내 리네이밍)</t>
+          <t>XM3</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -7838,7 +7837,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr">
+      <c r="G110" s="9" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M)</t>
         </is>
@@ -7856,26 +7855,22 @@
       </c>
       <c r="K110" s="9" t="inlineStr">
         <is>
-          <t>285979827R[구형 로고]</t>
+          <t>285979827R[해외 공용 품번], 285973979R[해외 공용 품번]</t>
         </is>
       </c>
       <c r="L110" s="9" t="inlineStr"/>
       <c r="M110" s="9" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="N110" s="9" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="O110" s="9" t="inlineStr">
         <is>
-          <t>ko.wikipedia(2024.4.3 르노 아르카나 차명 통일), renault.co.kr(아르카나 버튼시동 스마트카드 기본), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
-        </is>
-      </c>
-      <c r="P110" s="4" t="inlineStr">
-        <is>
-          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
-        </is>
-      </c>
+          <t>ko.wikipedia(2024.4.3 국내명 르노 아르카나로 통일), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
+        </is>
+      </c>
+      <c r="P110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
@@ -7890,7 +7885,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -7938,7 +7933,7 @@
       </c>
       <c r="O111" s="9" t="inlineStr">
         <is>
-          <t>ko.wikipedia(1.3 터보 2025.4 생산 중지), keytectools.com(르노 Hitag AES ID4A 2018-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
+          <t>ko.wikipedia(2024.4.3 르노 아르카나 차명 통일), renault.co.kr(아르카나 버튼시동 스마트카드 기본), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -7960,7 +7955,7 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -8008,7 +8003,7 @@
       </c>
       <c r="O112" s="9" t="inlineStr">
         <is>
-          <t>renault.co.kr(아르카나 판매 중), keytectools.com(르노 ID4A ~2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
+          <t>ko.wikipedia(1.3 터보 2025.4 생산 중지), keytectools.com(르노 Hitag AES ID4A 2018-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -8025,12 +8020,12 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>조에 (Zoe)</t>
+          <t>아르카나 (XM3 국내 리네이밍)</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -8048,7 +8043,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G113" s="9" t="inlineStr">
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M)</t>
         </is>
@@ -8061,27 +8056,31 @@
       <c r="I113" s="9" t="inlineStr"/>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>VA2</t>
+          <t>VA2, VA6[일부 자료]</t>
         </is>
       </c>
       <c r="K113" s="9" t="inlineStr">
         <is>
-          <t>285979827R</t>
+          <t>285979827R[구형 로고]</t>
         </is>
       </c>
       <c r="L113" s="9" t="inlineStr"/>
       <c r="M113" s="9" t="inlineStr"/>
-      <c r="N113" s="9" t="inlineStr">
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="O113" s="9" t="inlineStr">
         <is>
-          <t>ko.wikipedia/motoya.co.kr(조에 2020.8.18 국내 출시), car-keys-online.com(클리오·캡처·조에 순정 키카드 285979827R)</t>
-        </is>
-      </c>
-      <c r="P113" s="9" t="inlineStr"/>
+          <t>renault.co.kr(아르카나 판매 중), keytectools.com(르노 ID4A ~2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
+        </is>
+      </c>
+      <c r="P113" s="4" t="inlineStr">
+        <is>
+          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
@@ -8096,7 +8095,7 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -8144,7 +8143,7 @@
       </c>
       <c r="O114" s="9" t="inlineStr">
         <is>
-          <t>economist.co.kr(2021년형 재고 소진), keystation.co.uk(르노 2016-2021 NCF29A1M Hitag AES 4A)</t>
+          <t>ko.wikipedia/motoya.co.kr(조에 2020.8.18 국내 출시), car-keys-online.com(클리오·캡처·조에 순정 키카드 285979827R)</t>
         </is>
       </c>
       <c r="P114" s="9" t="inlineStr"/>
@@ -8162,7 +8161,7 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -8210,7 +8209,7 @@
       </c>
       <c r="O115" s="9" t="inlineStr">
         <is>
-          <t>economist.co.kr(2022 판매 중단·단종 수순), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
+          <t>economist.co.kr(2021년형 재고 소진), keystation.co.uk(르노 2016-2021 NCF29A1M Hitag AES 4A)</t>
         </is>
       </c>
       <c r="P115" s="9" t="inlineStr"/>
@@ -8223,12 +8222,12 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>클리오 (Clio)</t>
+          <t>조에 (Zoe)</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022(단종)</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -8248,7 +8247,7 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H116" s="9" t="inlineStr">
@@ -8264,7 +8263,7 @@
       </c>
       <c r="K116" s="9" t="inlineStr">
         <is>
-          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+          <t>285979827R</t>
         </is>
       </c>
       <c r="L116" s="9" t="inlineStr"/>
@@ -8276,7 +8275,7 @@
       </c>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>hankookilbo.com(르노 클리오 2018.5 국내 출시), honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+          <t>economist.co.kr(2022 판매 중단·단종 수순), keytectools.com(르노 Hitag AES ID4A 2018-2025)</t>
         </is>
       </c>
       <c r="P116" s="9" t="inlineStr"/>
@@ -8294,7 +8293,7 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -8342,7 +8341,7 @@
       </c>
       <c r="O117" s="9" t="inlineStr">
         <is>
-          <t>ko.wikipedia(클리오 4세대 국내 2018.5~2019말 판매, 5세대 미출시), keyfirst.eu(클리오4 2012-2019 285971998R VA2), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
+          <t>hankookilbo.com(르노 클리오 2018.5 국내 출시), honrow.com(클리오4·캡처 2013-2017 PCF7953M Hitag AES 4A 285971998R), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P117" s="9" t="inlineStr"/>
@@ -8355,22 +8354,22 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>마스터 (LCV)</t>
+          <t>클리오 (Clio)</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2019(단종)</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -8380,35 +8379,35 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7947)</t>
+          <t>ID4A(PCF7953M)[핸즈프리], ID4A(PCF7945M)[핸즈프리], ID4A(PCF7961M)[비핸즈프리]</t>
         </is>
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>카드키</t>
         </is>
       </c>
       <c r="I118" s="9" t="inlineStr"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>VA6</t>
-        </is>
-      </c>
-      <c r="K118" s="9" t="inlineStr"/>
+          <t>VA2</t>
+        </is>
+      </c>
+      <c r="K118" s="9" t="inlineStr">
+        <is>
+          <t>285971998R[핸즈프리], 285974100R[비핸즈프리]</t>
+        </is>
+      </c>
       <c r="L118" s="9" t="inlineStr"/>
-      <c r="M118" s="9" t="inlineStr">
-        <is>
-          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="M118" s="9" t="inlineStr"/>
       <c r="N118" s="9" t="inlineStr">
         <is>
-          <t>UCH</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O118" s="9" t="inlineStr">
         <is>
-          <t>namu.wiki(마스터 밴 2018.10.15 공개·국내 출시), autoecupart.net(PCF7961M 4A 433MHz 3버튼 — 마스터3 등), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+          <t>ko.wikipedia(클리오 4세대 국내 2018.5~2019말 판매, 5세대 미출시), keyfirst.eu(클리오4 2012-2019 285971998R VA2), key-code.com(클리오4·캡처 285971998R PCF7945M/PCF7953M ID4A), car-keys-online.com(285974100R 비핸즈프리)</t>
         </is>
       </c>
       <c r="P118" s="9" t="inlineStr"/>
@@ -8426,7 +8425,7 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -8474,7 +8473,7 @@
       </c>
       <c r="O119" s="9" t="inlineStr">
         <is>
-          <t>cvinfo.com/automorning.com(마스터 버스 2019.6.3 출시, 무선 리모컨키), onlyda.com(르노 순정 3버튼 PCF7961M Hitag AES 4A 434MHz), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+          <t>namu.wiki(마스터 밴 2018.10.15 공개·국내 출시), autoecupart.net(PCF7961M 4A 433MHz 3버튼 — 마스터3 등), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
       <c r="P119" s="9" t="inlineStr"/>
@@ -8492,7 +8491,7 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -8540,7 +8539,7 @@
       </c>
       <c r="O120" s="9" t="inlineStr">
         <is>
-          <t>carisyou.com(부분변경 르노 마스터 밴·버스 출시), onlyda.com(르노·다치아 PCF7961M 4A VA2), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+          <t>cvinfo.com/automorning.com(마스터 버스 2019.6.3 출시, 무선 리모컨키), onlyda.com(르노 순정 3버튼 PCF7961M Hitag AES 4A 434MHz), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
       <c r="P120" s="9" t="inlineStr"/>
@@ -8558,7 +8557,7 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -8576,7 +8575,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G121" s="4" t="inlineStr">
+      <c r="G121" s="9" t="inlineStr">
         <is>
           <t>ID46(PCF7947)</t>
         </is>
@@ -8599,21 +8598,17 @@
           <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr">
+      <c r="N121" s="9" t="inlineStr">
         <is>
           <t>UCH</t>
         </is>
       </c>
       <c r="O121" s="9" t="inlineStr">
         <is>
-          <t>carnoon.co.kr(뉴 마스터 가격·제원), cndiykey.com(르노 3버튼 PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
-        </is>
-      </c>
-      <c r="P121" s="4" t="inlineStr">
-        <is>
-          <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
-        </is>
-      </c>
+          <t>carisyou.com(부분변경 르노 마스터 밴·버스 출시), onlyda.com(르노·다치아 PCF7961M 4A VA2), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="P121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
@@ -8628,7 +8623,7 @@
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -8676,7 +8671,7 @@
       </c>
       <c r="O122" s="9" t="inlineStr">
         <is>
-          <t>namu.wiki(마스터 버스 2022년형 끝으로 단종), autoecupart.net(PCF7961M 4A 마스터3), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+          <t>carnoon.co.kr(뉴 마스터 가격·제원), cndiykey.com(르노 3버튼 PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
@@ -8698,7 +8693,7 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -8746,7 +8741,7 @@
       </c>
       <c r="O123" s="9" t="inlineStr">
         <is>
-          <t>namu.wiki(2023 수입 불안정 68대 판매), onlyda.com(PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+          <t>namu.wiki(마스터 버스 2022년형 끝으로 단종), autoecupart.net(PCF7961M 4A 마스터3), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -8768,7 +8763,7 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -8816,7 +8811,7 @@
       </c>
       <c r="O124" s="9" t="inlineStr">
         <is>
-          <t>carnoon.co.kr(뉴 마스터 2024년형 2.3 밴), motormag.co.kr(2024.5.13 700대 특별 판매), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+          <t>namu.wiki(2023 수입 불안정 68대 판매), onlyda.com(PCF7961M 4A), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -8838,7 +8833,7 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -8886,10 +8881,80 @@
       </c>
       <c r="O125" s="9" t="inlineStr">
         <is>
+          <t>carnoon.co.kr(뉴 마스터 2024년형 2.3 밴), motormag.co.kr(2024.5.13 700대 특별 판매), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
+        </is>
+      </c>
+      <c r="P125" s="4" t="inlineStr">
+        <is>
+          <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>르노(르노삼성)</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>마스터 (LCV)</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>2025(단종)</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>ID46(PCF7947)</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr"/>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>VA6</t>
+        </is>
+      </c>
+      <c r="K126" s="9" t="inlineStr"/>
+      <c r="L126" s="9" t="inlineStr"/>
+      <c r="M126" s="9" t="inlineStr">
+        <is>
+          <t>7701209236[해외 공용 품번], 998102668R[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>UCH</t>
+        </is>
+      </c>
+      <c r="O126" s="9" t="inlineStr">
+        <is>
           <t>namu.wiki(700대 한정 2025.9까지 판매), moter.kr(신형 마스터 4세대), [재조사] reidsremotes.com.au(캉구 X61·마스터 X62 2011-2019 3버튼 ID46 PCF7947 VA6), carkeyssolutions.co.uk(마스터 2010-2020 리모컨), eurocarkeyshop(3버튼 ID46 PCF7947 7701209236/998102668R), abrites.com(RR021 마스터3·캉구2 2016+ OBD 키 등록), mhhauto(마스터 UCH에서 PIN 읽기), autoecupart.net(마스터3 PCF7961M 4A 3버튼)</t>
         </is>
       </c>
-      <c r="P125" s="4" t="inlineStr">
+      <c r="P126" s="4" t="inlineStr">
         <is>
           <t>PCF7947(ID46) 리모컨 외 Master3용 PCF7961M(ID4A) 리모컨도 판매 — 후기형 칩 상충</t>
         </is>
@@ -8907,7 +8972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -9208,6 +9273,23 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>- 세대가 바뀌는 해는 세대별로 행을 나눔(구세대 1행 + 신세대 1행). 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 한 행에 전·후 값을 함께 적음</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +158,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -8972,302 +8975,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(SM5 1세대 1998년 출시분도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 마스터 밴 2018~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 르노 계열은 UCH(메간3/플루언스/래티튜드 세대) → BCM(클리오4·캡처 이후 Hitag AES 세대), 닛산 기반 구형 삼성 차종은 NATS(르노삼성 12자리 코드)로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>- 카드형 스마트키(르노 카드)는 '카드키(부품번호)' 칸에 적었습니다. 부품번호는 동일 플랫폼 르노 차종의 순정 번호(285975779R, 285977147R 등)이며 국내 순정 품번은 대부분 확인되지 않았습니다 — 르노코리아 부품은 VIN(KNMA…)별로 상이.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색에서 직접 나온 경우에만 적었고 나머지는 공란입니다(기아 파일 규칙). 키웨이는 카드 비상키 블레이드 기준(VA2/NSN14 등)입니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49·ID8A → X/△/O, 구형(ID46)·신형(AES) 칩이 병기된 행 → △/△/O(기아 파일 혼재 행 규칙). 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 원문 페이지를 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr"/>
+      <c r="A15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr"/>
+      <c r="A18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>- [재조사] SM3 CF는 르노삼성이 생산한 닛산 알메라 클래식(러시아)·써니(중동)와 같은 차라 ID46 PCF7936·NSN14로 확인했습니다. SM3 1세대는 같은 차체라 동일 가능성이 높으나 직접 자료는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>- SM5 1·2세대, SM7 1세대는 한국어·러시아·중남미·중동 자료를 다시 찾았지만 칩을 밝힌 자료가 없어 닛산 기준 추정(주황)으로 남겼습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>- [재조사] SM5 3세대·SM7 2세대는 래티튜드용 ID46 카드와 삼성 전용 AES(PCF7945M, 434MHz) 카드가 함께 판매되어 두 칩을 병기했습니다(주황). 285975779R 카드도 후기 순정품에 PCF7953M(4A) 사양이 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>- [재조사] 마스터3는 ID46 PCF7947, 블레이드 VA6 리모컨키입니다(이전 초안의 ID4A 추정은 오류). 그랑 콜레오스는 지리 몬자로 순정 키(Hitag AES 4A / DST AES 8A) 기준입니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>- SM5 2세대·SM7 1세대 카드형 스마트키: 0156 타입(2005~2007)과 T002 타입(2008~, 뉴아트·임프레션)은 서로 호환되지 않습니다. FCC TFWB1J637(312.4MHz).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>- SM3 2세대(플루언스), SM5 3세대·SM7 2세대(래티튜드): ID46 PCF7952 카드 285975779R, VA2, UCH. 2011년경부터 UCH 소프트웨어 변경으로 OBD 등록 제한 자료 있음.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>- QM5(콜레오스 H45): ID46 PCF7952 카드 285979045R(핸즈프리)/285970036R(비핸즈프리), 비상키 NSN14 또는 VA2 두 종류. QM5용 AES(PCF7953) 카드도 존재(적용 연식 미확인).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>- QM3·클리오4: 285971998R(핸즈프리 PCF7953M 4A) / 285974100R(비핸즈프리). SM6·QM6: 285977147R(PCF7953M/NCF29A1M 4A). 캡처2·조에·XM3·아르카나: 285979827R/285973979R(NCF29A1M 4A).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>- 그랑 콜레오스는 지리 싱웨L(몬자로) 기반으로, 키 칩 자료가 없어 지리 자료 기준 추정입니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
+      <c r="A29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
+      <c r="A37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
@@ -9284,9 +9287,26 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>- 세대가 바뀌는 해는 세대별로 행을 나눔(구세대 1행 + 신세대 1행). 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 한 행에 전·후 값을 함께 적음</t>
+      <c r="A48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>※ 행 구분 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +158,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -695,7 +698,7 @@
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
+          <t>1세대 칩 직접 자료 없음 — 원형 닛산 블루버드 실피(G10) 키는 46칩(NI04T) 판매처 표기, 같은 차체 CF 기준 추정</t>
         </is>
       </c>
     </row>
@@ -761,7 +764,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
+          <t>1세대 칩 직접 자료 없음 — 원형 닛산 블루버드 실피(G10) 키는 46칩(NI04T) 판매처 표기, 같은 차체 CF 기준 추정</t>
         </is>
       </c>
     </row>
@@ -827,7 +830,7 @@
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
+          <t>1세대 칩 직접 자료 없음 — 원형 닛산 블루버드 실피(G10) 키는 46칩(NI04T) 판매처 표기, 같은 차체 CF 기준 추정</t>
         </is>
       </c>
     </row>
@@ -893,7 +896,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>1세대 칩 직접 자료 없음 — 같은 차체 페이스리프트(CF) 기준 추정</t>
+          <t>1세대 칩 직접 자료 없음 — 원형 닛산 블루버드 실피(G10) 키는 46칩(NI04T) 판매처 표기, 같은 차체 CF 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4344,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>국내 카드키 칩 직접 자료 없음 — 닛산 티아나 J31 기준 추정</t>
+          <t>국내 카드키 칩 직접 자료 없음 — 2004.12부터 스마트키 적용, 닛산 티아나 J31 인텔리전트 키 ID46(PCF7936) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7909,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr">
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M)</t>
         </is>
@@ -7929,7 +7932,7 @@
       </c>
       <c r="L111" s="9" t="inlineStr"/>
       <c r="M111" s="9" t="inlineStr"/>
-      <c r="N111" s="4" t="inlineStr">
+      <c r="N111" s="12" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
@@ -7939,11 +7942,7 @@
           <t>ko.wikipedia(2024.4.3 르노 아르카나 차명 통일), renault.co.kr(아르카나 버튼시동 스마트카드 기본), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
-      <c r="P111" s="4" t="inlineStr">
-        <is>
-          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
-        </is>
-      </c>
+      <c r="P111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
@@ -7976,7 +7975,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr">
+      <c r="G112" s="12" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M)</t>
         </is>
@@ -7999,7 +7998,7 @@
       </c>
       <c r="L112" s="9" t="inlineStr"/>
       <c r="M112" s="9" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="N112" s="12" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
@@ -8009,11 +8008,7 @@
           <t>ko.wikipedia(1.3 터보 2025.4 생산 중지), keytectools.com(르노 Hitag AES ID4A 2018-2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
-      <c r="P112" s="4" t="inlineStr">
-        <is>
-          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
-        </is>
-      </c>
+      <c r="P112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
@@ -8046,7 +8041,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
+      <c r="G113" s="12" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M)</t>
         </is>
@@ -8069,7 +8064,7 @@
       </c>
       <c r="L113" s="9" t="inlineStr"/>
       <c r="M113" s="9" t="inlineStr"/>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="N113" s="12" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
@@ -8079,11 +8074,7 @@
           <t>renault.co.kr(아르카나 판매 중), keytectools.com(르노 ID4A ~2025), [재조사] autokeymaster.ru(르노 순정 카드 아르카나·메간4·캡처·콜레오스·탈리스만 2015-2024 HITAG AES 434MHz), car-keys-online.com(285979827R은 신형 로고 차량에 사용 불가)</t>
         </is>
       </c>
-      <c r="P113" s="4" t="inlineStr">
-        <is>
-          <t>신형 로고 차량용 카드 품번 미확인(285979827R 불일치 안내 있음)</t>
-        </is>
-      </c>
+      <c r="P113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
@@ -8975,338 +8966,345 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
+      <c r="A2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(SM5 1세대 1998년 출시분도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>- 원본 목록의 연식 범위가 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(SM3 2세대 2009~, SM6·QM6 2025 단종, 클리오는 4세대 2018~2019, 조에 2022 수입 중단, 마스터 밴 2018~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템': 르노 계열은 UCH(메간3/플루언스/래티튜드 세대) → BCM(클리오4·캡처 이후 Hitag AES 세대), 닛산 기반 구형 삼성 차종은 NATS(르노삼성 12자리 코드)로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>- 카드형 스마트키(르노 카드)는 '카드키(부품번호)' 칸에 적었습니다. 부품번호는 동일 플랫폼 르노 차종의 순정 번호(285975779R, 285977147R 등)이며 국내 순정 품번은 대부분 확인되지 않았습니다 — 르노코리아 부품은 VIN(KNMA…)별로 상이.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색에서 직접 나온 경우에만 적었고 나머지는 공란입니다(기아 파일 규칙). 키웨이는 카드 비상키 블레이드 기준(VA2/NSN14 등)입니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 표기 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID4A(Hitag AES)·ID47·ID49·ID8A → X/△/O, 구형(ID46)·신형(AES) 칩이 병기된 행 → △/△/O(기아 파일 혼재 행 규칙). 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 원문 페이지를 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr"/>
+      <c r="A15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>- 주황색: 국내 차종 자료가 없어 닛산/르노 동일 플랫폼 기준으로 추정했거나, 자료 연식 범위 밖이거나, 출처가 상충하는 경우 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
+      <c r="A18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>- [재조사] SM3 CF는 르노삼성이 생산한 닛산 알메라 클래식(러시아)·써니(중동)와 같은 차라 ID46 PCF7936·NSN14로 확인했습니다. SM3 1세대는 같은 차체라 동일 가능성이 높으나 직접 자료는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>- SM5 1·2세대, SM7 1세대는 한국어·러시아·중남미·중동 자료를 다시 찾았지만 칩을 밝힌 자료가 없어 닛산 기준 추정(주황)으로 남겼습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>- [재조사] SM5 3세대·SM7 2세대는 래티튜드용 ID46 카드와 삼성 전용 AES(PCF7945M, 434MHz) 카드가 함께 판매되어 두 칩을 병기했습니다(주황). 285975779R 카드도 후기 순정품에 PCF7953M(4A) 사양이 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>- [재조사] 마스터3는 ID46 PCF7947, 블레이드 VA6 리모컨키입니다(이전 초안의 ID4A 추정은 오류). 그랑 콜레오스는 지리 몬자로 순정 키(Hitag AES 4A / DST AES 8A) 기준입니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>- SM5 2세대·SM7 1세대 카드형 스마트키: 0156 타입(2005~2007)과 T002 타입(2008~, 뉴아트·임프레션)은 서로 호환되지 않습니다. FCC TFWB1J637(312.4MHz).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>- SM3 2세대(플루언스), SM5 3세대·SM7 2세대(래티튜드): ID46 PCF7952 카드 285975779R, VA2, UCH. 2011년경부터 UCH 소프트웨어 변경으로 OBD 등록 제한 자료 있음.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>- QM5(콜레오스 H45): ID46 PCF7952 카드 285979045R(핸즈프리)/285970036R(비핸즈프리), 비상키 NSN14 또는 VA2 두 종류. QM5용 AES(PCF7953) 카드도 존재(적용 연식 미확인).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>- QM3·클리오4: 285971998R(핸즈프리 PCF7953M 4A) / 285974100R(비핸즈프리). SM6·QM6: 285977147R(PCF7953M/NCF29A1M 4A). 캡처2·조에·XM3·아르카나: 285979827R/285973979R(NCF29A1M 4A).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>- 그랑 콜레오스는 지리 싱웨L(몬자로) 기반으로, 키 칩 자료가 없어 지리 자료 기준 추정입니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n"/>
+      <c r="A29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n"/>
+      <c r="A37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="n"/>
+      <c r="A46" s="15" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="n"/>
+      <c r="A48" s="15" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>- 아르카나 2024~: 카드키 칩은 NCF29A1M(ID4A) — 순정 285979827R·285973979R(신형 H-24985 포함) 모두 NCF29A1M 4A(car-keys-online·keystation) 확인, 카드 품번만 차량별 확인</t>
         </is>
       </c>
     </row>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -9197,7 +9197,7 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>

--- a/르노_models.xlsx
+++ b/르노_models.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +158,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -685,7 +688,11 @@
       </c>
       <c r="K2" s="9" t="inlineStr"/>
       <c r="L2" s="9" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-02-0055[리모컨키]</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -751,7 +758,11 @@
       </c>
       <c r="K3" s="9" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-02-0055[리모컨키]</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -817,7 +828,11 @@
       </c>
       <c r="K4" s="9" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-02-0055[리모컨키]</t>
+        </is>
+      </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -883,7 +898,11 @@
       </c>
       <c r="K5" s="9" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-02-0055[리모컨키]</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -949,7 +968,11 @@
       </c>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LARN-04-0381[리모컨키]</t>
+        </is>
+      </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -1011,7 +1034,11 @@
       </c>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LARN-04-0381[리모컨키]</t>
+        </is>
+      </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -1073,7 +1100,11 @@
       </c>
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LARN-04-0381[리모컨키]</t>
+        </is>
+      </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -1135,7 +1166,11 @@
       </c>
       <c r="K9" s="9" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LARN-04-0381[리모컨키, ~2008.5], KC CCP-RSM-T001[리모컨키, 2008.5~]</t>
+        </is>
+      </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -1197,7 +1232,11 @@
       </c>
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>KC CCP-RSM-T001[리모컨키]</t>
+        </is>
+      </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -1259,7 +1298,11 @@
       </c>
       <c r="K11" s="9" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>KC CCP-RSM-T001[리모컨키]</t>
+        </is>
+      </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -1321,7 +1364,11 @@
       </c>
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>KC CCP-RSM-T001[리모컨키]</t>
+        </is>
+      </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
           <t>NATS</t>
@@ -2593,7 +2640,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K31" s="9" t="n"/>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156</t>
+        </is>
+      </c>
       <c r="L31" s="9" t="inlineStr"/>
       <c r="M31" s="9" t="inlineStr"/>
       <c r="N31" s="12" t="inlineStr">
@@ -2655,7 +2706,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K32" s="9" t="n"/>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156</t>
+        </is>
+      </c>
       <c r="L32" s="9" t="inlineStr"/>
       <c r="M32" s="9" t="inlineStr"/>
       <c r="N32" s="12" t="inlineStr">
@@ -2717,7 +2772,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K33" s="9" t="n"/>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156</t>
+        </is>
+      </c>
       <c r="L33" s="9" t="inlineStr"/>
       <c r="M33" s="9" t="inlineStr"/>
       <c r="N33" s="12" t="inlineStr">
@@ -2779,7 +2838,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K34" s="9" t="n"/>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156[~2008.6], KC CCP-RSM-T002[2008.6~]</t>
+        </is>
+      </c>
       <c r="L34" s="9" t="inlineStr"/>
       <c r="M34" s="9" t="inlineStr"/>
       <c r="N34" s="12" t="inlineStr">
@@ -2841,7 +2904,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K35" s="9" t="n"/>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>KC CCP-RSM-T002</t>
+        </is>
+      </c>
       <c r="L35" s="9" t="inlineStr"/>
       <c r="M35" s="9" t="inlineStr"/>
       <c r="N35" s="12" t="inlineStr">
@@ -2903,7 +2970,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K36" s="9" t="n"/>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>KC CCP-RSM-T002</t>
+        </is>
+      </c>
       <c r="L36" s="9" t="inlineStr"/>
       <c r="M36" s="9" t="inlineStr"/>
       <c r="N36" s="12" t="inlineStr">
@@ -4329,7 +4400,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K57" s="9" t="n"/>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156</t>
+        </is>
+      </c>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
       <c r="N57" s="4" t="inlineStr">
@@ -4395,7 +4470,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K58" s="9" t="n"/>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156</t>
+        </is>
+      </c>
       <c r="L58" s="9" t="inlineStr"/>
       <c r="M58" s="9" t="inlineStr"/>
       <c r="N58" s="12" t="inlineStr">
@@ -4457,7 +4536,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K59" s="9" t="n"/>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156</t>
+        </is>
+      </c>
       <c r="L59" s="9" t="inlineStr"/>
       <c r="M59" s="9" t="inlineStr"/>
       <c r="N59" s="12" t="inlineStr">
@@ -4519,7 +4602,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K60" s="9" t="n"/>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156</t>
+        </is>
+      </c>
       <c r="L60" s="9" t="inlineStr"/>
       <c r="M60" s="9" t="inlineStr"/>
       <c r="N60" s="12" t="inlineStr">
@@ -4581,7 +4668,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K61" s="9" t="n"/>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>KC R-LPD1-04-0156[~2008.6], KC CCP-RSM-T002[2008.6~]</t>
+        </is>
+      </c>
       <c r="L61" s="9" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr"/>
       <c r="N61" s="12" t="inlineStr">
@@ -4643,7 +4734,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K62" s="9" t="n"/>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>KC CCP-RSM-T002</t>
+        </is>
+      </c>
       <c r="L62" s="9" t="inlineStr"/>
       <c r="M62" s="9" t="inlineStr"/>
       <c r="N62" s="12" t="inlineStr">
@@ -4705,7 +4800,11 @@
           <t>NSN14[추정]</t>
         </is>
       </c>
-      <c r="K63" s="9" t="n"/>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>KC CCP-RSM-T002</t>
+        </is>
+      </c>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
       <c r="N63" s="12" t="inlineStr">
@@ -8966,7 +9065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -9308,6 +9407,13 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>- 르노(르노삼성) 구형 키: 르노코리아 순정부품몰 mrsmall.co.kr 상품 설명의 제품 라벨(한국 전파인증 번호) — 순정 부품번호는 몰에 공개되지 않아 KC 번호만 기재. SM3 리모컨키 R-LPD1-02-0055(TFWB1J631, 한국알프스), 뉴SM3 리모컨키 R-LARN-04-0381(TFWB1J636, ~2008.5)·CCP-RSM-T001(RSM-T001, 2008.5~), SM5 2세대(EX)·SM7 1세대 스마트카드 R-LPD1-04-0156(TFWB1J637, ~2008.6)·CCP-RSM-T002(RSM-T002, 2008.6~)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
